--- a/ACTRIS_controlled_lists.xlsx
+++ b/ACTRIS_controlled_lists.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nilu365.sharepoint.com/sites/Project-ACTRIS/Shared Documents/WP2 - In-Situ/vocabulary/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{F560E02F-C79E-4580-AD8B-7309379EF73D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3A296F2-7636-4B95-81FF-9776BBB72405}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="8_{911A0C87-C02C-46F4-977B-819E7E5B7217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DECFD8D7-BD08-4E9A-8912-5D6E40D94C3F}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="46605" windowHeight="18075" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23550" yWindow="2100" windowWidth="25230" windowHeight="17685" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controlled-terminology" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="440">
   <si>
     <t xml:space="preserve">ConceptScheme URI </t>
   </si>
@@ -1192,16 +1192,196 @@
     <t>Open Researcher and Contributor ID</t>
   </si>
   <si>
-    <t>2026-08-03T16:50:00+02:00</t>
-  </si>
-  <si>
-    <t>1.1.1</t>
+    <t>1.1.2</t>
+  </si>
+  <si>
+    <t>AutoPollen</t>
+  </si>
+  <si>
+    <t>EMEP_campaign</t>
+  </si>
+  <si>
+    <t>CAPMoN</t>
+  </si>
+  <si>
+    <t>CARIBIC</t>
+  </si>
+  <si>
+    <t>EANET</t>
+  </si>
+  <si>
+    <t>EUCAARI</t>
+  </si>
+  <si>
+    <t>GEOmon</t>
+  </si>
+  <si>
+    <t>IMPACTS</t>
+  </si>
+  <si>
+    <t>IMPROVE</t>
+  </si>
+  <si>
+    <t>INDAAF</t>
+  </si>
+  <si>
+    <t>no framework</t>
+  </si>
+  <si>
+    <t>InGOS</t>
+  </si>
+  <si>
+    <t>MAMCS</t>
+  </si>
+  <si>
+    <t>MOCA</t>
+  </si>
+  <si>
+    <t>MOE</t>
+  </si>
+  <si>
+    <t>NAtChem</t>
+  </si>
+  <si>
+    <t>NOAA-GGGRN</t>
+  </si>
+  <si>
+    <t>OECD</t>
+  </si>
+  <si>
+    <t>PARIS</t>
+  </si>
+  <si>
+    <t>PollenScience</t>
+  </si>
+  <si>
+    <t>ReGAME</t>
+  </si>
+  <si>
+    <t>ROSHYDROMET</t>
+  </si>
+  <si>
+    <t>SOGE</t>
+  </si>
+  <si>
+    <t>SYLVA</t>
+  </si>
+  <si>
+    <t>UK DECC</t>
+  </si>
+  <si>
+    <t>WeBaSOOP</t>
+  </si>
+  <si>
+    <t>Baltic Marine Environment Protection Commission - Helsinki Commission</t>
+  </si>
+  <si>
+    <t>Atmospheric monitoring data for the assessment of the atmospheric input of selected contaminants to the Baltic sea area.</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0002-3500-6096</t>
+  </si>
+  <si>
+    <t>ACTRIS is the European Research Infrastructure for the observation of Aerosol, Clouds, and Trace gases. ACTRIS is composed of observing stations, exploratory platforms, instruments calibration centres, and a data centre.</t>
+  </si>
+  <si>
+    <t>ATMO-ACCESS is the organized response of distributed atmospheric research facilities for developing a pilot for a new model of Integrating Activities. The project will deliver a series of recommendations for establishing a comprehensive and sustainable framework for access to distributed atmospheric Research Infrastructures (RI), ensuring integrated access to and optimised use of the services they provide.</t>
+  </si>
+  <si>
+    <t>European Monitoring and Evaluation Programme</t>
+  </si>
+  <si>
+    <t>The European Monitoring and Evaluation Programme (EMEP) is a scientifically based and policy driven programme under the Convention on Long-range Transboundary Air Pollution (CLRTAP) for int'l co-operation to solve transboundary air pollution problems.</t>
+  </si>
+  <si>
+    <t>European Supersites for Atmospheric Aerosol Research</t>
+  </si>
+  <si>
+    <t>Integration of measurements of atmospheric aerosol properties performed in a distributed network of 20 high quality European ground-based stations in support of policy issues on air quality, long-range transport of pollutants and climate change.</t>
+  </si>
+  <si>
+    <t>World Data Centre for Aerosols</t>
+  </si>
+  <si>
+    <t>The World Data Centre for Aerosols is the data repository and archive for microphysical, optical, and chemical properties of atmospheric aerosol of the World Meteorological Organisation's (WMO) Global Atmosphere Watch (GAW) programme.</t>
+  </si>
+  <si>
+    <t>World Data Centre for Reactive Gases</t>
+  </si>
+  <si>
+    <t>The World Data Centre for Reactive Gases is the data repository and archive for reactive gases of the World Meteorological Organisation's (WMO) Global Atmosphere Watch (GAW) programme.</t>
+  </si>
+  <si>
+    <t>German Ultrafine Aerosol Networ</t>
+  </si>
+  <si>
+    <t>GUAN is a joint observation network, which aims to improve our understanding of atmospheric aerosol particles with regard to human particle exposure and aerosol climate effects.</t>
+  </si>
+  <si>
+    <t>Norwegian Institute for Air Research</t>
+  </si>
+  <si>
+    <t>Atmospheric measuremnts produced at NILU.</t>
+  </si>
+  <si>
+    <t>International Network to study Deposition and Atmospheric chemistry in AFrica</t>
+  </si>
+  <si>
+    <t>Atmospheric composition and deposition long-term monitoring in Africa</t>
+  </si>
+  <si>
+    <t>Mediterranean atmospheric mercury cycle system</t>
+  </si>
+  <si>
+    <t>Process Attribution of Regional Emissions</t>
+  </si>
+  <si>
+    <t>“Process Attribution of Regional Emissions“  (PARIS) is a 4-year Horizon Europe research project (2023-2026). We aim to significantly increase our knowledge about the emissions of climate forcers from eight European countries. PARIS focuses on the interface between bottom-up and top-down approaches and aims to strengthen the collaboration between scientists and national inventory teams for the evaluation and development of national inventories.</t>
+  </si>
+  <si>
+    <t>Pollen Science</t>
+  </si>
+  <si>
+    <t>The aim of Pollen Science is to collect and graphically display the data of different pollen measurement networks and stations.</t>
+  </si>
+  <si>
+    <t>EUMETNET AutoPollen programme</t>
+  </si>
+  <si>
+    <t>Automatic European pollen monitoring network, integrating developing and planned projects</t>
+  </si>
+  <si>
+    <t>The overall goal of SYLVA is to achieve a radical improvement and fill gaps in temporal resolution, timeliness, coverage, and availability of information about aeroalaeroallergens and other bioaerosols</t>
+  </si>
+  <si>
+    <t>Methane emissions from the Arctic OCean to the Atmosphere</t>
+  </si>
+  <si>
+    <t>MOCA is a project funded by the Norwegian Research Council that will apply advanced measurements and modelling to quantify the amount and present atmospheric impact of CH4 originating from MH.</t>
+  </si>
+  <si>
+    <t>Sustainable Access to Atmospheric Research Facilities</t>
+  </si>
+  <si>
+    <t>European Research Infrastructure for the observation of Aerosol, Clouds, and Trace gases</t>
+  </si>
+  <si>
+    <t>REliable Global Methane Emissions estimates in a changing world</t>
+  </si>
+  <si>
+    <t>In ReGAME, Reliable Global Methane Emissions estimates in a changing world, we integrate new measurement technologies into models to determine why atmospheric methane (CH4) is increasing, and whether climate-sensitive Arctic CH4 reservoirs will release significant CH4 to the atmosphere</t>
+  </si>
+  <si>
+    <t>Research Reinforcing in the Western Balkans in Offline and Online Monitoring and Source Identification of Atmospheric Particles</t>
   </si>
   <si>
     <t>https://vocabulary.actris.nilu.no/actris_controlled_lists/</t>
   </si>
   <si>
     <t>https://vocabulary.actris.nilu.no/actris_vocab/</t>
+  </si>
+  <si>
+    <t>2026-09-015T15:50:00+02:00</t>
   </si>
 </sst>
 </file>
@@ -1856,7 +2036,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P255"/>
+  <dimension ref="A1:P281"/>
   <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="56.77734375" style="1" customWidth="1"/>
@@ -1878,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>378</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75">
@@ -1889,7 +2069,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>378</v>
+        <v>437</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75">
@@ -1900,7 +2080,7 @@
         <v>149</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>379</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75">
@@ -1997,7 +2177,7 @@
         <v>22</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>376</v>
+        <v>439</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.75">
@@ -2005,7 +2185,7 @@
         <v>23</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1">
@@ -3004,7 +3184,7 @@
     </row>
     <row r="53" spans="1:16" ht="17.25" customHeight="1">
       <c r="A53" s="14" t="str">
-        <f t="shared" ref="A53:A102" si="1">IF(ISBLANK($B53),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
+        <f t="shared" ref="A53:A119" si="1">IF(ISBLANK($B53),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
         <v>ACTRIS_ctrl_lists:distributor</v>
       </c>
       <c r="B53" s="16" t="s">
@@ -3942,9 +4122,7 @@
       <c r="N85" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="O85" s="12" t="s">
-        <v>44</v>
-      </c>
+      <c r="O85" s="12"/>
       <c r="P85" s="12"/>
     </row>
     <row r="86" spans="1:16" ht="16.5" customHeight="1">
@@ -3955,8 +4133,12 @@
       <c r="B86" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="C86" s="17"/>
-      <c r="D86" s="16"/>
+      <c r="C86" s="17" t="s">
+        <v>433</v>
+      </c>
+      <c r="D86" s="16" t="s">
+        <v>406</v>
+      </c>
       <c r="E86" s="16" t="s">
         <v>113</v>
       </c>
@@ -3971,18 +4153,16 @@
       <c r="N86" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="O86" s="17" t="s">
-        <v>44</v>
-      </c>
+      <c r="O86" s="17"/>
       <c r="P86" s="17"/>
     </row>
-    <row r="87" spans="1:16" ht="16.5" customHeight="1">
+    <row r="87" spans="1:16" ht="17.25" customHeight="1">
       <c r="A87" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>ACTRIS_ctrl_lists:AMAP</v>
+        <v>ACTRIS_ctrl_lists:AERONET</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C87" s="17"/>
       <c r="D87" s="16"/>
@@ -4000,18 +4180,16 @@
       <c r="N87" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="O87" s="17" t="s">
-        <v>44</v>
-      </c>
+      <c r="O87" s="17"/>
       <c r="P87" s="17"/>
     </row>
     <row r="88" spans="1:16" ht="16.5" customHeight="1">
       <c r="A88" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>ACTRIS_ctrl_lists:ARM</v>
+        <v>ACTRIS_ctrl_lists:AMAP</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C88" s="17"/>
       <c r="D88" s="16"/>
@@ -4029,18 +4207,16 @@
       <c r="N88" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="O88" s="17" t="s">
-        <v>44</v>
-      </c>
+      <c r="O88" s="17"/>
       <c r="P88" s="17"/>
     </row>
     <row r="89" spans="1:16" ht="16.5" customHeight="1">
       <c r="A89" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>ACTRIS_ctrl_lists:ATMO-ACCESS</v>
+        <v>ACTRIS_ctrl_lists:ARM</v>
       </c>
       <c r="B89" s="16" t="s">
-        <v>232</v>
+        <v>115</v>
       </c>
       <c r="C89" s="17"/>
       <c r="D89" s="16"/>
@@ -4055,20 +4231,26 @@
       <c r="K89" s="17"/>
       <c r="L89" s="17"/>
       <c r="M89" s="17"/>
-      <c r="N89" s="18"/>
+      <c r="N89" s="18" t="s">
+        <v>43</v>
+      </c>
       <c r="O89" s="17"/>
       <c r="P89" s="17"/>
     </row>
     <row r="90" spans="1:16" ht="16.5" customHeight="1">
       <c r="A90" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>ACTRIS_ctrl_lists:CAMP</v>
+        <v>ACTRIS_ctrl_lists:ATMO-ACCESS</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="C90" s="17"/>
-      <c r="D90" s="16"/>
+        <v>232</v>
+      </c>
+      <c r="C90" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="D90" s="16" t="s">
+        <v>407</v>
+      </c>
       <c r="E90" s="16" t="s">
         <v>113</v>
       </c>
@@ -4083,21 +4265,23 @@
       <c r="N90" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="O90" s="17" t="s">
-        <v>44</v>
-      </c>
+      <c r="O90" s="17"/>
       <c r="P90" s="17"/>
     </row>
     <row r="91" spans="1:16" ht="16.5" customHeight="1">
       <c r="A91" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>ACTRIS_ctrl_lists:CLOUDNET</v>
+        <v>ACTRIS_ctrl_lists:AutoPollen</v>
       </c>
       <c r="B91" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C91" s="17"/>
-      <c r="D91" s="16"/>
+        <v>377</v>
+      </c>
+      <c r="C91" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="D91" s="16" t="s">
+        <v>428</v>
+      </c>
       <c r="E91" s="16" t="s">
         <v>113</v>
       </c>
@@ -4112,18 +4296,16 @@
       <c r="N91" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="O91" s="17" t="s">
-        <v>44</v>
-      </c>
+      <c r="O91" s="17"/>
       <c r="P91" s="17"/>
     </row>
     <row r="92" spans="1:16" ht="16.5" customHeight="1">
       <c r="A92" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>ACTRIS_ctrl_lists:CREATE</v>
+        <v>ACTRIS_ctrl_lists:CAMP</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C92" s="17"/>
       <c r="D92" s="16"/>
@@ -4141,18 +4323,16 @@
       <c r="N92" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="O92" s="17" t="s">
-        <v>44</v>
-      </c>
+      <c r="O92" s="17"/>
       <c r="P92" s="17"/>
     </row>
     <row r="93" spans="1:16" ht="16.5" customHeight="1">
       <c r="A93" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>ACTRIS_ctrl_lists:EARLINET</v>
+        <v>ACTRIS_ctrl_lists:CAPMoN</v>
       </c>
       <c r="B93" s="16" t="s">
-        <v>119</v>
+        <v>379</v>
       </c>
       <c r="C93" s="17"/>
       <c r="D93" s="16"/>
@@ -4170,18 +4350,16 @@
       <c r="N93" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="O93" s="17" t="s">
-        <v>44</v>
-      </c>
+      <c r="O93" s="17"/>
       <c r="P93" s="17"/>
     </row>
     <row r="94" spans="1:16" ht="16.5" customHeight="1">
       <c r="A94" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>ACTRIS_ctrl_lists:EMEP</v>
+        <v>ACTRIS_ctrl_lists:CARIBIC</v>
       </c>
       <c r="B94" s="16" t="s">
-        <v>120</v>
+        <v>380</v>
       </c>
       <c r="C94" s="17"/>
       <c r="D94" s="16"/>
@@ -4199,18 +4377,16 @@
       <c r="N94" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="O94" s="17" t="s">
-        <v>44</v>
-      </c>
+      <c r="O94" s="17"/>
       <c r="P94" s="17"/>
     </row>
     <row r="95" spans="1:16" ht="16.5" customHeight="1">
       <c r="A95" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>ACTRIS_ctrl_lists:EUROCHAMP</v>
+        <v>ACTRIS_ctrl_lists:CLOUDNET</v>
       </c>
       <c r="B95" s="16" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C95" s="17"/>
       <c r="D95" s="16"/>
@@ -4228,18 +4404,16 @@
       <c r="N95" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="O95" s="17" t="s">
-        <v>44</v>
-      </c>
+      <c r="O95" s="17"/>
       <c r="P95" s="17"/>
     </row>
     <row r="96" spans="1:16" ht="16.5" customHeight="1">
       <c r="A96" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>ACTRIS_ctrl_lists:EUSAAR</v>
+        <v>ACTRIS_ctrl_lists:CREATE</v>
       </c>
       <c r="B96" s="16" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C96" s="17"/>
       <c r="D96" s="16"/>
@@ -4257,18 +4431,16 @@
       <c r="N96" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="O96" s="17" t="s">
-        <v>44</v>
-      </c>
+      <c r="O96" s="17"/>
       <c r="P96" s="17"/>
     </row>
     <row r="97" spans="1:16" ht="16.5" customHeight="1">
       <c r="A97" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>ACTRIS_ctrl_lists:GAW-WDCA</v>
+        <v>ACTRIS_ctrl_lists:EANET</v>
       </c>
       <c r="B97" s="16" t="s">
-        <v>123</v>
+        <v>381</v>
       </c>
       <c r="C97" s="17"/>
       <c r="D97" s="16"/>
@@ -4286,18 +4458,16 @@
       <c r="N97" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="O97" s="17" t="s">
-        <v>44</v>
-      </c>
+      <c r="O97" s="17"/>
       <c r="P97" s="17"/>
     </row>
     <row r="98" spans="1:16" ht="16.5" customHeight="1">
       <c r="A98" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>ACTRIS_ctrl_lists:GAW-WDCRG</v>
+        <v>ACTRIS_ctrl_lists:EARLINET</v>
       </c>
       <c r="B98" s="16" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C98" s="17"/>
       <c r="D98" s="16"/>
@@ -4315,21 +4485,23 @@
       <c r="N98" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="O98" s="17" t="s">
-        <v>44</v>
-      </c>
+      <c r="O98" s="17"/>
       <c r="P98" s="17"/>
     </row>
     <row r="99" spans="1:16" ht="16.5" customHeight="1">
       <c r="A99" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>ACTRIS_ctrl_lists:GUAN</v>
+        <v>ACTRIS_ctrl_lists:EMEP</v>
       </c>
       <c r="B99" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="C99" s="17"/>
-      <c r="D99" s="16"/>
+        <v>120</v>
+      </c>
+      <c r="C99" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="D99" s="16" t="s">
+        <v>409</v>
+      </c>
       <c r="E99" s="16" t="s">
         <v>113</v>
       </c>
@@ -4344,18 +4516,16 @@
       <c r="N99" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="O99" s="17" t="s">
-        <v>44</v>
-      </c>
+      <c r="O99" s="17"/>
       <c r="P99" s="17"/>
     </row>
     <row r="100" spans="1:16" ht="16.5" customHeight="1">
       <c r="A100" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>ACTRIS_ctrl_lists:HELCOM</v>
+        <v>ACTRIS_ctrl_lists:EMEP_campaign</v>
       </c>
       <c r="B100" s="16" t="s">
-        <v>126</v>
+        <v>378</v>
       </c>
       <c r="C100" s="17"/>
       <c r="D100" s="16"/>
@@ -4373,18 +4543,16 @@
       <c r="N100" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="O100" s="17" t="s">
-        <v>44</v>
-      </c>
+      <c r="O100" s="17"/>
       <c r="P100" s="17"/>
     </row>
     <row r="101" spans="1:16" ht="16.5" customHeight="1">
       <c r="A101" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>ACTRIS_ctrl_lists:NDACC</v>
+        <v>ACTRIS_ctrl_lists:EUCAARI</v>
       </c>
       <c r="B101" s="16" t="s">
-        <v>127</v>
+        <v>382</v>
       </c>
       <c r="C101" s="17"/>
       <c r="D101" s="16"/>
@@ -4402,18 +4570,16 @@
       <c r="N101" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="O101" s="17" t="s">
-        <v>44</v>
-      </c>
+      <c r="O101" s="17"/>
       <c r="P101" s="17"/>
     </row>
     <row r="102" spans="1:16" ht="16.5" customHeight="1">
       <c r="A102" s="14" t="str">
         <f t="shared" si="1"/>
-        <v>ACTRIS_ctrl_lists:NILU</v>
+        <v>ACTRIS_ctrl_lists:EUROCHAMP</v>
       </c>
       <c r="B102" s="16" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C102" s="17"/>
       <c r="D102" s="16"/>
@@ -4431,21 +4597,23 @@
       <c r="N102" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="O102" s="17" t="s">
-        <v>44</v>
-      </c>
+      <c r="O102" s="17"/>
       <c r="P102" s="17"/>
     </row>
-    <row r="103" spans="1:16" ht="17.25" customHeight="1">
+    <row r="103" spans="1:16" ht="16.5" customHeight="1">
       <c r="A103" s="14" t="str">
-        <f t="shared" ref="A103:A187" si="4">IF(ISBLANK($B103),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B103," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
-        <v>ACTRIS_ctrl_lists:NOAA-ESRL</v>
+        <f t="shared" si="1"/>
+        <v>ACTRIS_ctrl_lists:EUSAAR</v>
       </c>
       <c r="B103" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="C103" s="17"/>
-      <c r="D103" s="16"/>
+        <v>122</v>
+      </c>
+      <c r="C103" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="D103" s="16" t="s">
+        <v>411</v>
+      </c>
       <c r="E103" s="16" t="s">
         <v>113</v>
       </c>
@@ -4460,14 +4628,12 @@
       <c r="N103" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="O103" s="17" t="s">
-        <v>44</v>
-      </c>
+      <c r="O103" s="17"/>
       <c r="P103" s="17"/>
     </row>
     <row r="104" spans="1:16" ht="17.25" customHeight="1">
       <c r="A104" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>ACTRIS_ctrl_lists:GALION</v>
       </c>
       <c r="B104" s="16" t="s">
@@ -4492,16 +4658,20 @@
       <c r="O104" s="17"/>
       <c r="P104" s="17"/>
     </row>
-    <row r="105" spans="1:16" ht="17.25" customHeight="1">
+    <row r="105" spans="1:16" ht="16.5" customHeight="1">
       <c r="A105" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:AERONET</v>
+        <f t="shared" si="1"/>
+        <v>ACTRIS_ctrl_lists:GAW-WDCA</v>
       </c>
       <c r="B105" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="C105" s="17"/>
-      <c r="D105" s="16"/>
+        <v>123</v>
+      </c>
+      <c r="C105" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="D105" s="16" t="s">
+        <v>413</v>
+      </c>
       <c r="E105" s="16" t="s">
         <v>113</v>
       </c>
@@ -4516,19 +4686,25 @@
       <c r="N105" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="O105" s="17"/>
+      <c r="O105" s="17" t="s">
+        <v>43</v>
+      </c>
       <c r="P105" s="17"/>
     </row>
-    <row r="106" spans="1:16" ht="17.25" customHeight="1">
+    <row r="106" spans="1:16" ht="16.5" customHeight="1">
       <c r="A106" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:RI-URBANS</v>
+        <f t="shared" si="1"/>
+        <v>ACTRIS_ctrl_lists:GAW-WDCRG</v>
       </c>
       <c r="B106" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="C106" s="17"/>
-      <c r="D106" s="16"/>
+        <v>124</v>
+      </c>
+      <c r="C106" s="17" t="s">
+        <v>414</v>
+      </c>
+      <c r="D106" s="16" t="s">
+        <v>415</v>
+      </c>
       <c r="E106" s="16" t="s">
         <v>113</v>
       </c>
@@ -4543,18 +4719,24 @@
       <c r="N106" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="O106" s="17"/>
+      <c r="O106" s="17" t="s">
+        <v>143</v>
+      </c>
       <c r="P106" s="17"/>
     </row>
-    <row r="107" spans="1:16" ht="17.25" customHeight="1">
+    <row r="107" spans="1:16" ht="16.5" customHeight="1">
       <c r="A107" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="B107" s="16"/>
+        <f t="shared" si="1"/>
+        <v>ACTRIS_ctrl_lists:GEOmon</v>
+      </c>
+      <c r="B107" s="16" t="s">
+        <v>383</v>
+      </c>
       <c r="C107" s="17"/>
       <c r="D107" s="16"/>
-      <c r="E107" s="16"/>
+      <c r="E107" s="16" t="s">
+        <v>113</v>
+      </c>
       <c r="F107" s="17"/>
       <c r="G107" s="17"/>
       <c r="H107" s="17"/>
@@ -4563,16 +4745,29 @@
       <c r="K107" s="17"/>
       <c r="L107" s="17"/>
       <c r="M107" s="17"/>
-      <c r="N107" s="22"/>
+      <c r="N107" s="18" t="s">
+        <v>43</v>
+      </c>
       <c r="O107" s="17"/>
       <c r="P107" s="17"/>
     </row>
-    <row r="108" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A108" s="14"/>
-      <c r="B108" s="16"/>
-      <c r="C108" s="17"/>
-      <c r="D108" s="16"/>
-      <c r="E108" s="16"/>
+    <row r="108" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A108" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>ACTRIS_ctrl_lists:GUAN</v>
+      </c>
+      <c r="B108" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="C108" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="D108" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="E108" s="16" t="s">
+        <v>113</v>
+      </c>
       <c r="F108" s="17"/>
       <c r="G108" s="17"/>
       <c r="H108" s="17"/>
@@ -4581,72 +4776,85 @@
       <c r="K108" s="17"/>
       <c r="L108" s="17"/>
       <c r="M108" s="17"/>
-      <c r="N108" s="22"/>
+      <c r="N108" s="18" t="s">
+        <v>43</v>
+      </c>
       <c r="O108" s="17"/>
       <c r="P108" s="17"/>
     </row>
-    <row r="109" spans="1:16" ht="15" customHeight="1">
-      <c r="A109" s="11" t="str">
-        <f t="shared" ref="A109:A110" si="5">IF(ISBLANK($B109),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B109," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
-        <v>ACTRIS_ctrl_lists:Glossary</v>
-      </c>
-      <c r="B109" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="C109" s="12"/>
-      <c r="D109" s="12"/>
-      <c r="E109" s="12"/>
-      <c r="F109" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="G109" s="12"/>
-      <c r="H109" s="12"/>
-      <c r="I109" s="12"/>
-      <c r="J109" s="12"/>
-      <c r="K109" s="12"/>
-      <c r="L109" s="12"/>
-      <c r="M109" s="12"/>
-      <c r="N109" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="O109" s="12"/>
-      <c r="P109" s="12"/>
-    </row>
-    <row r="110" spans="1:16" ht="17.25" customHeight="1">
+    <row r="109" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A109" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>ACTRIS_ctrl_lists:HELCOM</v>
+      </c>
+      <c r="B109" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C109" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="D109" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="E109" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="F109" s="17"/>
+      <c r="G109" s="17"/>
+      <c r="H109" s="17"/>
+      <c r="I109" s="17"/>
+      <c r="J109" s="17"/>
+      <c r="K109" s="17"/>
+      <c r="L109" s="17"/>
+      <c r="M109" s="17"/>
+      <c r="N109" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="O109" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="P109" s="17"/>
+    </row>
+    <row r="110" spans="1:16" ht="16.5" customHeight="1">
       <c r="A110" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>ACTRIS_ctrl_lists:ACTRISdata</v>
+        <f t="shared" si="1"/>
+        <v>ACTRIS_ctrl_lists:IMPACTS</v>
       </c>
       <c r="B110" s="16" t="s">
-        <v>146</v>
+        <v>384</v>
       </c>
       <c r="C110" s="17"/>
-      <c r="D110" s="16" t="s">
-        <v>151</v>
-      </c>
+      <c r="D110" s="16"/>
       <c r="E110" s="16" t="s">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="F110" s="17"/>
       <c r="G110" s="17"/>
-      <c r="H110" s="17" t="s">
-        <v>150</v>
-      </c>
+      <c r="H110" s="17"/>
       <c r="I110" s="17"/>
       <c r="J110" s="17"/>
       <c r="K110" s="17"/>
       <c r="L110" s="17"/>
       <c r="M110" s="17"/>
-      <c r="N110" s="22"/>
+      <c r="N110" s="18" t="s">
+        <v>43</v>
+      </c>
       <c r="O110" s="17"/>
       <c r="P110" s="17"/>
     </row>
-    <row r="111" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A111" s="14"/>
-      <c r="B111" s="16"/>
+    <row r="111" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A111" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>ACTRIS_ctrl_lists:IMPROVE</v>
+      </c>
+      <c r="B111" s="16" t="s">
+        <v>385</v>
+      </c>
       <c r="C111" s="17"/>
       <c r="D111" s="16"/>
-      <c r="E111" s="16"/>
+      <c r="E111" s="16" t="s">
+        <v>113</v>
+      </c>
       <c r="F111" s="17"/>
       <c r="G111" s="17"/>
       <c r="H111" s="17"/>
@@ -4655,78 +4863,84 @@
       <c r="K111" s="17"/>
       <c r="L111" s="17"/>
       <c r="M111" s="17"/>
-      <c r="N111" s="22"/>
+      <c r="N111" s="18" t="s">
+        <v>43</v>
+      </c>
       <c r="O111" s="17"/>
       <c r="P111" s="17"/>
     </row>
-    <row r="112" spans="1:16" ht="15" customHeight="1">
-      <c r="A112" s="11" t="str">
-        <f t="shared" ref="A112:A138" si="6">IF(ISBLANK($B112),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
-        <v>ACTRIS_ctrl_lists:calibrationscale</v>
-      </c>
-      <c r="B112" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="C112" s="12"/>
-      <c r="D112" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="E112" s="12"/>
-      <c r="F112" s="12"/>
-      <c r="G112" s="12"/>
-      <c r="H112" s="12"/>
-      <c r="I112" s="12"/>
-      <c r="J112" s="12"/>
-      <c r="K112" s="12"/>
-      <c r="L112" s="12"/>
-      <c r="M112" s="12"/>
-      <c r="N112" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="O112" s="12"/>
-      <c r="P112" s="12"/>
-    </row>
-    <row r="113" spans="1:16" ht="17.25" customHeight="1">
+    <row r="112" spans="1:16" ht="16.5" customHeight="1">
+      <c r="A112" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>ACTRIS_ctrl_lists:INDAAF</v>
+      </c>
+      <c r="B112" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="C112" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="D112" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="E112" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="F112" s="17"/>
+      <c r="G112" s="17"/>
+      <c r="H112" s="17"/>
+      <c r="I112" s="17"/>
+      <c r="J112" s="17"/>
+      <c r="K112" s="17"/>
+      <c r="L112" s="17"/>
+      <c r="M112" s="17"/>
+      <c r="N112" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="O112" s="17"/>
+      <c r="P112" s="17"/>
+    </row>
+    <row r="113" spans="1:16" ht="16.5" customHeight="1">
       <c r="A113" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>ACTRIS_ctrl_lists:Apel-Riemer</v>
+        <f t="shared" si="1"/>
+        <v>ACTRIS_ctrl_lists:InGOS</v>
       </c>
       <c r="B113" s="16" t="s">
-        <v>206</v>
+        <v>388</v>
       </c>
       <c r="C113" s="17"/>
       <c r="D113" s="16"/>
       <c r="E113" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F113" s="17"/>
       <c r="G113" s="17"/>
-      <c r="H113" s="17" t="s">
-        <v>150</v>
-      </c>
+      <c r="H113" s="17"/>
       <c r="I113" s="17"/>
       <c r="J113" s="17"/>
       <c r="K113" s="17"/>
       <c r="L113" s="17"/>
       <c r="M113" s="17"/>
-      <c r="N113" s="22" t="s">
+      <c r="N113" s="18" t="s">
         <v>43</v>
       </c>
       <c r="O113" s="17"/>
       <c r="P113" s="17"/>
     </row>
-    <row r="114" spans="1:16" ht="17.25" customHeight="1">
+    <row r="114" spans="1:16" ht="16.5" customHeight="1">
       <c r="A114" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>ACTRIS_ctrl_lists:Empa-2015-p</v>
+        <f t="shared" si="1"/>
+        <v>ACTRIS_ctrl_lists:MAMCS</v>
       </c>
       <c r="B114" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="C114" s="17"/>
+        <v>389</v>
+      </c>
+      <c r="C114" s="17" t="s">
+        <v>422</v>
+      </c>
       <c r="D114" s="16"/>
       <c r="E114" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F114" s="17"/>
       <c r="G114" s="17"/>
@@ -4736,24 +4950,28 @@
       <c r="K114" s="17"/>
       <c r="L114" s="17"/>
       <c r="M114" s="17"/>
-      <c r="N114" s="22" t="s">
+      <c r="N114" s="18" t="s">
         <v>43</v>
       </c>
       <c r="O114" s="17"/>
       <c r="P114" s="17"/>
     </row>
-    <row r="115" spans="1:16" ht="17.25" customHeight="1">
+    <row r="115" spans="1:16" ht="16.5" customHeight="1">
       <c r="A115" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>ACTRIS_ctrl_lists:MPI-2009</v>
+        <f t="shared" si="1"/>
+        <v>ACTRIS_ctrl_lists:MOCA</v>
       </c>
       <c r="B115" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="C115" s="17"/>
-      <c r="D115" s="16"/>
+        <v>390</v>
+      </c>
+      <c r="C115" s="17" t="s">
+        <v>430</v>
+      </c>
+      <c r="D115" s="16" t="s">
+        <v>431</v>
+      </c>
       <c r="E115" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F115" s="17"/>
       <c r="G115" s="17"/>
@@ -4763,24 +4981,24 @@
       <c r="K115" s="17"/>
       <c r="L115" s="17"/>
       <c r="M115" s="17"/>
-      <c r="N115" s="22" t="s">
+      <c r="N115" s="18" t="s">
         <v>43</v>
       </c>
       <c r="O115" s="17"/>
       <c r="P115" s="17"/>
     </row>
-    <row r="116" spans="1:16" ht="17.25" customHeight="1">
+    <row r="116" spans="1:16" ht="16.5" customHeight="1">
       <c r="A116" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>ACTRIS_ctrl_lists:NOAA-2003</v>
+        <f t="shared" si="1"/>
+        <v>ACTRIS_ctrl_lists:MOE</v>
       </c>
       <c r="B116" s="16" t="s">
-        <v>213</v>
+        <v>391</v>
       </c>
       <c r="C116" s="17"/>
       <c r="D116" s="16"/>
       <c r="E116" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F116" s="17"/>
       <c r="G116" s="17"/>
@@ -4790,24 +5008,24 @@
       <c r="K116" s="17"/>
       <c r="L116" s="17"/>
       <c r="M116" s="17"/>
-      <c r="N116" s="22" t="s">
+      <c r="N116" s="18" t="s">
         <v>43</v>
       </c>
       <c r="O116" s="17"/>
       <c r="P116" s="17"/>
     </row>
-    <row r="117" spans="1:16" ht="17.25" customHeight="1">
+    <row r="117" spans="1:16" ht="16.5" customHeight="1">
       <c r="A117" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>ACTRIS_ctrl_lists:NOAA-2003B</v>
+        <f t="shared" si="1"/>
+        <v>ACTRIS_ctrl_lists:NAtChem</v>
       </c>
       <c r="B117" s="16" t="s">
-        <v>208</v>
+        <v>392</v>
       </c>
       <c r="C117" s="17"/>
       <c r="D117" s="16"/>
       <c r="E117" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F117" s="17"/>
       <c r="G117" s="17"/>
@@ -4817,24 +5035,24 @@
       <c r="K117" s="17"/>
       <c r="L117" s="17"/>
       <c r="M117" s="17"/>
-      <c r="N117" s="22" t="s">
+      <c r="N117" s="18" t="s">
         <v>43</v>
       </c>
       <c r="O117" s="17"/>
       <c r="P117" s="17"/>
     </row>
-    <row r="118" spans="1:16" ht="17.25" customHeight="1">
+    <row r="118" spans="1:16" ht="16.5" customHeight="1">
       <c r="A118" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>ACTRIS_ctrl_lists:NOAA-2004</v>
+        <f t="shared" si="1"/>
+        <v>ACTRIS_ctrl_lists:NDACC</v>
       </c>
       <c r="B118" s="16" t="s">
-        <v>219</v>
+        <v>127</v>
       </c>
       <c r="C118" s="17"/>
       <c r="D118" s="16"/>
       <c r="E118" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F118" s="17"/>
       <c r="G118" s="17"/>
@@ -4844,24 +5062,28 @@
       <c r="K118" s="17"/>
       <c r="L118" s="17"/>
       <c r="M118" s="17"/>
-      <c r="N118" s="22" t="s">
+      <c r="N118" s="18" t="s">
         <v>43</v>
       </c>
       <c r="O118" s="17"/>
       <c r="P118" s="17"/>
     </row>
-    <row r="119" spans="1:16" ht="17.25" customHeight="1">
+    <row r="119" spans="1:16" ht="16.5" customHeight="1">
       <c r="A119" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>ACTRIS_ctrl_lists:NOAA-Jul10-p</v>
+        <f t="shared" si="1"/>
+        <v>ACTRIS_ctrl_lists:NILU</v>
       </c>
       <c r="B119" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="C119" s="17"/>
-      <c r="D119" s="16"/>
+        <v>128</v>
+      </c>
+      <c r="C119" s="17" t="s">
+        <v>418</v>
+      </c>
+      <c r="D119" s="16" t="s">
+        <v>419</v>
+      </c>
       <c r="E119" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F119" s="17"/>
       <c r="G119" s="17"/>
@@ -4871,24 +5093,26 @@
       <c r="K119" s="17"/>
       <c r="L119" s="17"/>
       <c r="M119" s="17"/>
-      <c r="N119" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="O119" s="17"/>
+      <c r="N119" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="O119" s="17" t="s">
+        <v>405</v>
+      </c>
       <c r="P119" s="17"/>
     </row>
-    <row r="120" spans="1:16" ht="17.25" customHeight="1">
+    <row r="120" spans="1:16" ht="16.5" customHeight="1">
       <c r="A120" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>ACTRIS_ctrl_lists:NOAA04</v>
+        <f t="shared" ref="A120" si="4">IF(ISBLANK($B120),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B120," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
+        <v>ACTRIS_ctrl_lists:noframework</v>
       </c>
       <c r="B120" s="16" t="s">
-        <v>223</v>
+        <v>387</v>
       </c>
       <c r="C120" s="17"/>
       <c r="D120" s="16"/>
       <c r="E120" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F120" s="17"/>
       <c r="G120" s="17"/>
@@ -4898,24 +5122,26 @@
       <c r="K120" s="17"/>
       <c r="L120" s="17"/>
       <c r="M120" s="17"/>
-      <c r="N120" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="O120" s="17"/>
+      <c r="N120" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="O120" s="17" t="s">
+        <v>405</v>
+      </c>
       <c r="P120" s="17"/>
     </row>
     <row r="121" spans="1:16" ht="17.25" customHeight="1">
       <c r="A121" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>ACTRIS_ctrl_lists:NPL</v>
+        <f t="shared" ref="A121:A213" si="5">IF(ISBLANK($B121),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B121," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
+        <v>ACTRIS_ctrl_lists:NOAA-ESRL</v>
       </c>
       <c r="B121" s="16" t="s">
-        <v>205</v>
+        <v>129</v>
       </c>
       <c r="C121" s="17"/>
       <c r="D121" s="16"/>
       <c r="E121" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F121" s="17"/>
       <c r="G121" s="17"/>
@@ -4925,24 +5151,26 @@
       <c r="K121" s="17"/>
       <c r="L121" s="17"/>
       <c r="M121" s="17"/>
-      <c r="N121" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="O121" s="17"/>
+      <c r="N121" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="O121" s="17" t="s">
+        <v>43</v>
+      </c>
       <c r="P121" s="17"/>
     </row>
     <row r="122" spans="1:16" ht="17.25" customHeight="1">
       <c r="A122" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>ACTRIS_ctrl_lists:NPLplusGPT</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:NOAA-GGGRN</v>
       </c>
       <c r="B122" s="16" t="s">
-        <v>225</v>
+        <v>393</v>
       </c>
       <c r="C122" s="17"/>
       <c r="D122" s="16"/>
       <c r="E122" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F122" s="17"/>
       <c r="G122" s="17"/>
@@ -4952,7 +5180,7 @@
       <c r="K122" s="17"/>
       <c r="L122" s="17"/>
       <c r="M122" s="17"/>
-      <c r="N122" s="22" t="s">
+      <c r="N122" s="18" t="s">
         <v>43</v>
       </c>
       <c r="O122" s="17"/>
@@ -4960,16 +5188,16 @@
     </row>
     <row r="123" spans="1:16" ht="17.25" customHeight="1">
       <c r="A123" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>ACTRIS_ctrl_lists:SIO1998</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:OECD</v>
       </c>
       <c r="B123" s="16" t="s">
-        <v>229</v>
+        <v>394</v>
       </c>
       <c r="C123" s="17"/>
       <c r="D123" s="16"/>
       <c r="E123" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F123" s="17"/>
       <c r="G123" s="17"/>
@@ -4979,7 +5207,7 @@
       <c r="K123" s="17"/>
       <c r="L123" s="17"/>
       <c r="M123" s="17"/>
-      <c r="N123" s="22" t="s">
+      <c r="N123" s="18" t="s">
         <v>43</v>
       </c>
       <c r="O123" s="17"/>
@@ -4987,16 +5215,20 @@
     </row>
     <row r="124" spans="1:16" ht="17.25" customHeight="1">
       <c r="A124" s="14" t="str">
-        <f t="shared" ref="A124:A129" si="7">IF(ISBLANK($B124),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B124," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
-        <v>ACTRIS_ctrl_lists:SIO2005</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:PARIS</v>
       </c>
       <c r="B124" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="C124" s="17"/>
-      <c r="D124" s="16"/>
+        <v>395</v>
+      </c>
+      <c r="C124" s="17" t="s">
+        <v>423</v>
+      </c>
+      <c r="D124" s="16" t="s">
+        <v>424</v>
+      </c>
       <c r="E124" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F124" s="17"/>
       <c r="G124" s="17"/>
@@ -5006,7 +5238,7 @@
       <c r="K124" s="17"/>
       <c r="L124" s="17"/>
       <c r="M124" s="17"/>
-      <c r="N124" s="22" t="s">
+      <c r="N124" s="18" t="s">
         <v>43</v>
       </c>
       <c r="O124" s="17"/>
@@ -5014,16 +5246,20 @@
     </row>
     <row r="125" spans="1:16" ht="17.25" customHeight="1">
       <c r="A125" s="14" t="str">
-        <f t="shared" si="7"/>
-        <v>ACTRIS_ctrl_lists:SIO2007</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:PollenScience</v>
       </c>
       <c r="B125" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="C125" s="17"/>
-      <c r="D125" s="16"/>
+        <v>396</v>
+      </c>
+      <c r="C125" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="D125" s="16" t="s">
+        <v>426</v>
+      </c>
       <c r="E125" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F125" s="17"/>
       <c r="G125" s="17"/>
@@ -5033,7 +5269,7 @@
       <c r="K125" s="17"/>
       <c r="L125" s="17"/>
       <c r="M125" s="17"/>
-      <c r="N125" s="22" t="s">
+      <c r="N125" s="18" t="s">
         <v>43</v>
       </c>
       <c r="O125" s="17"/>
@@ -5041,16 +5277,20 @@
     </row>
     <row r="126" spans="1:16" ht="17.25" customHeight="1">
       <c r="A126" s="14" t="str">
-        <f t="shared" si="7"/>
-        <v>ACTRIS_ctrl_lists:SIO2012</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:ReGAME</v>
       </c>
       <c r="B126" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="C126" s="17"/>
-      <c r="D126" s="16"/>
+        <v>397</v>
+      </c>
+      <c r="C126" s="17" t="s">
+        <v>434</v>
+      </c>
+      <c r="D126" s="16" t="s">
+        <v>435</v>
+      </c>
       <c r="E126" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F126" s="17"/>
       <c r="G126" s="17"/>
@@ -5060,7 +5300,7 @@
       <c r="K126" s="17"/>
       <c r="L126" s="17"/>
       <c r="M126" s="17"/>
-      <c r="N126" s="22" t="s">
+      <c r="N126" s="18" t="s">
         <v>43</v>
       </c>
       <c r="O126" s="17"/>
@@ -5068,16 +5308,16 @@
     </row>
     <row r="127" spans="1:16" ht="17.25" customHeight="1">
       <c r="A127" s="14" t="str">
-        <f t="shared" si="7"/>
-        <v>ACTRIS_ctrl_lists:SIO2014</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:RI-URBANS</v>
       </c>
       <c r="B127" s="16" t="s">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c r="C127" s="17"/>
       <c r="D127" s="16"/>
       <c r="E127" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F127" s="17"/>
       <c r="G127" s="17"/>
@@ -5087,7 +5327,7 @@
       <c r="K127" s="17"/>
       <c r="L127" s="17"/>
       <c r="M127" s="17"/>
-      <c r="N127" s="22" t="s">
+      <c r="N127" s="18" t="s">
         <v>43</v>
       </c>
       <c r="O127" s="17"/>
@@ -5095,16 +5335,16 @@
     </row>
     <row r="128" spans="1:16" ht="17.25" customHeight="1">
       <c r="A128" s="14" t="str">
-        <f t="shared" si="7"/>
-        <v>ACTRIS_ctrl_lists:SIO-p</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:ROSHYDROMET</v>
       </c>
       <c r="B128" s="16" t="s">
-        <v>211</v>
+        <v>398</v>
       </c>
       <c r="C128" s="17"/>
       <c r="D128" s="16"/>
       <c r="E128" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F128" s="17"/>
       <c r="G128" s="17"/>
@@ -5114,7 +5354,7 @@
       <c r="K128" s="17"/>
       <c r="L128" s="17"/>
       <c r="M128" s="17"/>
-      <c r="N128" s="22" t="s">
+      <c r="N128" s="18" t="s">
         <v>43</v>
       </c>
       <c r="O128" s="17"/>
@@ -5122,16 +5362,16 @@
     </row>
     <row r="129" spans="1:16" ht="17.25" customHeight="1">
       <c r="A129" s="14" t="str">
-        <f t="shared" si="7"/>
-        <v>ACTRIS_ctrl_lists:UB-98</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:SOGE</v>
       </c>
       <c r="B129" s="16" t="s">
-        <v>228</v>
+        <v>399</v>
       </c>
       <c r="C129" s="17"/>
       <c r="D129" s="16"/>
       <c r="E129" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F129" s="17"/>
       <c r="G129" s="17"/>
@@ -5141,7 +5381,7 @@
       <c r="K129" s="17"/>
       <c r="L129" s="17"/>
       <c r="M129" s="17"/>
-      <c r="N129" s="22" t="s">
+      <c r="N129" s="18" t="s">
         <v>43</v>
       </c>
       <c r="O129" s="17"/>
@@ -5149,16 +5389,20 @@
     </row>
     <row r="130" spans="1:16" ht="17.25" customHeight="1">
       <c r="A130" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>ACTRIS_ctrl_lists:UB-p</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:SYLVA</v>
       </c>
       <c r="B130" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="C130" s="17"/>
-      <c r="D130" s="16"/>
+        <v>400</v>
+      </c>
+      <c r="C130" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="D130" s="16" t="s">
+        <v>429</v>
+      </c>
       <c r="E130" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F130" s="17"/>
       <c r="G130" s="17"/>
@@ -5168,7 +5412,7 @@
       <c r="K130" s="17"/>
       <c r="L130" s="17"/>
       <c r="M130" s="17"/>
-      <c r="N130" s="22" t="s">
+      <c r="N130" s="18" t="s">
         <v>43</v>
       </c>
       <c r="O130" s="17"/>
@@ -5176,16 +5420,16 @@
     </row>
     <row r="131" spans="1:16" ht="17.25" customHeight="1">
       <c r="A131" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>ACTRIS_ctrl_lists:WMOCH4X2004</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:UKDECC</v>
       </c>
       <c r="B131" s="16" t="s">
-        <v>224</v>
+        <v>401</v>
       </c>
       <c r="C131" s="17"/>
       <c r="D131" s="16"/>
       <c r="E131" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F131" s="17"/>
       <c r="G131" s="17"/>
@@ -5195,7 +5439,7 @@
       <c r="K131" s="17"/>
       <c r="L131" s="17"/>
       <c r="M131" s="17"/>
-      <c r="N131" s="22" t="s">
+      <c r="N131" s="18" t="s">
         <v>43</v>
       </c>
       <c r="O131" s="17"/>
@@ -5203,16 +5447,18 @@
     </row>
     <row r="132" spans="1:16" ht="17.25" customHeight="1">
       <c r="A132" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>ACTRIS_ctrl_lists:WMOCOX2004</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:WeBaSOOP</v>
       </c>
       <c r="B132" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="C132" s="17"/>
+        <v>402</v>
+      </c>
+      <c r="C132" s="17" t="s">
+        <v>436</v>
+      </c>
       <c r="D132" s="16"/>
       <c r="E132" s="16" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="F132" s="17"/>
       <c r="G132" s="17"/>
@@ -5222,7 +5468,7 @@
       <c r="K132" s="17"/>
       <c r="L132" s="17"/>
       <c r="M132" s="17"/>
-      <c r="N132" s="22" t="s">
+      <c r="N132" s="18" t="s">
         <v>43</v>
       </c>
       <c r="O132" s="17"/>
@@ -5230,17 +5476,13 @@
     </row>
     <row r="133" spans="1:16" ht="17.25" customHeight="1">
       <c r="A133" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>ACTRIS_ctrl_lists:WMOCOX2014</v>
-      </c>
-      <c r="B133" s="16" t="s">
-        <v>215</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B133" s="16"/>
       <c r="C133" s="17"/>
       <c r="D133" s="16"/>
-      <c r="E133" s="16" t="s">
-        <v>231</v>
-      </c>
+      <c r="E133" s="16"/>
       <c r="F133" s="17"/>
       <c r="G133" s="17"/>
       <c r="H133" s="17"/>
@@ -5249,25 +5491,16 @@
       <c r="K133" s="17"/>
       <c r="L133" s="17"/>
       <c r="M133" s="17"/>
-      <c r="N133" s="22" t="s">
-        <v>43</v>
-      </c>
+      <c r="N133" s="22"/>
       <c r="O133" s="17"/>
       <c r="P133" s="17"/>
     </row>
     <row r="134" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A134" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>ACTRIS_ctrl_lists:WMOCOX2014A</v>
-      </c>
-      <c r="B134" s="16" t="s">
-        <v>216</v>
-      </c>
+      <c r="A134" s="14"/>
+      <c r="B134" s="16"/>
       <c r="C134" s="17"/>
       <c r="D134" s="16"/>
-      <c r="E134" s="16" t="s">
-        <v>231</v>
-      </c>
+      <c r="E134" s="16"/>
       <c r="F134" s="17"/>
       <c r="G134" s="17"/>
       <c r="H134" s="17"/>
@@ -5276,79 +5509,72 @@
       <c r="K134" s="17"/>
       <c r="L134" s="17"/>
       <c r="M134" s="17"/>
-      <c r="N134" s="22" t="s">
-        <v>43</v>
-      </c>
+      <c r="N134" s="22"/>
       <c r="O134" s="17"/>
       <c r="P134" s="17"/>
     </row>
-    <row r="135" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A135" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>ACTRIS_ctrl_lists:WMOCO2X2007</v>
-      </c>
-      <c r="B135" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="C135" s="17"/>
-      <c r="D135" s="16"/>
-      <c r="E135" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="F135" s="17"/>
-      <c r="G135" s="17"/>
-      <c r="H135" s="17"/>
-      <c r="I135" s="17"/>
-      <c r="J135" s="17"/>
-      <c r="K135" s="17"/>
-      <c r="L135" s="17"/>
-      <c r="M135" s="17"/>
-      <c r="N135" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="O135" s="17"/>
-      <c r="P135" s="17"/>
+    <row r="135" spans="1:16" ht="15" customHeight="1">
+      <c r="A135" s="11" t="str">
+        <f t="shared" ref="A135:A136" si="6">IF(ISBLANK($B135),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B135," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
+        <v>ACTRIS_ctrl_lists:Glossary</v>
+      </c>
+      <c r="B135" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C135" s="12"/>
+      <c r="D135" s="12"/>
+      <c r="E135" s="12"/>
+      <c r="F135" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="G135" s="12"/>
+      <c r="H135" s="12"/>
+      <c r="I135" s="12"/>
+      <c r="J135" s="12"/>
+      <c r="K135" s="12"/>
+      <c r="L135" s="12"/>
+      <c r="M135" s="12"/>
+      <c r="N135" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="O135" s="12"/>
+      <c r="P135" s="12"/>
     </row>
     <row r="136" spans="1:16" ht="17.25" customHeight="1">
       <c r="A136" s="14" t="str">
         <f t="shared" si="6"/>
-        <v>ACTRIS_ctrl_lists:WMOCO2X2019</v>
+        <v>ACTRIS_ctrl_lists:ACTRISdata</v>
       </c>
       <c r="B136" s="16" t="s">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="C136" s="17"/>
-      <c r="D136" s="16"/>
+      <c r="D136" s="16" t="s">
+        <v>151</v>
+      </c>
       <c r="E136" s="16" t="s">
-        <v>231</v>
+        <v>147</v>
       </c>
       <c r="F136" s="17"/>
       <c r="G136" s="17"/>
-      <c r="H136" s="17"/>
+      <c r="H136" s="17" t="s">
+        <v>150</v>
+      </c>
       <c r="I136" s="17"/>
       <c r="J136" s="17"/>
       <c r="K136" s="17"/>
       <c r="L136" s="17"/>
       <c r="M136" s="17"/>
-      <c r="N136" s="22" t="s">
-        <v>43</v>
-      </c>
+      <c r="N136" s="22"/>
       <c r="O136" s="17"/>
       <c r="P136" s="17"/>
     </row>
     <row r="137" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A137" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>ACTRIS_ctrl_lists:WMON2OX2006A</v>
-      </c>
-      <c r="B137" s="16" t="s">
-        <v>221</v>
-      </c>
+      <c r="A137" s="14"/>
+      <c r="B137" s="16"/>
       <c r="C137" s="17"/>
       <c r="D137" s="16"/>
-      <c r="E137" s="16" t="s">
-        <v>231</v>
-      </c>
+      <c r="E137" s="16"/>
       <c r="F137" s="17"/>
       <c r="G137" s="17"/>
       <c r="H137" s="17"/>
@@ -5357,126 +5583,132 @@
       <c r="K137" s="17"/>
       <c r="L137" s="17"/>
       <c r="M137" s="17"/>
-      <c r="N137" s="22" t="s">
-        <v>43</v>
-      </c>
+      <c r="N137" s="22"/>
       <c r="O137" s="17"/>
       <c r="P137" s="17"/>
     </row>
-    <row r="138" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A138" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="B138" s="16"/>
-      <c r="C138" s="17"/>
-      <c r="D138" s="16"/>
-      <c r="E138" s="16"/>
-      <c r="F138" s="17"/>
-      <c r="G138" s="17"/>
-      <c r="H138" s="17"/>
-      <c r="I138" s="17"/>
-      <c r="J138" s="17"/>
-      <c r="K138" s="17"/>
-      <c r="L138" s="17"/>
-      <c r="M138" s="17"/>
-      <c r="N138" s="22"/>
-      <c r="O138" s="17"/>
-      <c r="P138" s="17"/>
-    </row>
-    <row r="139" spans="1:16" ht="15" customHeight="1">
-      <c r="A139" s="11" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:usemetadata</v>
-      </c>
-      <c r="B139" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="C139" s="12"/>
-      <c r="D139" s="12" t="s">
-        <v>176</v>
-      </c>
-      <c r="E139" s="12"/>
-      <c r="F139" s="12"/>
-      <c r="G139" s="12"/>
-      <c r="H139" s="12"/>
-      <c r="I139" s="12"/>
-      <c r="J139" s="12"/>
-      <c r="K139" s="12"/>
-      <c r="L139" s="12"/>
-      <c r="M139" s="12"/>
-      <c r="N139" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="O139" s="12"/>
-      <c r="P139" s="12"/>
-    </row>
-    <row r="140" spans="1:16" ht="15" customHeight="1">
-      <c r="A140" s="23" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:simulationchambercontrolledlists</v>
-      </c>
-      <c r="B140" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="C140" s="24"/>
-      <c r="D140" s="24"/>
-      <c r="E140" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="F140" s="24"/>
-      <c r="G140" s="24"/>
-      <c r="H140" s="24"/>
-      <c r="I140" s="24"/>
-      <c r="J140" s="24"/>
-      <c r="K140" s="24"/>
-      <c r="L140" s="24"/>
-      <c r="M140" s="24"/>
-      <c r="N140" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="O140" s="24"/>
-      <c r="P140" s="24"/>
-    </row>
-    <row r="141" spans="1:16" ht="15" customHeight="1">
-      <c r="A141" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:simulationchamberlightsources</v>
-      </c>
-      <c r="B141" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="C141" s="27"/>
-      <c r="D141" s="27"/>
-      <c r="E141" s="27" t="s">
-        <v>183</v>
-      </c>
-      <c r="F141" s="27"/>
-      <c r="G141" s="27"/>
-      <c r="H141" s="27"/>
-      <c r="I141" s="27"/>
-      <c r="J141" s="27"/>
-      <c r="K141" s="27"/>
-      <c r="L141" s="27"/>
-      <c r="M141" s="27"/>
-      <c r="N141" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="O141" s="27"/>
-      <c r="P141" s="27"/>
+    <row r="138" spans="1:16" ht="15" customHeight="1">
+      <c r="A138" s="11" t="str">
+        <f t="shared" ref="A138:A164" si="7">IF(ISBLANK($B138),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B138," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
+        <v>ACTRIS_ctrl_lists:calibrationscale</v>
+      </c>
+      <c r="B138" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C138" s="12"/>
+      <c r="D138" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="E138" s="12"/>
+      <c r="F138" s="12"/>
+      <c r="G138" s="12"/>
+      <c r="H138" s="12"/>
+      <c r="I138" s="12"/>
+      <c r="J138" s="12"/>
+      <c r="K138" s="12"/>
+      <c r="L138" s="12"/>
+      <c r="M138" s="12"/>
+      <c r="N138" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="O138" s="12"/>
+      <c r="P138" s="12"/>
+    </row>
+    <row r="139" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A139" s="14" t="str">
+        <f t="shared" si="7"/>
+        <v>ACTRIS_ctrl_lists:Apel-Riemer</v>
+      </c>
+      <c r="B139" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="C139" s="17"/>
+      <c r="D139" s="16"/>
+      <c r="E139" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="F139" s="17"/>
+      <c r="G139" s="17"/>
+      <c r="H139" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="I139" s="17"/>
+      <c r="J139" s="17"/>
+      <c r="K139" s="17"/>
+      <c r="L139" s="17"/>
+      <c r="M139" s="17"/>
+      <c r="N139" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="O139" s="17"/>
+      <c r="P139" s="17"/>
+    </row>
+    <row r="140" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A140" s="14" t="str">
+        <f t="shared" si="7"/>
+        <v>ACTRIS_ctrl_lists:Empa-2015-p</v>
+      </c>
+      <c r="B140" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="C140" s="17"/>
+      <c r="D140" s="16"/>
+      <c r="E140" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="F140" s="17"/>
+      <c r="G140" s="17"/>
+      <c r="H140" s="17"/>
+      <c r="I140" s="17"/>
+      <c r="J140" s="17"/>
+      <c r="K140" s="17"/>
+      <c r="L140" s="17"/>
+      <c r="M140" s="17"/>
+      <c r="N140" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="O140" s="17"/>
+      <c r="P140" s="17"/>
+    </row>
+    <row r="141" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A141" s="14" t="str">
+        <f t="shared" si="7"/>
+        <v>ACTRIS_ctrl_lists:MPI-2009</v>
+      </c>
+      <c r="B141" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="C141" s="17"/>
+      <c r="D141" s="16"/>
+      <c r="E141" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="F141" s="17"/>
+      <c r="G141" s="17"/>
+      <c r="H141" s="17"/>
+      <c r="I141" s="17"/>
+      <c r="J141" s="17"/>
+      <c r="K141" s="17"/>
+      <c r="L141" s="17"/>
+      <c r="M141" s="17"/>
+      <c r="N141" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="O141" s="17"/>
+      <c r="P141" s="17"/>
     </row>
     <row r="142" spans="1:16" ht="17.25" customHeight="1">
       <c r="A142" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:darkchamber</v>
+        <f t="shared" si="7"/>
+        <v>ACTRIS_ctrl_lists:NOAA-2003</v>
       </c>
       <c r="B142" s="16" t="s">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="C142" s="17"/>
       <c r="D142" s="16"/>
-      <c r="E142" s="17" t="s">
-        <v>184</v>
+      <c r="E142" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="F142" s="17"/>
       <c r="G142" s="17"/>
@@ -5489,21 +5721,21 @@
       <c r="N142" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="O142" s="22"/>
+      <c r="O142" s="17"/>
       <c r="P142" s="17"/>
     </row>
     <row r="143" spans="1:16" ht="17.25" customHeight="1">
       <c r="A143" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:fluorescentlamps</v>
+        <f t="shared" si="7"/>
+        <v>ACTRIS_ctrl_lists:NOAA-2003B</v>
       </c>
       <c r="B143" s="16" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="C143" s="17"/>
       <c r="D143" s="16"/>
-      <c r="E143" s="17" t="s">
-        <v>184</v>
+      <c r="E143" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="F143" s="17"/>
       <c r="G143" s="17"/>
@@ -5516,21 +5748,21 @@
       <c r="N143" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="O143" s="22"/>
+      <c r="O143" s="17"/>
       <c r="P143" s="17"/>
     </row>
     <row r="144" spans="1:16" ht="17.25" customHeight="1">
       <c r="A144" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:naturalsunlight</v>
+        <f t="shared" si="7"/>
+        <v>ACTRIS_ctrl_lists:NOAA-2004</v>
       </c>
       <c r="B144" s="16" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="C144" s="17"/>
       <c r="D144" s="16"/>
-      <c r="E144" s="17" t="s">
-        <v>184</v>
+      <c r="E144" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="F144" s="17"/>
       <c r="G144" s="17"/>
@@ -5543,21 +5775,21 @@
       <c r="N144" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="O144" s="22"/>
+      <c r="O144" s="17"/>
       <c r="P144" s="17"/>
     </row>
     <row r="145" spans="1:16" ht="17.25" customHeight="1">
       <c r="A145" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:otherartificiallightsource</v>
+        <f t="shared" si="7"/>
+        <v>ACTRIS_ctrl_lists:NOAA-Jul10-p</v>
       </c>
       <c r="B145" s="16" t="s">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="C145" s="17"/>
       <c r="D145" s="16"/>
-      <c r="E145" s="17" t="s">
-        <v>184</v>
+      <c r="E145" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="F145" s="17"/>
       <c r="G145" s="17"/>
@@ -5570,21 +5802,21 @@
       <c r="N145" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="O145" s="22"/>
+      <c r="O145" s="17"/>
       <c r="P145" s="17"/>
     </row>
     <row r="146" spans="1:16" ht="17.25" customHeight="1">
       <c r="A146" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:xenonarclamps</v>
+        <f t="shared" si="7"/>
+        <v>ACTRIS_ctrl_lists:NOAA04</v>
       </c>
       <c r="B146" s="16" t="s">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="C146" s="17"/>
       <c r="D146" s="16"/>
-      <c r="E146" s="17" t="s">
-        <v>184</v>
+      <c r="E146" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="F146" s="17"/>
       <c r="G146" s="17"/>
@@ -5597,18 +5829,22 @@
       <c r="N146" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="O146" s="22"/>
+      <c r="O146" s="17"/>
       <c r="P146" s="17"/>
     </row>
     <row r="147" spans="1:16" ht="17.25" customHeight="1">
       <c r="A147" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="B147" s="16"/>
+        <f t="shared" si="7"/>
+        <v>ACTRIS_ctrl_lists:NPL</v>
+      </c>
+      <c r="B147" s="16" t="s">
+        <v>205</v>
+      </c>
       <c r="C147" s="17"/>
       <c r="D147" s="16"/>
-      <c r="E147" s="17"/>
+      <c r="E147" s="16" t="s">
+        <v>231</v>
+      </c>
       <c r="F147" s="17"/>
       <c r="G147" s="17"/>
       <c r="H147" s="17"/>
@@ -5617,49 +5853,51 @@
       <c r="K147" s="17"/>
       <c r="L147" s="17"/>
       <c r="M147" s="17"/>
-      <c r="N147" s="22"/>
-      <c r="O147" s="22"/>
+      <c r="N147" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="O147" s="17"/>
       <c r="P147" s="17"/>
     </row>
-    <row r="148" spans="1:16" ht="15" customHeight="1">
-      <c r="A148" s="26" t="str">
-        <f t="shared" ref="A148" si="8">IF(ISBLANK($B148),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
-        <v>ACTRIS_ctrl_lists:simulationchamberwalltypes</v>
-      </c>
-      <c r="B148" s="27" t="s">
-        <v>185</v>
-      </c>
-      <c r="C148" s="27"/>
-      <c r="D148" s="27"/>
-      <c r="E148" s="27" t="s">
-        <v>183</v>
-      </c>
-      <c r="F148" s="27"/>
-      <c r="G148" s="27"/>
-      <c r="H148" s="27"/>
-      <c r="I148" s="27"/>
-      <c r="J148" s="27"/>
-      <c r="K148" s="27"/>
-      <c r="L148" s="27"/>
-      <c r="M148" s="27"/>
-      <c r="N148" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="O148" s="27"/>
-      <c r="P148" s="27"/>
+    <row r="148" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A148" s="14" t="str">
+        <f t="shared" si="7"/>
+        <v>ACTRIS_ctrl_lists:NPLplusGPT</v>
+      </c>
+      <c r="B148" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="C148" s="17"/>
+      <c r="D148" s="16"/>
+      <c r="E148" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="F148" s="17"/>
+      <c r="G148" s="17"/>
+      <c r="H148" s="17"/>
+      <c r="I148" s="17"/>
+      <c r="J148" s="17"/>
+      <c r="K148" s="17"/>
+      <c r="L148" s="17"/>
+      <c r="M148" s="17"/>
+      <c r="N148" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="O148" s="17"/>
+      <c r="P148" s="17"/>
     </row>
     <row r="149" spans="1:16" ht="17.25" customHeight="1">
       <c r="A149" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:aluminium</v>
+        <f t="shared" si="7"/>
+        <v>ACTRIS_ctrl_lists:SIO1998</v>
       </c>
       <c r="B149" s="16" t="s">
-        <v>190</v>
+        <v>229</v>
       </c>
       <c r="C149" s="17"/>
       <c r="D149" s="16"/>
-      <c r="E149" s="17" t="s">
-        <v>192</v>
+      <c r="E149" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="F149" s="17"/>
       <c r="G149" s="17"/>
@@ -5672,23 +5910,21 @@
       <c r="N149" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="O149" s="22"/>
+      <c r="O149" s="17"/>
       <c r="P149" s="17"/>
     </row>
     <row r="150" spans="1:16" ht="17.25" customHeight="1">
       <c r="A150" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:fluorinatedethylenepropylenefilm</v>
+        <f t="shared" ref="A150:A155" si="8">IF(ISBLANK($B150),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
+        <v>ACTRIS_ctrl_lists:SIO2005</v>
       </c>
       <c r="B150" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="C150" s="16" t="s">
-        <v>186</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="C150" s="17"/>
       <c r="D150" s="16"/>
-      <c r="E150" s="17" t="s">
-        <v>192</v>
+      <c r="E150" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="F150" s="17"/>
       <c r="G150" s="17"/>
@@ -5701,21 +5937,21 @@
       <c r="N150" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="O150" s="22"/>
+      <c r="O150" s="17"/>
       <c r="P150" s="17"/>
     </row>
     <row r="151" spans="1:16" ht="17.25" customHeight="1">
       <c r="A151" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:Pyrex</v>
+        <f t="shared" si="8"/>
+        <v>ACTRIS_ctrl_lists:SIO2007</v>
       </c>
       <c r="B151" s="16" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="C151" s="17"/>
       <c r="D151" s="16"/>
-      <c r="E151" s="17" t="s">
-        <v>192</v>
+      <c r="E151" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="F151" s="17"/>
       <c r="G151" s="17"/>
@@ -5728,21 +5964,21 @@
       <c r="N151" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="O151" s="22"/>
+      <c r="O151" s="17"/>
       <c r="P151" s="17"/>
     </row>
     <row r="152" spans="1:16" ht="17.25" customHeight="1">
       <c r="A152" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:quartz</v>
+        <f t="shared" si="8"/>
+        <v>ACTRIS_ctrl_lists:SIO2012</v>
       </c>
       <c r="B152" s="16" t="s">
-        <v>188</v>
+        <v>226</v>
       </c>
       <c r="C152" s="17"/>
       <c r="D152" s="16"/>
-      <c r="E152" s="17" t="s">
-        <v>192</v>
+      <c r="E152" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="F152" s="17"/>
       <c r="G152" s="17"/>
@@ -5755,21 +5991,21 @@
       <c r="N152" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="O152" s="22"/>
+      <c r="O152" s="17"/>
       <c r="P152" s="17"/>
     </row>
     <row r="153" spans="1:16" ht="17.25" customHeight="1">
       <c r="A153" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:stainlesssteel</v>
+        <f t="shared" si="8"/>
+        <v>ACTRIS_ctrl_lists:SIO2014</v>
       </c>
       <c r="B153" s="16" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="C153" s="17"/>
       <c r="D153" s="16"/>
-      <c r="E153" s="17" t="s">
-        <v>192</v>
+      <c r="E153" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="F153" s="17"/>
       <c r="G153" s="17"/>
@@ -5782,18 +6018,22 @@
       <c r="N153" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="O153" s="22"/>
+      <c r="O153" s="17"/>
       <c r="P153" s="17"/>
     </row>
     <row r="154" spans="1:16" ht="17.25" customHeight="1">
       <c r="A154" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="B154" s="16"/>
+        <f t="shared" si="8"/>
+        <v>ACTRIS_ctrl_lists:SIO-p</v>
+      </c>
+      <c r="B154" s="16" t="s">
+        <v>211</v>
+      </c>
       <c r="C154" s="17"/>
       <c r="D154" s="16"/>
-      <c r="E154" s="17"/>
+      <c r="E154" s="16" t="s">
+        <v>231</v>
+      </c>
       <c r="F154" s="17"/>
       <c r="G154" s="17"/>
       <c r="H154" s="17"/>
@@ -5802,19 +6042,25 @@
       <c r="K154" s="17"/>
       <c r="L154" s="17"/>
       <c r="M154" s="17"/>
-      <c r="N154" s="22"/>
-      <c r="O154" s="22"/>
+      <c r="N154" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="O154" s="17"/>
       <c r="P154" s="17"/>
     </row>
     <row r="155" spans="1:16" ht="17.25" customHeight="1">
       <c r="A155" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="B155" s="16"/>
+        <f t="shared" si="8"/>
+        <v>ACTRIS_ctrl_lists:UB-98</v>
+      </c>
+      <c r="B155" s="16" t="s">
+        <v>228</v>
+      </c>
       <c r="C155" s="17"/>
       <c r="D155" s="16"/>
-      <c r="E155" s="17"/>
+      <c r="E155" s="16" t="s">
+        <v>231</v>
+      </c>
       <c r="F155" s="17"/>
       <c r="G155" s="17"/>
       <c r="H155" s="17"/>
@@ -5823,82 +6069,82 @@
       <c r="K155" s="17"/>
       <c r="L155" s="17"/>
       <c r="M155" s="17"/>
-      <c r="N155" s="22"/>
-      <c r="O155" s="22"/>
+      <c r="N155" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="O155" s="17"/>
       <c r="P155" s="17"/>
     </row>
-    <row r="156" spans="1:16" ht="15" customHeight="1">
-      <c r="A156" s="23" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:aerosolinsitucontrolledlists</v>
-      </c>
-      <c r="B156" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="C156" s="24"/>
-      <c r="D156" s="24"/>
-      <c r="E156" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="F156" s="24"/>
-      <c r="G156" s="24"/>
-      <c r="H156" s="24"/>
-      <c r="I156" s="24"/>
-      <c r="J156" s="24"/>
-      <c r="K156" s="24"/>
-      <c r="L156" s="24"/>
-      <c r="M156" s="24"/>
-      <c r="N156" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="O156" s="24"/>
-      <c r="P156" s="24"/>
-    </row>
-    <row r="157" spans="1:16" ht="15" customHeight="1">
-      <c r="A157" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:filtertype</v>
-      </c>
-      <c r="B157" s="27" t="s">
-        <v>193</v>
-      </c>
-      <c r="C157" s="27"/>
-      <c r="D157" s="27"/>
-      <c r="E157" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="F157" s="27"/>
-      <c r="G157" s="27"/>
-      <c r="H157" s="27"/>
-      <c r="I157" s="27"/>
-      <c r="J157" s="27"/>
-      <c r="K157" s="27"/>
-      <c r="L157" s="27"/>
-      <c r="M157" s="27"/>
-      <c r="N157" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="O157" s="27"/>
-      <c r="P157" s="27"/>
+    <row r="156" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A156" s="14" t="str">
+        <f t="shared" si="7"/>
+        <v>ACTRIS_ctrl_lists:UB-p</v>
+      </c>
+      <c r="B156" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="C156" s="17"/>
+      <c r="D156" s="16"/>
+      <c r="E156" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="F156" s="17"/>
+      <c r="G156" s="17"/>
+      <c r="H156" s="17"/>
+      <c r="I156" s="17"/>
+      <c r="J156" s="17"/>
+      <c r="K156" s="17"/>
+      <c r="L156" s="17"/>
+      <c r="M156" s="17"/>
+      <c r="N156" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="O156" s="17"/>
+      <c r="P156" s="17"/>
+    </row>
+    <row r="157" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A157" s="14" t="str">
+        <f t="shared" si="7"/>
+        <v>ACTRIS_ctrl_lists:WMOCH4X2004</v>
+      </c>
+      <c r="B157" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="C157" s="17"/>
+      <c r="D157" s="16"/>
+      <c r="E157" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="F157" s="17"/>
+      <c r="G157" s="17"/>
+      <c r="H157" s="17"/>
+      <c r="I157" s="17"/>
+      <c r="J157" s="17"/>
+      <c r="K157" s="17"/>
+      <c r="L157" s="17"/>
+      <c r="M157" s="17"/>
+      <c r="N157" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="O157" s="17"/>
+      <c r="P157" s="17"/>
     </row>
     <row r="158" spans="1:16" ht="17.25" customHeight="1">
       <c r="A158" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:MageeAE33-FT</v>
+        <f t="shared" si="7"/>
+        <v>ACTRIS_ctrl_lists:WMOCOX2004</v>
       </c>
       <c r="B158" s="16" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C158" s="17"/>
       <c r="D158" s="16"/>
-      <c r="E158" s="17" t="s">
-        <v>195</v>
+      <c r="E158" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="F158" s="17"/>
       <c r="G158" s="17"/>
-      <c r="H158" s="17" t="s">
-        <v>312</v>
-      </c>
+      <c r="H158" s="17"/>
       <c r="I158" s="17"/>
       <c r="J158" s="17"/>
       <c r="K158" s="17"/>
@@ -5907,27 +6153,25 @@
       <c r="N158" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="O158" s="22"/>
+      <c r="O158" s="17"/>
       <c r="P158" s="17"/>
     </row>
     <row r="159" spans="1:16" ht="17.25" customHeight="1">
       <c r="A159" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:Magee8050</v>
+        <f t="shared" si="7"/>
+        <v>ACTRIS_ctrl_lists:WMOCOX2014</v>
       </c>
       <c r="B159" s="16" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="C159" s="17"/>
       <c r="D159" s="16"/>
-      <c r="E159" s="17" t="s">
-        <v>195</v>
+      <c r="E159" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="F159" s="17"/>
       <c r="G159" s="17"/>
-      <c r="H159" s="17" t="s">
-        <v>312</v>
-      </c>
+      <c r="H159" s="17"/>
       <c r="I159" s="17"/>
       <c r="J159" s="17"/>
       <c r="K159" s="17"/>
@@ -5936,27 +6180,25 @@
       <c r="N159" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="O159" s="22"/>
+      <c r="O159" s="17"/>
       <c r="P159" s="17"/>
     </row>
     <row r="160" spans="1:16" ht="17.25" customHeight="1">
       <c r="A160" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:Magee8060</v>
+        <f t="shared" si="7"/>
+        <v>ACTRIS_ctrl_lists:WMOCOX2014A</v>
       </c>
       <c r="B160" s="16" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="C160" s="17"/>
       <c r="D160" s="16"/>
-      <c r="E160" s="17" t="s">
-        <v>195</v>
+      <c r="E160" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="F160" s="17"/>
       <c r="G160" s="17"/>
-      <c r="H160" s="17" t="s">
-        <v>312</v>
-      </c>
+      <c r="H160" s="17"/>
       <c r="I160" s="17"/>
       <c r="J160" s="17"/>
       <c r="K160" s="17"/>
@@ -5965,15 +6207,22 @@
       <c r="N160" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="O160" s="22"/>
+      <c r="O160" s="17"/>
       <c r="P160" s="17"/>
     </row>
     <row r="161" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A161" s="14"/>
-      <c r="B161" s="16"/>
+      <c r="A161" s="14" t="str">
+        <f t="shared" si="7"/>
+        <v>ACTRIS_ctrl_lists:WMOCO2X2007</v>
+      </c>
+      <c r="B161" s="16" t="s">
+        <v>217</v>
+      </c>
       <c r="C161" s="17"/>
       <c r="D161" s="16"/>
-      <c r="E161" s="17"/>
+      <c r="E161" s="16" t="s">
+        <v>231</v>
+      </c>
       <c r="F161" s="17"/>
       <c r="G161" s="17"/>
       <c r="H161" s="17"/>
@@ -5982,59 +6231,55 @@
       <c r="K161" s="17"/>
       <c r="L161" s="17"/>
       <c r="M161" s="17"/>
-      <c r="N161" s="22"/>
-      <c r="O161" s="22"/>
+      <c r="N161" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="O161" s="17"/>
       <c r="P161" s="17"/>
     </row>
-    <row r="162" spans="1:16" ht="15" customHeight="1">
-      <c r="A162" s="26" t="str">
-        <f t="shared" ref="A162" si="9">IF(ISBLANK($B162),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B162," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
-        <v>ACTRIS_ctrl_lists:instrumentstatuscheck</v>
-      </c>
-      <c r="B162" s="27" t="s">
-        <v>233</v>
-      </c>
-      <c r="C162" s="27"/>
-      <c r="D162" s="27"/>
-      <c r="E162" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="F162" s="27" t="s">
-        <v>234</v>
-      </c>
-      <c r="G162" s="27"/>
-      <c r="H162" s="27"/>
-      <c r="I162" s="27"/>
-      <c r="J162" s="27"/>
-      <c r="K162" s="27"/>
-      <c r="L162" s="27"/>
-      <c r="M162" s="27"/>
-      <c r="N162" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="O162" s="27"/>
-      <c r="P162" s="27"/>
+    <row r="162" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A162" s="14" t="str">
+        <f t="shared" si="7"/>
+        <v>ACTRIS_ctrl_lists:WMOCO2X2019</v>
+      </c>
+      <c r="B162" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="C162" s="17"/>
+      <c r="D162" s="16"/>
+      <c r="E162" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="F162" s="17"/>
+      <c r="G162" s="17"/>
+      <c r="H162" s="17"/>
+      <c r="I162" s="17"/>
+      <c r="J162" s="17"/>
+      <c r="K162" s="17"/>
+      <c r="L162" s="17"/>
+      <c r="M162" s="17"/>
+      <c r="N162" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="O162" s="17"/>
+      <c r="P162" s="17"/>
     </row>
     <row r="163" spans="1:16" ht="17.25" customHeight="1">
       <c r="A163" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:checkdiagnosticvalues</v>
+        <f t="shared" si="7"/>
+        <v>ACTRIS_ctrl_lists:WMON2OX2006A</v>
       </c>
       <c r="B163" s="16" t="s">
-        <v>279</v>
+        <v>221</v>
       </c>
       <c r="C163" s="17"/>
-      <c r="D163" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="E163" s="17" t="s">
-        <v>251</v>
+      <c r="D163" s="16"/>
+      <c r="E163" s="16" t="s">
+        <v>231</v>
       </c>
       <c r="F163" s="17"/>
       <c r="G163" s="17"/>
-      <c r="H163" s="17" t="s">
-        <v>311</v>
-      </c>
+      <c r="H163" s="17"/>
       <c r="I163" s="17"/>
       <c r="J163" s="17"/>
       <c r="K163" s="17"/>
@@ -6043,151 +6288,127 @@
       <c r="N163" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="O163" s="22"/>
+      <c r="O163" s="17"/>
       <c r="P163" s="17"/>
     </row>
     <row r="164" spans="1:16" ht="17.25" customHeight="1">
       <c r="A164" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:checkcleanlinessofoptics</v>
-      </c>
-      <c r="B164" s="16" t="s">
-        <v>235</v>
-      </c>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="B164" s="16"/>
       <c r="C164" s="17"/>
-      <c r="D164" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="E164" s="17" t="s">
-        <v>251</v>
-      </c>
+      <c r="D164" s="16"/>
+      <c r="E164" s="16"/>
       <c r="F164" s="17"/>
       <c r="G164" s="17"/>
-      <c r="H164" s="17" t="s">
-        <v>311</v>
-      </c>
+      <c r="H164" s="17"/>
       <c r="I164" s="17"/>
       <c r="J164" s="17"/>
       <c r="K164" s="17"/>
       <c r="L164" s="17"/>
       <c r="M164" s="17"/>
-      <c r="N164" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="O164" s="22"/>
+      <c r="N164" s="22"/>
+      <c r="O164" s="17"/>
       <c r="P164" s="17"/>
     </row>
-    <row r="165" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A165" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:boundarycheck</v>
-      </c>
-      <c r="B165" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="C165" s="17"/>
-      <c r="D165" s="16"/>
-      <c r="E165" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="F165" s="17"/>
-      <c r="G165" s="17"/>
-      <c r="H165" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="I165" s="17"/>
-      <c r="J165" s="17"/>
-      <c r="K165" s="17"/>
-      <c r="L165" s="17"/>
-      <c r="M165" s="17"/>
-      <c r="N165" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="O165" s="22"/>
-      <c r="P165" s="17"/>
-    </row>
-    <row r="166" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A166" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:checksampleflow</v>
-      </c>
-      <c r="B166" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="C166" s="17"/>
-      <c r="D166" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="E166" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="F166" s="17"/>
-      <c r="G166" s="17"/>
-      <c r="H166" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="I166" s="17"/>
-      <c r="J166" s="17"/>
-      <c r="K166" s="17"/>
-      <c r="L166" s="17"/>
-      <c r="M166" s="17"/>
-      <c r="N166" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="O166" s="22"/>
-      <c r="P166" s="17"/>
-    </row>
-    <row r="167" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A167" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:checksheathairflow</v>
-      </c>
-      <c r="B167" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="C167" s="17"/>
-      <c r="D167" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="E167" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="F167" s="17"/>
-      <c r="G167" s="17"/>
-      <c r="H167" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="I167" s="17"/>
-      <c r="J167" s="17"/>
-      <c r="K167" s="17"/>
-      <c r="L167" s="17"/>
-      <c r="M167" s="17"/>
-      <c r="N167" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="O167" s="22"/>
-      <c r="P167" s="17"/>
+    <row r="165" spans="1:16" ht="15" customHeight="1">
+      <c r="A165" s="11" t="str">
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:usemetadata</v>
+      </c>
+      <c r="B165" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="C165" s="12"/>
+      <c r="D165" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="E165" s="12"/>
+      <c r="F165" s="12"/>
+      <c r="G165" s="12"/>
+      <c r="H165" s="12"/>
+      <c r="I165" s="12"/>
+      <c r="J165" s="12"/>
+      <c r="K165" s="12"/>
+      <c r="L165" s="12"/>
+      <c r="M165" s="12"/>
+      <c r="N165" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="O165" s="12"/>
+      <c r="P165" s="12"/>
+    </row>
+    <row r="166" spans="1:16" ht="15" customHeight="1">
+      <c r="A166" s="23" t="str">
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:simulationchambercontrolledlists</v>
+      </c>
+      <c r="B166" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="C166" s="24"/>
+      <c r="D166" s="24"/>
+      <c r="E166" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="F166" s="24"/>
+      <c r="G166" s="24"/>
+      <c r="H166" s="24"/>
+      <c r="I166" s="24"/>
+      <c r="J166" s="24"/>
+      <c r="K166" s="24"/>
+      <c r="L166" s="24"/>
+      <c r="M166" s="24"/>
+      <c r="N166" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="O166" s="24"/>
+      <c r="P166" s="24"/>
+    </row>
+    <row r="167" spans="1:16" ht="15" customHeight="1">
+      <c r="A167" s="26" t="str">
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:simulationchamberlightsources</v>
+      </c>
+      <c r="B167" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="C167" s="27"/>
+      <c r="D167" s="27"/>
+      <c r="E167" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="F167" s="27"/>
+      <c r="G167" s="27"/>
+      <c r="H167" s="27"/>
+      <c r="I167" s="27"/>
+      <c r="J167" s="27"/>
+      <c r="K167" s="27"/>
+      <c r="L167" s="27"/>
+      <c r="M167" s="27"/>
+      <c r="N167" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="O167" s="27"/>
+      <c r="P167" s="27"/>
     </row>
     <row r="168" spans="1:16" ht="17.25" customHeight="1">
       <c r="A168" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:checkdataacquisition</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:darkchamber</v>
       </c>
       <c r="B168" s="16" t="s">
-        <v>239</v>
+        <v>178</v>
       </c>
       <c r="C168" s="17"/>
-      <c r="D168" s="16" t="s">
-        <v>247</v>
-      </c>
+      <c r="D168" s="16"/>
       <c r="E168" s="17" t="s">
-        <v>251</v>
+        <v>184</v>
       </c>
       <c r="F168" s="17"/>
       <c r="G168" s="17"/>
-      <c r="H168" s="17" t="s">
-        <v>311</v>
-      </c>
+      <c r="H168" s="17"/>
       <c r="I168" s="17"/>
       <c r="J168" s="17"/>
       <c r="K168" s="17"/>
@@ -6201,24 +6422,20 @@
     </row>
     <row r="169" spans="1:16" ht="17.25" customHeight="1">
       <c r="A169" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:checkoperatingfluids</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:fluorescentlamps</v>
       </c>
       <c r="B169" s="16" t="s">
-        <v>240</v>
+        <v>179</v>
       </c>
       <c r="C169" s="17"/>
-      <c r="D169" s="16" t="s">
-        <v>248</v>
-      </c>
+      <c r="D169" s="16"/>
       <c r="E169" s="17" t="s">
-        <v>251</v>
+        <v>184</v>
       </c>
       <c r="F169" s="17"/>
       <c r="G169" s="17"/>
-      <c r="H169" s="17" t="s">
-        <v>311</v>
-      </c>
+      <c r="H169" s="17"/>
       <c r="I169" s="17"/>
       <c r="J169" s="17"/>
       <c r="K169" s="17"/>
@@ -6232,24 +6449,20 @@
     </row>
     <row r="170" spans="1:16" ht="17.25" customHeight="1">
       <c r="A170" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:checkfiltertapelength</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:naturalsunlight</v>
       </c>
       <c r="B170" s="16" t="s">
-        <v>241</v>
+        <v>180</v>
       </c>
       <c r="C170" s="17"/>
-      <c r="D170" s="16" t="s">
-        <v>249</v>
-      </c>
+      <c r="D170" s="16"/>
       <c r="E170" s="17" t="s">
-        <v>251</v>
+        <v>184</v>
       </c>
       <c r="F170" s="17"/>
       <c r="G170" s="17"/>
-      <c r="H170" s="17" t="s">
-        <v>311</v>
-      </c>
+      <c r="H170" s="17"/>
       <c r="I170" s="17"/>
       <c r="J170" s="17"/>
       <c r="K170" s="17"/>
@@ -6263,24 +6476,20 @@
     </row>
     <row r="171" spans="1:16" ht="17.25" customHeight="1">
       <c r="A171" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:checktransmittancedecrease</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:otherartificiallightsource</v>
       </c>
       <c r="B171" s="16" t="s">
-        <v>242</v>
+        <v>181</v>
       </c>
       <c r="C171" s="17"/>
-      <c r="D171" s="16" t="s">
-        <v>250</v>
-      </c>
+      <c r="D171" s="16"/>
       <c r="E171" s="17" t="s">
-        <v>251</v>
+        <v>184</v>
       </c>
       <c r="F171" s="17"/>
       <c r="G171" s="17"/>
-      <c r="H171" s="17" t="s">
-        <v>311</v>
-      </c>
+      <c r="H171" s="17"/>
       <c r="I171" s="17"/>
       <c r="J171" s="17"/>
       <c r="K171" s="17"/>
@@ -6294,13 +6503,17 @@
     </row>
     <row r="172" spans="1:16" ht="17.25" customHeight="1">
       <c r="A172" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="B172" s="16"/>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:xenonarclamps</v>
+      </c>
+      <c r="B172" s="16" t="s">
+        <v>182</v>
+      </c>
       <c r="C172" s="17"/>
       <c r="D172" s="16"/>
-      <c r="E172" s="17"/>
+      <c r="E172" s="17" t="s">
+        <v>184</v>
+      </c>
       <c r="F172" s="17"/>
       <c r="G172" s="17"/>
       <c r="H172" s="17"/>
@@ -6309,90 +6522,76 @@
       <c r="K172" s="17"/>
       <c r="L172" s="17"/>
       <c r="M172" s="17"/>
-      <c r="N172" s="22"/>
+      <c r="N172" s="22" t="s">
+        <v>43</v>
+      </c>
       <c r="O172" s="22"/>
       <c r="P172" s="17"/>
     </row>
-    <row r="173" spans="1:16" ht="15" customHeight="1">
-      <c r="A173" s="26" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:instrumentperformancecheck</v>
-      </c>
-      <c r="B173" s="27" t="s">
-        <v>252</v>
-      </c>
-      <c r="C173" s="27"/>
-      <c r="D173" s="27"/>
-      <c r="E173" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="F173" s="27" t="s">
-        <v>270</v>
-      </c>
-      <c r="G173" s="27"/>
-      <c r="H173" s="27"/>
-      <c r="I173" s="27"/>
-      <c r="J173" s="27"/>
-      <c r="K173" s="27"/>
-      <c r="L173" s="27"/>
-      <c r="M173" s="27"/>
-      <c r="N173" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="O173" s="27"/>
-      <c r="P173" s="27"/>
-    </row>
-    <row r="174" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A174" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:checkofdetectionefficiency</v>
-      </c>
-      <c r="B174" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="C174" s="17"/>
-      <c r="D174" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="E174" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="F174" s="17"/>
-      <c r="G174" s="17"/>
-      <c r="H174" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="I174" s="17"/>
-      <c r="J174" s="17"/>
-      <c r="K174" s="17"/>
-      <c r="L174" s="17"/>
-      <c r="M174" s="17"/>
-      <c r="N174" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="O174" s="22"/>
-      <c r="P174" s="17"/>
+    <row r="173" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A173" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B173" s="16"/>
+      <c r="C173" s="17"/>
+      <c r="D173" s="16"/>
+      <c r="E173" s="17"/>
+      <c r="F173" s="17"/>
+      <c r="G173" s="17"/>
+      <c r="H173" s="17"/>
+      <c r="I173" s="17"/>
+      <c r="J173" s="17"/>
+      <c r="K173" s="17"/>
+      <c r="L173" s="17"/>
+      <c r="M173" s="17"/>
+      <c r="N173" s="22"/>
+      <c r="O173" s="22"/>
+      <c r="P173" s="17"/>
+    </row>
+    <row r="174" spans="1:16" ht="15" customHeight="1">
+      <c r="A174" s="26" t="str">
+        <f t="shared" ref="A174" si="9">IF(ISBLANK($B174),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B174," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
+        <v>ACTRIS_ctrl_lists:simulationchamberwalltypes</v>
+      </c>
+      <c r="B174" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="C174" s="27"/>
+      <c r="D174" s="27"/>
+      <c r="E174" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="F174" s="27"/>
+      <c r="G174" s="27"/>
+      <c r="H174" s="27"/>
+      <c r="I174" s="27"/>
+      <c r="J174" s="27"/>
+      <c r="K174" s="27"/>
+      <c r="L174" s="27"/>
+      <c r="M174" s="27"/>
+      <c r="N174" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="O174" s="27"/>
+      <c r="P174" s="27"/>
     </row>
     <row r="175" spans="1:16" ht="17.25" customHeight="1">
       <c r="A175" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:checkofsizingaccuracy</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:aluminium</v>
       </c>
       <c r="B175" s="16" t="s">
-        <v>254</v>
+        <v>190</v>
       </c>
       <c r="C175" s="17"/>
-      <c r="D175" s="16" t="s">
-        <v>262</v>
-      </c>
+      <c r="D175" s="16"/>
       <c r="E175" s="17" t="s">
-        <v>269</v>
+        <v>192</v>
       </c>
       <c r="F175" s="17"/>
       <c r="G175" s="17"/>
-      <c r="H175" s="17" t="s">
-        <v>311</v>
-      </c>
+      <c r="H175" s="17"/>
       <c r="I175" s="17"/>
       <c r="J175" s="17"/>
       <c r="K175" s="17"/>
@@ -6406,24 +6605,22 @@
     </row>
     <row r="176" spans="1:16" ht="17.25" customHeight="1">
       <c r="A176" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:checkofbaseline-zerocheck</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:fluorinatedethylenepropylenefilm</v>
       </c>
       <c r="B176" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="C176" s="17"/>
-      <c r="D176" s="16" t="s">
-        <v>263</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="C176" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="D176" s="16"/>
       <c r="E176" s="17" t="s">
-        <v>269</v>
+        <v>192</v>
       </c>
       <c r="F176" s="17"/>
       <c r="G176" s="17"/>
-      <c r="H176" s="17" t="s">
-        <v>311</v>
-      </c>
+      <c r="H176" s="17"/>
       <c r="I176" s="17"/>
       <c r="J176" s="17"/>
       <c r="K176" s="17"/>
@@ -6437,24 +6634,20 @@
     </row>
     <row r="177" spans="1:16" ht="17.25" customHeight="1">
       <c r="A177" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:checkofnoise</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:Pyrex</v>
       </c>
       <c r="B177" s="16" t="s">
-        <v>256</v>
+        <v>187</v>
       </c>
       <c r="C177" s="17"/>
-      <c r="D177" s="16" t="s">
-        <v>264</v>
-      </c>
+      <c r="D177" s="16"/>
       <c r="E177" s="17" t="s">
-        <v>269</v>
+        <v>192</v>
       </c>
       <c r="F177" s="17"/>
       <c r="G177" s="17"/>
-      <c r="H177" s="17" t="s">
-        <v>311</v>
-      </c>
+      <c r="H177" s="17"/>
       <c r="I177" s="17"/>
       <c r="J177" s="17"/>
       <c r="K177" s="17"/>
@@ -6468,24 +6661,20 @@
     </row>
     <row r="178" spans="1:16" ht="17.25" customHeight="1">
       <c r="A178" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:checkofoffset</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:quartz</v>
       </c>
       <c r="B178" s="16" t="s">
-        <v>257</v>
+        <v>188</v>
       </c>
       <c r="C178" s="17"/>
-      <c r="D178" s="16" t="s">
-        <v>265</v>
-      </c>
+      <c r="D178" s="16"/>
       <c r="E178" s="17" t="s">
-        <v>269</v>
+        <v>192</v>
       </c>
       <c r="F178" s="17"/>
       <c r="G178" s="17"/>
-      <c r="H178" s="17" t="s">
-        <v>311</v>
-      </c>
+      <c r="H178" s="17"/>
       <c r="I178" s="17"/>
       <c r="J178" s="17"/>
       <c r="K178" s="17"/>
@@ -6499,24 +6688,20 @@
     </row>
     <row r="179" spans="1:16" ht="17.25" customHeight="1">
       <c r="A179" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:checkoffilterspot</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:stainlesssteel</v>
       </c>
       <c r="B179" s="16" t="s">
-        <v>258</v>
+        <v>189</v>
       </c>
       <c r="C179" s="17"/>
-      <c r="D179" s="16" t="s">
-        <v>266</v>
-      </c>
+      <c r="D179" s="16"/>
       <c r="E179" s="17" t="s">
-        <v>269</v>
+        <v>192</v>
       </c>
       <c r="F179" s="17"/>
       <c r="G179" s="17"/>
-      <c r="H179" s="17" t="s">
-        <v>311</v>
-      </c>
+      <c r="H179" s="17"/>
       <c r="I179" s="17"/>
       <c r="J179" s="17"/>
       <c r="K179" s="17"/>
@@ -6530,103 +6715,87 @@
     </row>
     <row r="180" spans="1:16" ht="17.25" customHeight="1">
       <c r="A180" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:checkofhighvoltage</v>
-      </c>
-      <c r="B180" s="16" t="s">
-        <v>259</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B180" s="16"/>
       <c r="C180" s="17"/>
-      <c r="D180" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="E180" s="17" t="s">
-        <v>269</v>
-      </c>
+      <c r="D180" s="16"/>
+      <c r="E180" s="17"/>
       <c r="F180" s="17"/>
       <c r="G180" s="17"/>
-      <c r="H180" s="17" t="s">
-        <v>311</v>
-      </c>
+      <c r="H180" s="17"/>
       <c r="I180" s="17"/>
       <c r="J180" s="17"/>
       <c r="K180" s="17"/>
       <c r="L180" s="17"/>
       <c r="M180" s="17"/>
-      <c r="N180" s="22" t="s">
-        <v>43</v>
-      </c>
+      <c r="N180" s="22"/>
       <c r="O180" s="22"/>
       <c r="P180" s="17"/>
     </row>
     <row r="181" spans="1:16" ht="17.25" customHeight="1">
       <c r="A181" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:highspancheckorspangascheck</v>
-      </c>
-      <c r="B181" s="16" t="s">
-        <v>260</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B181" s="16"/>
       <c r="C181" s="17"/>
-      <c r="D181" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="E181" s="17" t="s">
-        <v>269</v>
-      </c>
+      <c r="D181" s="16"/>
+      <c r="E181" s="17"/>
       <c r="F181" s="17"/>
       <c r="G181" s="17"/>
-      <c r="H181" s="17" t="s">
-        <v>311</v>
-      </c>
+      <c r="H181" s="17"/>
       <c r="I181" s="17"/>
       <c r="J181" s="17"/>
       <c r="K181" s="17"/>
       <c r="L181" s="17"/>
       <c r="M181" s="17"/>
-      <c r="N181" s="22" t="s">
-        <v>43</v>
-      </c>
+      <c r="N181" s="22"/>
       <c r="O181" s="22"/>
       <c r="P181" s="17"/>
     </row>
-    <row r="182" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A182" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="B182" s="16"/>
-      <c r="C182" s="17"/>
-      <c r="D182" s="16"/>
-      <c r="E182" s="17"/>
-      <c r="F182" s="17"/>
-      <c r="G182" s="17"/>
-      <c r="H182" s="17"/>
-      <c r="I182" s="17"/>
-      <c r="J182" s="17"/>
-      <c r="K182" s="17"/>
-      <c r="L182" s="17"/>
-      <c r="M182" s="17"/>
-      <c r="N182" s="22"/>
-      <c r="O182" s="22"/>
-      <c r="P182" s="17"/>
+    <row r="182" spans="1:16" ht="15" customHeight="1">
+      <c r="A182" s="23" t="str">
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:aerosolinsitucontrolledlists</v>
+      </c>
+      <c r="B182" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="C182" s="24"/>
+      <c r="D182" s="24"/>
+      <c r="E182" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="F182" s="24"/>
+      <c r="G182" s="24"/>
+      <c r="H182" s="24"/>
+      <c r="I182" s="24"/>
+      <c r="J182" s="24"/>
+      <c r="K182" s="24"/>
+      <c r="L182" s="24"/>
+      <c r="M182" s="24"/>
+      <c r="N182" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="O182" s="24"/>
+      <c r="P182" s="24"/>
     </row>
     <row r="183" spans="1:16" ht="15" customHeight="1">
       <c r="A183" s="26" t="str">
-        <f t="shared" ref="A183" si="10">IF(ISBLANK($B183),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B183," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
-        <v>ACTRIS_ctrl_lists:instrumentcalibration</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:filtertype</v>
       </c>
       <c r="B183" s="27" t="s">
-        <v>271</v>
+        <v>193</v>
       </c>
       <c r="C183" s="27"/>
       <c r="D183" s="27"/>
       <c r="E183" s="27" t="s">
         <v>196</v>
       </c>
-      <c r="F183" s="27" t="s">
-        <v>272</v>
-      </c>
+      <c r="F183" s="27"/>
       <c r="G183" s="27"/>
       <c r="H183" s="27"/>
       <c r="I183" s="27"/>
@@ -6642,23 +6811,21 @@
     </row>
     <row r="184" spans="1:16" ht="17.25" customHeight="1">
       <c r="A184" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:highvoltagecalibration</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:MageeAE33-FT</v>
       </c>
       <c r="B184" s="16" t="s">
-        <v>273</v>
+        <v>194</v>
       </c>
       <c r="C184" s="17"/>
-      <c r="D184" s="16" t="s">
-        <v>278</v>
-      </c>
+      <c r="D184" s="16"/>
       <c r="E184" s="17" t="s">
-        <v>277</v>
+        <v>195</v>
       </c>
       <c r="F184" s="17"/>
       <c r="G184" s="17"/>
       <c r="H184" s="17" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I184" s="17"/>
       <c r="J184" s="17"/>
@@ -6673,21 +6840,21 @@
     </row>
     <row r="185" spans="1:16" ht="17.25" customHeight="1">
       <c r="A185" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:highspancalibration</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:Magee8050</v>
       </c>
       <c r="B185" s="16" t="s">
-        <v>274</v>
+        <v>202</v>
       </c>
       <c r="C185" s="17"/>
       <c r="D185" s="16"/>
       <c r="E185" s="17" t="s">
-        <v>277</v>
+        <v>195</v>
       </c>
       <c r="F185" s="17"/>
       <c r="G185" s="17"/>
       <c r="H185" s="17" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I185" s="17"/>
       <c r="J185" s="17"/>
@@ -6702,23 +6869,21 @@
     </row>
     <row r="186" spans="1:16" ht="17.25" customHeight="1">
       <c r="A186" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v>ACTRIS_ctrl_lists:flowcalibration</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:Magee8060</v>
       </c>
       <c r="B186" s="16" t="s">
-        <v>275</v>
+        <v>203</v>
       </c>
       <c r="C186" s="17"/>
-      <c r="D186" s="16" t="s">
-        <v>276</v>
-      </c>
+      <c r="D186" s="16"/>
       <c r="E186" s="17" t="s">
-        <v>277</v>
+        <v>195</v>
       </c>
       <c r="F186" s="17"/>
       <c r="G186" s="17"/>
       <c r="H186" s="17" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I186" s="17"/>
       <c r="J186" s="17"/>
@@ -6732,10 +6897,7 @@
       <c r="P186" s="17"/>
     </row>
     <row r="187" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A187" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="A187" s="14"/>
       <c r="B187" s="16"/>
       <c r="C187" s="17"/>
       <c r="D187" s="16"/>
@@ -6753,160 +6915,198 @@
       <c r="P187" s="17"/>
     </row>
     <row r="188" spans="1:16" ht="15" customHeight="1">
-      <c r="A188" s="23" t="str">
-        <f t="shared" ref="A188:A189" si="11">IF(ISBLANK($B188),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
-        <v>ACTRIS_ctrl_lists:cloudinsitucontrolledlists</v>
-      </c>
-      <c r="B188" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="C188" s="24"/>
-      <c r="D188" s="24"/>
-      <c r="E188" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="F188" s="24"/>
-      <c r="G188" s="24"/>
-      <c r="H188" s="24"/>
-      <c r="I188" s="24"/>
-      <c r="J188" s="24"/>
-      <c r="K188" s="24"/>
-      <c r="L188" s="24"/>
-      <c r="M188" s="24"/>
-      <c r="N188" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="O188" s="24"/>
-      <c r="P188" s="24"/>
-    </row>
-    <row r="189" spans="1:16" ht="15" customHeight="1">
-      <c r="A189" s="26" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="B189" s="27"/>
-      <c r="C189" s="27"/>
-      <c r="D189" s="27"/>
-      <c r="E189" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="F189" s="27"/>
-      <c r="G189" s="27"/>
-      <c r="H189" s="27"/>
-      <c r="I189" s="27"/>
-      <c r="J189" s="27"/>
-      <c r="K189" s="27"/>
-      <c r="L189" s="27"/>
-      <c r="M189" s="27"/>
-      <c r="N189" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="O189" s="27"/>
-      <c r="P189" s="27"/>
+      <c r="A188" s="26" t="str">
+        <f t="shared" ref="A188" si="10">IF(ISBLANK($B188),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B188," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
+        <v>ACTRIS_ctrl_lists:instrumentstatuscheck</v>
+      </c>
+      <c r="B188" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="C188" s="27"/>
+      <c r="D188" s="27"/>
+      <c r="E188" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="F188" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="G188" s="27"/>
+      <c r="H188" s="27"/>
+      <c r="I188" s="27"/>
+      <c r="J188" s="27"/>
+      <c r="K188" s="27"/>
+      <c r="L188" s="27"/>
+      <c r="M188" s="27"/>
+      <c r="N188" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="O188" s="27"/>
+      <c r="P188" s="27"/>
+    </row>
+    <row r="189" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A189" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:checkdiagnosticvalues</v>
+      </c>
+      <c r="B189" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="C189" s="17"/>
+      <c r="D189" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="E189" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="F189" s="17"/>
+      <c r="G189" s="17"/>
+      <c r="H189" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="I189" s="17"/>
+      <c r="J189" s="17"/>
+      <c r="K189" s="17"/>
+      <c r="L189" s="17"/>
+      <c r="M189" s="17"/>
+      <c r="N189" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="O189" s="22"/>
+      <c r="P189" s="17"/>
     </row>
     <row r="190" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A190" s="14"/>
-      <c r="B190" s="16"/>
+      <c r="A190" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:checkcleanlinessofoptics</v>
+      </c>
+      <c r="B190" s="16" t="s">
+        <v>235</v>
+      </c>
       <c r="C190" s="17"/>
-      <c r="D190" s="16"/>
-      <c r="E190" s="17"/>
+      <c r="D190" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="E190" s="17" t="s">
+        <v>251</v>
+      </c>
       <c r="F190" s="17"/>
       <c r="G190" s="17"/>
-      <c r="H190" s="17"/>
+      <c r="H190" s="17" t="s">
+        <v>311</v>
+      </c>
       <c r="I190" s="17"/>
       <c r="J190" s="17"/>
       <c r="K190" s="17"/>
       <c r="L190" s="17"/>
       <c r="M190" s="17"/>
-      <c r="N190" s="22"/>
+      <c r="N190" s="22" t="s">
+        <v>43</v>
+      </c>
       <c r="O190" s="22"/>
       <c r="P190" s="17"/>
     </row>
     <row r="191" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A191" s="14"/>
-      <c r="B191" s="16"/>
+      <c r="A191" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:boundarycheck</v>
+      </c>
+      <c r="B191" s="16" t="s">
+        <v>236</v>
+      </c>
       <c r="C191" s="17"/>
       <c r="D191" s="16"/>
-      <c r="E191" s="17"/>
+      <c r="E191" s="17" t="s">
+        <v>251</v>
+      </c>
       <c r="F191" s="17"/>
       <c r="G191" s="17"/>
-      <c r="H191" s="17"/>
+      <c r="H191" s="17" t="s">
+        <v>311</v>
+      </c>
       <c r="I191" s="17"/>
       <c r="J191" s="17"/>
       <c r="K191" s="17"/>
       <c r="L191" s="17"/>
       <c r="M191" s="17"/>
-      <c r="N191" s="22"/>
+      <c r="N191" s="22" t="s">
+        <v>43</v>
+      </c>
       <c r="O191" s="22"/>
       <c r="P191" s="17"/>
     </row>
-    <row r="192" spans="1:16" ht="15" customHeight="1">
-      <c r="A192" s="23" t="str">
-        <f t="shared" ref="A192:A204" si="12">IF(ISBLANK($B192),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B192," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
-        <v>ACTRIS_ctrl_lists:reactivetracegasinsitucontrolledlists</v>
-      </c>
-      <c r="B192" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="C192" s="24"/>
-      <c r="D192" s="24"/>
-      <c r="E192" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="F192" s="24"/>
-      <c r="G192" s="24"/>
-      <c r="H192" s="24"/>
-      <c r="I192" s="24"/>
-      <c r="J192" s="24"/>
-      <c r="K192" s="24"/>
-      <c r="L192" s="24"/>
-      <c r="M192" s="24"/>
-      <c r="N192" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="O192" s="24"/>
-      <c r="P192" s="24"/>
-    </row>
-    <row r="193" spans="1:16" ht="15" customHeight="1">
-      <c r="A193" s="26" t="str">
-        <f t="shared" si="12"/>
-        <v>ACTRIS_ctrl_lists:instrumentstatuscheck</v>
-      </c>
-      <c r="B193" s="27" t="s">
-        <v>233</v>
-      </c>
-      <c r="C193" s="27"/>
-      <c r="D193" s="27"/>
-      <c r="E193" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="F193" s="27" t="s">
-        <v>234</v>
-      </c>
-      <c r="G193" s="27"/>
-      <c r="H193" s="27"/>
-      <c r="I193" s="27"/>
-      <c r="J193" s="27"/>
-      <c r="K193" s="27"/>
-      <c r="L193" s="27"/>
-      <c r="M193" s="27"/>
-      <c r="N193" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="O193" s="27"/>
-      <c r="P193" s="27"/>
+    <row r="192" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A192" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:checksampleflow</v>
+      </c>
+      <c r="B192" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="C192" s="17"/>
+      <c r="D192" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="E192" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="F192" s="17"/>
+      <c r="G192" s="17"/>
+      <c r="H192" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="I192" s="17"/>
+      <c r="J192" s="17"/>
+      <c r="K192" s="17"/>
+      <c r="L192" s="17"/>
+      <c r="M192" s="17"/>
+      <c r="N192" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="O192" s="22"/>
+      <c r="P192" s="17"/>
+    </row>
+    <row r="193" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A193" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:checksheathairflow</v>
+      </c>
+      <c r="B193" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="C193" s="17"/>
+      <c r="D193" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="E193" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="F193" s="17"/>
+      <c r="G193" s="17"/>
+      <c r="H193" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="I193" s="17"/>
+      <c r="J193" s="17"/>
+      <c r="K193" s="17"/>
+      <c r="L193" s="17"/>
+      <c r="M193" s="17"/>
+      <c r="N193" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="O193" s="22"/>
+      <c r="P193" s="17"/>
     </row>
     <row r="194" spans="1:16" ht="17.25" customHeight="1">
       <c r="A194" s="14" t="str">
-        <f t="shared" si="12"/>
-        <v>ACTRIS_ctrl_lists:voltagesettingcheck</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:checkdataacquisition</v>
       </c>
       <c r="B194" s="16" t="s">
-        <v>315</v>
+        <v>239</v>
       </c>
       <c r="C194" s="17"/>
       <c r="D194" s="16" t="s">
-        <v>319</v>
+        <v>247</v>
       </c>
       <c r="E194" s="17" t="s">
         <v>251</v>
@@ -6914,30 +7114,30 @@
       <c r="F194" s="17"/>
       <c r="G194" s="17"/>
       <c r="H194" s="17" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I194" s="17"/>
       <c r="J194" s="17"/>
       <c r="K194" s="17"/>
       <c r="L194" s="17"/>
       <c r="M194" s="17"/>
-      <c r="N194" s="32" t="s">
-        <v>323</v>
+      <c r="N194" s="22" t="s">
+        <v>43</v>
       </c>
       <c r="O194" s="22"/>
       <c r="P194" s="17"/>
     </row>
     <row r="195" spans="1:16" ht="17.25" customHeight="1">
       <c r="A195" s="14" t="str">
-        <f t="shared" si="12"/>
-        <v>ACTRIS_ctrl_lists:flowsettingcheck</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:checkoperatingfluids</v>
       </c>
       <c r="B195" s="16" t="s">
-        <v>316</v>
+        <v>240</v>
       </c>
       <c r="C195" s="17"/>
       <c r="D195" s="16" t="s">
-        <v>320</v>
+        <v>248</v>
       </c>
       <c r="E195" s="17" t="s">
         <v>251</v>
@@ -6945,30 +7145,30 @@
       <c r="F195" s="17"/>
       <c r="G195" s="17"/>
       <c r="H195" s="17" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I195" s="17"/>
       <c r="J195" s="17"/>
       <c r="K195" s="17"/>
       <c r="L195" s="17"/>
       <c r="M195" s="17"/>
-      <c r="N195" s="32" t="s">
-        <v>324</v>
+      <c r="N195" s="22" t="s">
+        <v>43</v>
       </c>
       <c r="O195" s="22"/>
       <c r="P195" s="17"/>
     </row>
     <row r="196" spans="1:16" ht="17.25" customHeight="1">
       <c r="A196" s="14" t="str">
-        <f t="shared" si="12"/>
-        <v>ACTRIS_ctrl_lists:pressuresettingcheck</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:checkfiltertapelength</v>
       </c>
       <c r="B196" s="16" t="s">
-        <v>317</v>
+        <v>241</v>
       </c>
       <c r="C196" s="17"/>
       <c r="D196" s="16" t="s">
-        <v>321</v>
+        <v>249</v>
       </c>
       <c r="E196" s="17" t="s">
         <v>251</v>
@@ -6976,30 +7176,30 @@
       <c r="F196" s="17"/>
       <c r="G196" s="17"/>
       <c r="H196" s="17" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I196" s="17"/>
       <c r="J196" s="17"/>
       <c r="K196" s="17"/>
       <c r="L196" s="17"/>
       <c r="M196" s="17"/>
-      <c r="N196" s="32" t="s">
-        <v>325</v>
+      <c r="N196" s="22" t="s">
+        <v>43</v>
       </c>
       <c r="O196" s="22"/>
       <c r="P196" s="17"/>
     </row>
     <row r="197" spans="1:16" ht="17.25" customHeight="1">
       <c r="A197" s="14" t="str">
-        <f t="shared" si="12"/>
-        <v>ACTRIS_ctrl_lists:instrumentinterferencecheck</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:checktransmittancedecrease</v>
       </c>
       <c r="B197" s="16" t="s">
-        <v>318</v>
+        <v>242</v>
       </c>
       <c r="C197" s="17"/>
       <c r="D197" s="16" t="s">
-        <v>322</v>
+        <v>250</v>
       </c>
       <c r="E197" s="17" t="s">
         <v>251</v>
@@ -7007,22 +7207,22 @@
       <c r="F197" s="17"/>
       <c r="G197" s="17"/>
       <c r="H197" s="17" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I197" s="17"/>
       <c r="J197" s="17"/>
       <c r="K197" s="17"/>
       <c r="L197" s="17"/>
       <c r="M197" s="17"/>
-      <c r="N197" s="32" t="s">
-        <v>326</v>
+      <c r="N197" s="22" t="s">
+        <v>43</v>
       </c>
       <c r="O197" s="22"/>
       <c r="P197" s="17"/>
     </row>
     <row r="198" spans="1:16" ht="17.25" customHeight="1">
       <c r="A198" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="B198" s="16"/>
@@ -7043,19 +7243,19 @@
     </row>
     <row r="199" spans="1:16" ht="15" customHeight="1">
       <c r="A199" s="26" t="str">
-        <f t="shared" ref="A199" si="13">IF(ISBLANK($B199),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B199," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
-        <v>ACTRIS_ctrl_lists:stationaudit</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:instrumentperformancecheck</v>
       </c>
       <c r="B199" s="27" t="s">
-        <v>327</v>
+        <v>252</v>
       </c>
       <c r="C199" s="27"/>
       <c r="D199" s="27"/>
       <c r="E199" s="27" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F199" s="27" t="s">
-        <v>328</v>
+        <v>270</v>
       </c>
       <c r="G199" s="27"/>
       <c r="H199" s="27"/>
@@ -7072,224 +7272,240 @@
     </row>
     <row r="200" spans="1:16" ht="17.25" customHeight="1">
       <c r="A200" s="14" t="str">
-        <f t="shared" si="12"/>
-        <v>ACTRIS_ctrl_lists:checkifprocessedaccordingtoCiGas-NMHCmeasurementguidelinerequirements</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:checkofdetectionefficiency</v>
       </c>
       <c r="B200" s="16" t="s">
-        <v>329</v>
+        <v>253</v>
       </c>
       <c r="C200" s="17"/>
       <c r="D200" s="16" t="s">
-        <v>329</v>
+        <v>261</v>
       </c>
       <c r="E200" s="17" t="s">
-        <v>333</v>
+        <v>269</v>
       </c>
       <c r="F200" s="17"/>
       <c r="G200" s="17"/>
       <c r="H200" s="17" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I200" s="17"/>
       <c r="J200" s="17"/>
       <c r="K200" s="17"/>
       <c r="L200" s="17"/>
       <c r="M200" s="17"/>
-      <c r="N200" s="32" t="s">
-        <v>323</v>
+      <c r="N200" s="22" t="s">
+        <v>43</v>
       </c>
       <c r="O200" s="22"/>
       <c r="P200" s="17"/>
     </row>
     <row r="201" spans="1:16" ht="17.25" customHeight="1">
       <c r="A201" s="14" t="str">
-        <f t="shared" si="12"/>
-        <v>ACTRIS_ctrl_lists:checkifprocessedaccordingtoCiGas-VOCmeasurementguidelinerequirements</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:checkofsizingaccuracy</v>
       </c>
       <c r="B201" s="16" t="s">
-        <v>330</v>
+        <v>254</v>
       </c>
       <c r="C201" s="17"/>
       <c r="D201" s="16" t="s">
-        <v>330</v>
+        <v>262</v>
       </c>
       <c r="E201" s="17" t="s">
-        <v>333</v>
+        <v>269</v>
       </c>
       <c r="F201" s="17"/>
       <c r="G201" s="17"/>
       <c r="H201" s="17" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I201" s="17"/>
       <c r="J201" s="17"/>
       <c r="K201" s="17"/>
       <c r="L201" s="17"/>
       <c r="M201" s="17"/>
-      <c r="N201" s="32" t="s">
-        <v>323</v>
+      <c r="N201" s="22" t="s">
+        <v>43</v>
       </c>
       <c r="O201" s="22"/>
       <c r="P201" s="17"/>
     </row>
     <row r="202" spans="1:16" ht="17.25" customHeight="1">
       <c r="A202" s="14" t="str">
-        <f t="shared" si="12"/>
-        <v>ACTRIS_ctrl_lists:checkifprocessedaccordingtoCiGas-NOxmeasurementguidelinerequirements</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:checkofbaseline-zerocheck</v>
       </c>
       <c r="B202" s="16" t="s">
-        <v>331</v>
+        <v>255</v>
       </c>
       <c r="C202" s="17"/>
       <c r="D202" s="16" t="s">
-        <v>331</v>
+        <v>263</v>
       </c>
       <c r="E202" s="17" t="s">
-        <v>333</v>
+        <v>269</v>
       </c>
       <c r="F202" s="17"/>
       <c r="G202" s="17"/>
       <c r="H202" s="17" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I202" s="17"/>
       <c r="J202" s="17"/>
       <c r="K202" s="17"/>
       <c r="L202" s="17"/>
       <c r="M202" s="17"/>
-      <c r="N202" s="32" t="s">
-        <v>323</v>
+      <c r="N202" s="22" t="s">
+        <v>43</v>
       </c>
       <c r="O202" s="22"/>
       <c r="P202" s="17"/>
     </row>
     <row r="203" spans="1:16" ht="17.25" customHeight="1">
       <c r="A203" s="14" t="str">
-        <f t="shared" si="12"/>
-        <v>ACTRIS_ctrl_lists:checkifprocessedaccordingtoCiGas-condensablesmeasurementguidelinerequirements</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:checkofnoise</v>
       </c>
       <c r="B203" s="16" t="s">
-        <v>332</v>
+        <v>256</v>
       </c>
       <c r="C203" s="17"/>
       <c r="D203" s="16" t="s">
-        <v>332</v>
+        <v>264</v>
       </c>
       <c r="E203" s="17" t="s">
-        <v>333</v>
+        <v>269</v>
       </c>
       <c r="F203" s="17"/>
       <c r="G203" s="17"/>
       <c r="H203" s="17" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I203" s="17"/>
       <c r="J203" s="17"/>
       <c r="K203" s="17"/>
       <c r="L203" s="17"/>
       <c r="M203" s="17"/>
-      <c r="N203" s="32" t="s">
-        <v>323</v>
+      <c r="N203" s="22" t="s">
+        <v>43</v>
       </c>
       <c r="O203" s="22"/>
       <c r="P203" s="17"/>
     </row>
     <row r="204" spans="1:16" ht="17.25" customHeight="1">
       <c r="A204" s="14" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="B204" s="16"/>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:checkofoffset</v>
+      </c>
+      <c r="B204" s="16" t="s">
+        <v>257</v>
+      </c>
       <c r="C204" s="17"/>
-      <c r="D204" s="16"/>
-      <c r="E204" s="17"/>
+      <c r="D204" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="E204" s="17" t="s">
+        <v>269</v>
+      </c>
       <c r="F204" s="17"/>
       <c r="G204" s="17"/>
-      <c r="H204" s="17"/>
+      <c r="H204" s="17" t="s">
+        <v>311</v>
+      </c>
       <c r="I204" s="17"/>
       <c r="J204" s="17"/>
       <c r="K204" s="17"/>
       <c r="L204" s="17"/>
       <c r="M204" s="17"/>
-      <c r="N204" s="22"/>
+      <c r="N204" s="22" t="s">
+        <v>43</v>
+      </c>
       <c r="O204" s="22"/>
       <c r="P204" s="17"/>
     </row>
-    <row r="205" spans="1:16" ht="15" customHeight="1">
-      <c r="A205" s="23" t="str">
-        <f t="shared" ref="A205:A215" si="14">IF(ISBLANK($B205),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B205," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
-        <v>ACTRIS_ctrl_lists:aerosolremotesensingcontrolledlists</v>
-      </c>
-      <c r="B205" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="C205" s="24"/>
-      <c r="D205" s="24"/>
-      <c r="E205" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="F205" s="24"/>
-      <c r="G205" s="24"/>
-      <c r="H205" s="24"/>
-      <c r="I205" s="24"/>
-      <c r="J205" s="24"/>
-      <c r="K205" s="24"/>
-      <c r="L205" s="24"/>
-      <c r="M205" s="24"/>
-      <c r="N205" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="O205" s="24"/>
-      <c r="P205" s="24"/>
-    </row>
-    <row r="206" spans="1:16" ht="15" customHeight="1">
-      <c r="A206" s="26" t="str">
-        <f t="shared" si="14"/>
-        <v>ACTRIS_ctrl_lists:boundarycheck</v>
-      </c>
-      <c r="B206" s="27" t="s">
-        <v>236</v>
-      </c>
-      <c r="C206" s="27"/>
-      <c r="D206" s="27"/>
-      <c r="E206" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="F206" s="27" t="s">
-        <v>299</v>
-      </c>
-      <c r="G206" s="27"/>
-      <c r="H206" s="27"/>
-      <c r="I206" s="27"/>
-      <c r="J206" s="27"/>
-      <c r="K206" s="27"/>
-      <c r="L206" s="27"/>
-      <c r="M206" s="27"/>
-      <c r="N206" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="O206" s="27"/>
-      <c r="P206" s="27"/>
+    <row r="205" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A205" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:checkoffilterspot</v>
+      </c>
+      <c r="B205" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="C205" s="17"/>
+      <c r="D205" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="E205" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="F205" s="17"/>
+      <c r="G205" s="17"/>
+      <c r="H205" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="I205" s="17"/>
+      <c r="J205" s="17"/>
+      <c r="K205" s="17"/>
+      <c r="L205" s="17"/>
+      <c r="M205" s="17"/>
+      <c r="N205" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="O205" s="22"/>
+      <c r="P205" s="17"/>
+    </row>
+    <row r="206" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A206" s="14" t="str">
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:checkofhighvoltage</v>
+      </c>
+      <c r="B206" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="C206" s="17"/>
+      <c r="D206" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="E206" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="F206" s="17"/>
+      <c r="G206" s="17"/>
+      <c r="H206" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="I206" s="17"/>
+      <c r="J206" s="17"/>
+      <c r="K206" s="17"/>
+      <c r="L206" s="17"/>
+      <c r="M206" s="17"/>
+      <c r="N206" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="O206" s="22"/>
+      <c r="P206" s="17"/>
     </row>
     <row r="207" spans="1:16" ht="17.25" customHeight="1">
       <c r="A207" s="14" t="str">
-        <f t="shared" si="14"/>
-        <v>ACTRIS_ctrl_lists:negativeerrorcheck</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:highspancheckorspangascheck</v>
       </c>
       <c r="B207" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="C207" s="16"/>
+        <v>260</v>
+      </c>
+      <c r="C207" s="17"/>
       <c r="D207" s="16" t="s">
-        <v>291</v>
+        <v>268</v>
       </c>
       <c r="E207" s="17" t="s">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="F207" s="17"/>
       <c r="G207" s="17"/>
       <c r="H207" s="17" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I207" s="17"/>
       <c r="J207" s="17"/>
@@ -7297,98 +7513,80 @@
       <c r="L207" s="17"/>
       <c r="M207" s="17"/>
       <c r="N207" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O207" s="16" t="s">
-        <v>306</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="O207" s="22"/>
       <c r="P207" s="17"/>
     </row>
     <row r="208" spans="1:16" ht="17.25" customHeight="1">
       <c r="A208" s="14" t="str">
-        <f t="shared" si="14"/>
-        <v>ACTRIS_ctrl_lists:negativevaluescheck</v>
-      </c>
-      <c r="B208" s="16" t="s">
-        <v>289</v>
-      </c>
-      <c r="C208" s="16"/>
-      <c r="D208" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="E208" s="17" t="s">
-        <v>290</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B208" s="16"/>
+      <c r="C208" s="17"/>
+      <c r="D208" s="16"/>
+      <c r="E208" s="17"/>
       <c r="F208" s="17"/>
       <c r="G208" s="17"/>
-      <c r="H208" s="17" t="s">
-        <v>314</v>
-      </c>
+      <c r="H208" s="17"/>
       <c r="I208" s="17"/>
       <c r="J208" s="17"/>
       <c r="K208" s="17"/>
       <c r="L208" s="17"/>
       <c r="M208" s="17"/>
-      <c r="N208" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O208" s="16" t="s">
-        <v>306</v>
-      </c>
+      <c r="N208" s="22"/>
+      <c r="O208" s="22"/>
       <c r="P208" s="17"/>
     </row>
-    <row r="209" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A209" s="14" t="str">
-        <f t="shared" si="14"/>
-        <v>ACTRIS_ctrl_lists:checkonAerosolOpticalDepth</v>
-      </c>
-      <c r="B209" s="16" t="s">
-        <v>282</v>
-      </c>
-      <c r="C209" s="16"/>
-      <c r="D209" s="16" t="s">
-        <v>293</v>
-      </c>
-      <c r="E209" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="F209" s="17"/>
-      <c r="G209" s="17"/>
-      <c r="H209" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I209" s="17"/>
-      <c r="J209" s="17"/>
-      <c r="K209" s="17"/>
-      <c r="L209" s="17"/>
-      <c r="M209" s="17"/>
-      <c r="N209" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O209" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="P209" s="17"/>
+    <row r="209" spans="1:16" ht="15" customHeight="1">
+      <c r="A209" s="26" t="str">
+        <f t="shared" ref="A209" si="11">IF(ISBLANK($B209),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B209," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
+        <v>ACTRIS_ctrl_lists:instrumentcalibration</v>
+      </c>
+      <c r="B209" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="C209" s="27"/>
+      <c r="D209" s="27"/>
+      <c r="E209" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="F209" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="G209" s="27"/>
+      <c r="H209" s="27"/>
+      <c r="I209" s="27"/>
+      <c r="J209" s="27"/>
+      <c r="K209" s="27"/>
+      <c r="L209" s="27"/>
+      <c r="M209" s="27"/>
+      <c r="N209" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="O209" s="27"/>
+      <c r="P209" s="27"/>
     </row>
     <row r="210" spans="1:16" ht="17.25" customHeight="1">
       <c r="A210" s="14" t="str">
-        <f t="shared" si="14"/>
-        <v>ACTRIS_ctrl_lists:checkonIntegratedBackscatter</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:highvoltagecalibration</v>
       </c>
       <c r="B210" s="16" t="s">
-        <v>283</v>
-      </c>
-      <c r="C210" s="16"/>
+        <v>273</v>
+      </c>
+      <c r="C210" s="17"/>
       <c r="D210" s="16" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="E210" s="17" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="F210" s="17"/>
       <c r="G210" s="17"/>
       <c r="H210" s="17" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I210" s="17"/>
       <c r="J210" s="17"/>
@@ -7396,32 +7594,28 @@
       <c r="L210" s="17"/>
       <c r="M210" s="17"/>
       <c r="N210" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O210" s="16" t="s">
-        <v>306</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="O210" s="22"/>
       <c r="P210" s="17"/>
     </row>
     <row r="211" spans="1:16" ht="17.25" customHeight="1">
       <c r="A211" s="14" t="str">
-        <f t="shared" si="14"/>
-        <v>ACTRIS_ctrl_lists:checkonlidarratio</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:highspancalibration</v>
       </c>
       <c r="B211" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="C211" s="16"/>
-      <c r="D211" s="16" t="s">
-        <v>295</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="C211" s="17"/>
+      <c r="D211" s="16"/>
       <c r="E211" s="17" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="F211" s="17"/>
       <c r="G211" s="17"/>
       <c r="H211" s="17" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I211" s="17"/>
       <c r="J211" s="17"/>
@@ -7429,32 +7623,30 @@
       <c r="L211" s="17"/>
       <c r="M211" s="17"/>
       <c r="N211" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O211" s="16" t="s">
-        <v>306</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="O211" s="22"/>
       <c r="P211" s="17"/>
     </row>
     <row r="212" spans="1:16" ht="17.25" customHeight="1">
       <c r="A212" s="14" t="str">
-        <f t="shared" si="14"/>
-        <v>ACTRIS_ctrl_lists:checkonvolumedepolarization</v>
+        <f t="shared" si="5"/>
+        <v>ACTRIS_ctrl_lists:flowcalibration</v>
       </c>
       <c r="B212" s="16" t="s">
-        <v>286</v>
-      </c>
-      <c r="C212" s="16"/>
+        <v>275</v>
+      </c>
+      <c r="C212" s="17"/>
       <c r="D212" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="E212" s="17" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="F212" s="17"/>
       <c r="G212" s="17"/>
       <c r="H212" s="17" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="I212" s="17"/>
       <c r="J212" s="17"/>
@@ -7462,1230 +7654,1966 @@
       <c r="L212" s="17"/>
       <c r="M212" s="17"/>
       <c r="N212" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O212" s="16" t="s">
-        <v>306</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="O212" s="22"/>
       <c r="P212" s="17"/>
     </row>
     <row r="213" spans="1:16" ht="17.25" customHeight="1">
       <c r="A213" s="14" t="str">
-        <f t="shared" si="14"/>
-        <v>ACTRIS_ctrl_lists:checkonparticledepolarization</v>
-      </c>
-      <c r="B213" s="16" t="s">
-        <v>285</v>
-      </c>
-      <c r="C213" s="16"/>
-      <c r="D213" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="E213" s="17" t="s">
-        <v>290</v>
-      </c>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="B213" s="16"/>
+      <c r="C213" s="17"/>
+      <c r="D213" s="16"/>
+      <c r="E213" s="17"/>
       <c r="F213" s="17"/>
       <c r="G213" s="17"/>
-      <c r="H213" s="17" t="s">
-        <v>314</v>
-      </c>
+      <c r="H213" s="17"/>
       <c r="I213" s="17"/>
       <c r="J213" s="17"/>
       <c r="K213" s="17"/>
       <c r="L213" s="17"/>
       <c r="M213" s="17"/>
-      <c r="N213" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O213" s="16" t="s">
-        <v>306</v>
-      </c>
+      <c r="N213" s="22"/>
+      <c r="O213" s="22"/>
       <c r="P213" s="17"/>
     </row>
-    <row r="214" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A214" s="14" t="str">
-        <f t="shared" si="14"/>
-        <v>ACTRIS_ctrl_lists:checkonwatervapormixingratio</v>
-      </c>
-      <c r="B214" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="C214" s="16"/>
-      <c r="D214" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="E214" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="F214" s="17"/>
-      <c r="G214" s="17"/>
-      <c r="H214" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I214" s="17"/>
-      <c r="J214" s="17"/>
-      <c r="K214" s="17"/>
-      <c r="L214" s="17"/>
-      <c r="M214" s="17"/>
-      <c r="N214" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O214" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="P214" s="17"/>
-    </row>
-    <row r="215" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A215" s="14" t="str">
-        <f t="shared" si="14"/>
+    <row r="214" spans="1:16" ht="15" customHeight="1">
+      <c r="A214" s="23" t="str">
+        <f t="shared" ref="A214:A215" si="12">IF(ISBLANK($B214),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B214," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
+        <v>ACTRIS_ctrl_lists:cloudinsitucontrolledlists</v>
+      </c>
+      <c r="B214" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="C214" s="24"/>
+      <c r="D214" s="24"/>
+      <c r="E214" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="F214" s="24"/>
+      <c r="G214" s="24"/>
+      <c r="H214" s="24"/>
+      <c r="I214" s="24"/>
+      <c r="J214" s="24"/>
+      <c r="K214" s="24"/>
+      <c r="L214" s="24"/>
+      <c r="M214" s="24"/>
+      <c r="N214" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="O214" s="24"/>
+      <c r="P214" s="24"/>
+    </row>
+    <row r="215" spans="1:16" ht="15" customHeight="1">
+      <c r="A215" s="26" t="str">
+        <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="B215" s="16"/>
-      <c r="C215" s="17"/>
-      <c r="D215" s="16"/>
-      <c r="E215" s="17"/>
-      <c r="F215" s="17"/>
-      <c r="G215" s="17"/>
-      <c r="H215" s="17"/>
-      <c r="I215" s="17"/>
-      <c r="J215" s="17"/>
-      <c r="K215" s="17"/>
-      <c r="L215" s="17"/>
-      <c r="M215" s="17"/>
-      <c r="N215" s="22"/>
-      <c r="O215" s="22"/>
-      <c r="P215" s="17"/>
-    </row>
-    <row r="216" spans="1:16" ht="15" customHeight="1">
-      <c r="A216" s="26" t="str">
-        <f t="shared" ref="A216:A219" si="15">IF(ISBLANK($B216),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B216," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
-        <v>ACTRIS_ctrl_lists:combinedassessment</v>
-      </c>
-      <c r="B216" s="27" t="s">
-        <v>280</v>
-      </c>
-      <c r="C216" s="27"/>
-      <c r="D216" s="27"/>
-      <c r="E216" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="F216" s="27" t="s">
-        <v>334</v>
-      </c>
-      <c r="G216" s="27"/>
-      <c r="H216" s="27"/>
-      <c r="I216" s="27"/>
-      <c r="J216" s="27"/>
-      <c r="K216" s="27"/>
-      <c r="L216" s="27"/>
-      <c r="M216" s="27"/>
-      <c r="N216" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="O216" s="27"/>
-      <c r="P216" s="27"/>
+      <c r="B215" s="27"/>
+      <c r="C215" s="27"/>
+      <c r="D215" s="27"/>
+      <c r="E215" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="F215" s="27"/>
+      <c r="G215" s="27"/>
+      <c r="H215" s="27"/>
+      <c r="I215" s="27"/>
+      <c r="J215" s="27"/>
+      <c r="K215" s="27"/>
+      <c r="L215" s="27"/>
+      <c r="M215" s="27"/>
+      <c r="N215" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="O215" s="27"/>
+      <c r="P215" s="27"/>
+    </row>
+    <row r="216" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A216" s="14"/>
+      <c r="B216" s="16"/>
+      <c r="C216" s="17"/>
+      <c r="D216" s="16"/>
+      <c r="E216" s="17"/>
+      <c r="F216" s="17"/>
+      <c r="G216" s="17"/>
+      <c r="H216" s="17"/>
+      <c r="I216" s="17"/>
+      <c r="J216" s="17"/>
+      <c r="K216" s="17"/>
+      <c r="L216" s="17"/>
+      <c r="M216" s="17"/>
+      <c r="N216" s="22"/>
+      <c r="O216" s="22"/>
+      <c r="P216" s="17"/>
     </row>
     <row r="217" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A217" s="14" t="str">
-        <f t="shared" si="15"/>
-        <v>ACTRIS_ctrl_lists:Earlinetlegacydatalabeledascirruscontaminated</v>
-      </c>
-      <c r="B217" s="16" t="s">
-        <v>300</v>
-      </c>
-      <c r="C217" s="16"/>
-      <c r="D217" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="E217" s="17" t="s">
-        <v>304</v>
-      </c>
+      <c r="A217" s="14"/>
+      <c r="B217" s="16"/>
+      <c r="C217" s="17"/>
+      <c r="D217" s="16"/>
+      <c r="E217" s="17"/>
       <c r="F217" s="17"/>
       <c r="G217" s="17"/>
-      <c r="H217" s="17" t="s">
-        <v>314</v>
-      </c>
+      <c r="H217" s="17"/>
       <c r="I217" s="17"/>
       <c r="J217" s="17"/>
       <c r="K217" s="17"/>
       <c r="L217" s="17"/>
       <c r="M217" s="17"/>
-      <c r="N217" s="22" t="s">
+      <c r="N217" s="22"/>
+      <c r="O217" s="22"/>
+      <c r="P217" s="17"/>
+    </row>
+    <row r="218" spans="1:16" ht="15" customHeight="1">
+      <c r="A218" s="23" t="str">
+        <f t="shared" ref="A218:A230" si="13">IF(ISBLANK($B218),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B218," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
+        <v>ACTRIS_ctrl_lists:reactivetracegasinsitucontrolledlists</v>
+      </c>
+      <c r="B218" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="C218" s="24"/>
+      <c r="D218" s="24"/>
+      <c r="E218" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="F218" s="24"/>
+      <c r="G218" s="24"/>
+      <c r="H218" s="24"/>
+      <c r="I218" s="24"/>
+      <c r="J218" s="24"/>
+      <c r="K218" s="24"/>
+      <c r="L218" s="24"/>
+      <c r="M218" s="24"/>
+      <c r="N218" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="O218" s="24"/>
+      <c r="P218" s="24"/>
+    </row>
+    <row r="219" spans="1:16" ht="15" customHeight="1">
+      <c r="A219" s="26" t="str">
+        <f t="shared" si="13"/>
+        <v>ACTRIS_ctrl_lists:instrumentstatuscheck</v>
+      </c>
+      <c r="B219" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="C219" s="27"/>
+      <c r="D219" s="27"/>
+      <c r="E219" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="F219" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="G219" s="27"/>
+      <c r="H219" s="27"/>
+      <c r="I219" s="27"/>
+      <c r="J219" s="27"/>
+      <c r="K219" s="27"/>
+      <c r="L219" s="27"/>
+      <c r="M219" s="27"/>
+      <c r="N219" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="O219" s="27"/>
+      <c r="P219" s="27"/>
+    </row>
+    <row r="220" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A220" s="14" t="str">
+        <f t="shared" si="13"/>
+        <v>ACTRIS_ctrl_lists:voltagesettingcheck</v>
+      </c>
+      <c r="B220" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="C220" s="17"/>
+      <c r="D220" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="E220" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="F220" s="17"/>
+      <c r="G220" s="17"/>
+      <c r="H220" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="I220" s="17"/>
+      <c r="J220" s="17"/>
+      <c r="K220" s="17"/>
+      <c r="L220" s="17"/>
+      <c r="M220" s="17"/>
+      <c r="N220" s="32" t="s">
+        <v>323</v>
+      </c>
+      <c r="O220" s="22"/>
+      <c r="P220" s="17"/>
+    </row>
+    <row r="221" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A221" s="14" t="str">
+        <f t="shared" si="13"/>
+        <v>ACTRIS_ctrl_lists:flowsettingcheck</v>
+      </c>
+      <c r="B221" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="C221" s="17"/>
+      <c r="D221" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="E221" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="F221" s="17"/>
+      <c r="G221" s="17"/>
+      <c r="H221" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="I221" s="17"/>
+      <c r="J221" s="17"/>
+      <c r="K221" s="17"/>
+      <c r="L221" s="17"/>
+      <c r="M221" s="17"/>
+      <c r="N221" s="32" t="s">
+        <v>324</v>
+      </c>
+      <c r="O221" s="22"/>
+      <c r="P221" s="17"/>
+    </row>
+    <row r="222" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A222" s="14" t="str">
+        <f t="shared" si="13"/>
+        <v>ACTRIS_ctrl_lists:pressuresettingcheck</v>
+      </c>
+      <c r="B222" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="C222" s="17"/>
+      <c r="D222" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="E222" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="F222" s="17"/>
+      <c r="G222" s="17"/>
+      <c r="H222" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="I222" s="17"/>
+      <c r="J222" s="17"/>
+      <c r="K222" s="17"/>
+      <c r="L222" s="17"/>
+      <c r="M222" s="17"/>
+      <c r="N222" s="32" t="s">
+        <v>325</v>
+      </c>
+      <c r="O222" s="22"/>
+      <c r="P222" s="17"/>
+    </row>
+    <row r="223" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A223" s="14" t="str">
+        <f t="shared" si="13"/>
+        <v>ACTRIS_ctrl_lists:instrumentinterferencecheck</v>
+      </c>
+      <c r="B223" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="C223" s="17"/>
+      <c r="D223" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="E223" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="F223" s="17"/>
+      <c r="G223" s="17"/>
+      <c r="H223" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="I223" s="17"/>
+      <c r="J223" s="17"/>
+      <c r="K223" s="17"/>
+      <c r="L223" s="17"/>
+      <c r="M223" s="17"/>
+      <c r="N223" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="O223" s="22"/>
+      <c r="P223" s="17"/>
+    </row>
+    <row r="224" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A224" s="14" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="B224" s="16"/>
+      <c r="C224" s="17"/>
+      <c r="D224" s="16"/>
+      <c r="E224" s="17"/>
+      <c r="F224" s="17"/>
+      <c r="G224" s="17"/>
+      <c r="H224" s="17"/>
+      <c r="I224" s="17"/>
+      <c r="J224" s="17"/>
+      <c r="K224" s="17"/>
+      <c r="L224" s="17"/>
+      <c r="M224" s="17"/>
+      <c r="N224" s="22"/>
+      <c r="O224" s="22"/>
+      <c r="P224" s="17"/>
+    </row>
+    <row r="225" spans="1:16" ht="15" customHeight="1">
+      <c r="A225" s="26" t="str">
+        <f t="shared" ref="A225" si="14">IF(ISBLANK($B225),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B225," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
+        <v>ACTRIS_ctrl_lists:stationaudit</v>
+      </c>
+      <c r="B225" s="27" t="s">
+        <v>327</v>
+      </c>
+      <c r="C225" s="27"/>
+      <c r="D225" s="27"/>
+      <c r="E225" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="F225" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="G225" s="27"/>
+      <c r="H225" s="27"/>
+      <c r="I225" s="27"/>
+      <c r="J225" s="27"/>
+      <c r="K225" s="27"/>
+      <c r="L225" s="27"/>
+      <c r="M225" s="27"/>
+      <c r="N225" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="O225" s="27"/>
+      <c r="P225" s="27"/>
+    </row>
+    <row r="226" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A226" s="14" t="str">
+        <f t="shared" si="13"/>
+        <v>ACTRIS_ctrl_lists:checkifprocessedaccordingtoCiGas-NMHCmeasurementguidelinerequirements</v>
+      </c>
+      <c r="B226" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="C226" s="17"/>
+      <c r="D226" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="E226" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="F226" s="17"/>
+      <c r="G226" s="17"/>
+      <c r="H226" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="I226" s="17"/>
+      <c r="J226" s="17"/>
+      <c r="K226" s="17"/>
+      <c r="L226" s="17"/>
+      <c r="M226" s="17"/>
+      <c r="N226" s="32" t="s">
+        <v>323</v>
+      </c>
+      <c r="O226" s="22"/>
+      <c r="P226" s="17"/>
+    </row>
+    <row r="227" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A227" s="14" t="str">
+        <f t="shared" si="13"/>
+        <v>ACTRIS_ctrl_lists:checkifprocessedaccordingtoCiGas-VOCmeasurementguidelinerequirements</v>
+      </c>
+      <c r="B227" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="C227" s="17"/>
+      <c r="D227" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="E227" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="F227" s="17"/>
+      <c r="G227" s="17"/>
+      <c r="H227" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="I227" s="17"/>
+      <c r="J227" s="17"/>
+      <c r="K227" s="17"/>
+      <c r="L227" s="17"/>
+      <c r="M227" s="17"/>
+      <c r="N227" s="32" t="s">
+        <v>323</v>
+      </c>
+      <c r="O227" s="22"/>
+      <c r="P227" s="17"/>
+    </row>
+    <row r="228" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A228" s="14" t="str">
+        <f t="shared" si="13"/>
+        <v>ACTRIS_ctrl_lists:checkifprocessedaccordingtoCiGas-NOxmeasurementguidelinerequirements</v>
+      </c>
+      <c r="B228" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="C228" s="17"/>
+      <c r="D228" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="E228" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="F228" s="17"/>
+      <c r="G228" s="17"/>
+      <c r="H228" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="I228" s="17"/>
+      <c r="J228" s="17"/>
+      <c r="K228" s="17"/>
+      <c r="L228" s="17"/>
+      <c r="M228" s="17"/>
+      <c r="N228" s="32" t="s">
+        <v>323</v>
+      </c>
+      <c r="O228" s="22"/>
+      <c r="P228" s="17"/>
+    </row>
+    <row r="229" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A229" s="14" t="str">
+        <f t="shared" si="13"/>
+        <v>ACTRIS_ctrl_lists:checkifprocessedaccordingtoCiGas-condensablesmeasurementguidelinerequirements</v>
+      </c>
+      <c r="B229" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="C229" s="17"/>
+      <c r="D229" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="E229" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="F229" s="17"/>
+      <c r="G229" s="17"/>
+      <c r="H229" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="I229" s="17"/>
+      <c r="J229" s="17"/>
+      <c r="K229" s="17"/>
+      <c r="L229" s="17"/>
+      <c r="M229" s="17"/>
+      <c r="N229" s="32" t="s">
+        <v>323</v>
+      </c>
+      <c r="O229" s="22"/>
+      <c r="P229" s="17"/>
+    </row>
+    <row r="230" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A230" s="14" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="B230" s="16"/>
+      <c r="C230" s="17"/>
+      <c r="D230" s="16"/>
+      <c r="E230" s="17"/>
+      <c r="F230" s="17"/>
+      <c r="G230" s="17"/>
+      <c r="H230" s="17"/>
+      <c r="I230" s="17"/>
+      <c r="J230" s="17"/>
+      <c r="K230" s="17"/>
+      <c r="L230" s="17"/>
+      <c r="M230" s="17"/>
+      <c r="N230" s="22"/>
+      <c r="O230" s="22"/>
+      <c r="P230" s="17"/>
+    </row>
+    <row r="231" spans="1:16" ht="15" customHeight="1">
+      <c r="A231" s="23" t="str">
+        <f t="shared" ref="A231:A241" si="15">IF(ISBLANK($B231),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B231," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
+        <v>ACTRIS_ctrl_lists:aerosolremotesensingcontrolledlists</v>
+      </c>
+      <c r="B231" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="C231" s="24"/>
+      <c r="D231" s="24"/>
+      <c r="E231" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="F231" s="24"/>
+      <c r="G231" s="24"/>
+      <c r="H231" s="24"/>
+      <c r="I231" s="24"/>
+      <c r="J231" s="24"/>
+      <c r="K231" s="24"/>
+      <c r="L231" s="24"/>
+      <c r="M231" s="24"/>
+      <c r="N231" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="O231" s="24"/>
+      <c r="P231" s="24"/>
+    </row>
+    <row r="232" spans="1:16" ht="15" customHeight="1">
+      <c r="A232" s="26" t="str">
+        <f t="shared" si="15"/>
+        <v>ACTRIS_ctrl_lists:boundarycheck</v>
+      </c>
+      <c r="B232" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="C232" s="27"/>
+      <c r="D232" s="27"/>
+      <c r="E232" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="F232" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="G232" s="27"/>
+      <c r="H232" s="27"/>
+      <c r="I232" s="27"/>
+      <c r="J232" s="27"/>
+      <c r="K232" s="27"/>
+      <c r="L232" s="27"/>
+      <c r="M232" s="27"/>
+      <c r="N232" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="O232" s="27"/>
+      <c r="P232" s="27"/>
+    </row>
+    <row r="233" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A233" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>ACTRIS_ctrl_lists:negativeerrorcheck</v>
+      </c>
+      <c r="B233" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="C233" s="16"/>
+      <c r="D233" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="E233" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="F233" s="17"/>
+      <c r="G233" s="17"/>
+      <c r="H233" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I233" s="17"/>
+      <c r="J233" s="17"/>
+      <c r="K233" s="17"/>
+      <c r="L233" s="17"/>
+      <c r="M233" s="17"/>
+      <c r="N233" s="22" t="s">
         <v>305</v>
       </c>
-      <c r="O217" s="16" t="s">
+      <c r="O233" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="P217" s="17"/>
-    </row>
-    <row r="218" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A218" s="14" t="str">
+      <c r="P233" s="17"/>
+    </row>
+    <row r="234" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A234" s="14" t="str">
         <f t="shared" si="15"/>
-        <v>ACTRIS_ctrl_lists:checkonatmosphericmolecularcalculationsource</v>
-      </c>
-      <c r="B218" s="16" t="s">
-        <v>302</v>
-      </c>
-      <c r="C218" s="16"/>
-      <c r="D218" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="E218" s="17" t="s">
-        <v>304</v>
-      </c>
-      <c r="F218" s="17"/>
-      <c r="G218" s="17"/>
-      <c r="H218" s="17" t="s">
+        <v>ACTRIS_ctrl_lists:negativevaluescheck</v>
+      </c>
+      <c r="B234" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="C234" s="16"/>
+      <c r="D234" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="E234" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="F234" s="17"/>
+      <c r="G234" s="17"/>
+      <c r="H234" s="17" t="s">
         <v>314</v>
       </c>
-      <c r="I218" s="17"/>
-      <c r="J218" s="17"/>
-      <c r="K218" s="17"/>
-      <c r="L218" s="17"/>
-      <c r="M218" s="17"/>
-      <c r="N218" s="22" t="s">
+      <c r="I234" s="17"/>
+      <c r="J234" s="17"/>
+      <c r="K234" s="17"/>
+      <c r="L234" s="17"/>
+      <c r="M234" s="17"/>
+      <c r="N234" s="22" t="s">
         <v>305</v>
       </c>
-      <c r="O218" s="16" t="s">
+      <c r="O234" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="P218" s="17"/>
-    </row>
-    <row r="219" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A219" s="14" t="str">
+      <c r="P234" s="17"/>
+    </row>
+    <row r="235" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A235" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>ACTRIS_ctrl_lists:checkonAerosolOpticalDepth</v>
+      </c>
+      <c r="B235" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="C235" s="16"/>
+      <c r="D235" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="E235" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="F235" s="17"/>
+      <c r="G235" s="17"/>
+      <c r="H235" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I235" s="17"/>
+      <c r="J235" s="17"/>
+      <c r="K235" s="17"/>
+      <c r="L235" s="17"/>
+      <c r="M235" s="17"/>
+      <c r="N235" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O235" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="P235" s="17"/>
+    </row>
+    <row r="236" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A236" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>ACTRIS_ctrl_lists:checkonIntegratedBackscatter</v>
+      </c>
+      <c r="B236" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="C236" s="16"/>
+      <c r="D236" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="E236" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="F236" s="17"/>
+      <c r="G236" s="17"/>
+      <c r="H236" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I236" s="17"/>
+      <c r="J236" s="17"/>
+      <c r="K236" s="17"/>
+      <c r="L236" s="17"/>
+      <c r="M236" s="17"/>
+      <c r="N236" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O236" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="P236" s="17"/>
+    </row>
+    <row r="237" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A237" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>ACTRIS_ctrl_lists:checkonlidarratio</v>
+      </c>
+      <c r="B237" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="C237" s="16"/>
+      <c r="D237" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="E237" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="F237" s="17"/>
+      <c r="G237" s="17"/>
+      <c r="H237" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I237" s="17"/>
+      <c r="J237" s="17"/>
+      <c r="K237" s="17"/>
+      <c r="L237" s="17"/>
+      <c r="M237" s="17"/>
+      <c r="N237" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O237" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="P237" s="17"/>
+    </row>
+    <row r="238" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A238" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>ACTRIS_ctrl_lists:checkonvolumedepolarization</v>
+      </c>
+      <c r="B238" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="C238" s="16"/>
+      <c r="D238" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="E238" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="F238" s="17"/>
+      <c r="G238" s="17"/>
+      <c r="H238" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I238" s="17"/>
+      <c r="J238" s="17"/>
+      <c r="K238" s="17"/>
+      <c r="L238" s="17"/>
+      <c r="M238" s="17"/>
+      <c r="N238" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O238" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="P238" s="17"/>
+    </row>
+    <row r="239" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A239" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>ACTRIS_ctrl_lists:checkonparticledepolarization</v>
+      </c>
+      <c r="B239" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="C239" s="16"/>
+      <c r="D239" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="E239" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="F239" s="17"/>
+      <c r="G239" s="17"/>
+      <c r="H239" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I239" s="17"/>
+      <c r="J239" s="17"/>
+      <c r="K239" s="17"/>
+      <c r="L239" s="17"/>
+      <c r="M239" s="17"/>
+      <c r="N239" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O239" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="P239" s="17"/>
+    </row>
+    <row r="240" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A240" s="14" t="str">
+        <f t="shared" si="15"/>
+        <v>ACTRIS_ctrl_lists:checkonwatervapormixingratio</v>
+      </c>
+      <c r="B240" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C240" s="16"/>
+      <c r="D240" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="E240" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="F240" s="17"/>
+      <c r="G240" s="17"/>
+      <c r="H240" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I240" s="17"/>
+      <c r="J240" s="17"/>
+      <c r="K240" s="17"/>
+      <c r="L240" s="17"/>
+      <c r="M240" s="17"/>
+      <c r="N240" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O240" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="P240" s="17"/>
+    </row>
+    <row r="241" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A241" s="14" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="B219" s="16"/>
-      <c r="C219" s="17"/>
-      <c r="D219" s="16"/>
-      <c r="E219" s="17"/>
-      <c r="F219" s="17"/>
-      <c r="G219" s="17"/>
-      <c r="H219" s="17"/>
-      <c r="I219" s="17"/>
-      <c r="J219" s="17"/>
-      <c r="K219" s="17"/>
-      <c r="L219" s="17"/>
-      <c r="M219" s="17"/>
-      <c r="N219" s="22"/>
-      <c r="O219" s="22"/>
-      <c r="P219" s="17"/>
-    </row>
-    <row r="220" spans="1:16" ht="15" customHeight="1">
-      <c r="A220" s="26" t="str">
-        <f t="shared" ref="A220:A221" si="16">IF(ISBLANK($B220),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B220," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
-        <v>ACTRIS_ctrl_lists:physicaldependencecheck</v>
-      </c>
-      <c r="B220" s="27" t="s">
-        <v>281</v>
-      </c>
-      <c r="C220" s="27"/>
-      <c r="D220" s="27"/>
-      <c r="E220" s="27" t="s">
+      <c r="B241" s="16"/>
+      <c r="C241" s="17"/>
+      <c r="D241" s="16"/>
+      <c r="E241" s="17"/>
+      <c r="F241" s="17"/>
+      <c r="G241" s="17"/>
+      <c r="H241" s="17"/>
+      <c r="I241" s="17"/>
+      <c r="J241" s="17"/>
+      <c r="K241" s="17"/>
+      <c r="L241" s="17"/>
+      <c r="M241" s="17"/>
+      <c r="N241" s="22"/>
+      <c r="O241" s="22"/>
+      <c r="P241" s="17"/>
+    </row>
+    <row r="242" spans="1:16" ht="15" customHeight="1">
+      <c r="A242" s="26" t="str">
+        <f t="shared" ref="A242:A245" si="16">IF(ISBLANK($B242),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B242," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
+        <v>ACTRIS_ctrl_lists:combinedassessment</v>
+      </c>
+      <c r="B242" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="C242" s="27"/>
+      <c r="D242" s="27"/>
+      <c r="E242" s="27" t="s">
         <v>199</v>
       </c>
-      <c r="F220" s="27" t="s">
-        <v>309</v>
-      </c>
-      <c r="G220" s="27"/>
-      <c r="H220" s="27"/>
-      <c r="I220" s="27"/>
-      <c r="J220" s="27"/>
-      <c r="K220" s="27"/>
-      <c r="L220" s="27"/>
-      <c r="M220" s="27"/>
-      <c r="N220" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="O220" s="27"/>
-      <c r="P220" s="27"/>
-    </row>
-    <row r="221" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A221" s="14" t="str">
-        <f t="shared" si="16"/>
-        <v>ACTRIS_ctrl_lists:consistencyofdifferentopticalproperties</v>
-      </c>
-      <c r="B221" s="16" t="s">
-        <v>307</v>
-      </c>
-      <c r="C221" s="16"/>
-      <c r="D221" s="16" t="s">
-        <v>308</v>
-      </c>
-      <c r="E221" s="16" t="s">
-        <v>310</v>
-      </c>
-      <c r="F221" s="16"/>
-      <c r="G221" s="16"/>
-      <c r="H221" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I221" s="16"/>
-      <c r="J221" s="16"/>
-      <c r="K221" s="16"/>
-      <c r="L221" s="16"/>
-      <c r="M221" s="16"/>
-      <c r="N221" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O221" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="P221" s="17"/>
-    </row>
-    <row r="222" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A222" s="14"/>
-      <c r="B222" s="16"/>
-      <c r="C222" s="16"/>
-      <c r="D222" s="16"/>
-      <c r="E222" s="16"/>
-      <c r="F222" s="16"/>
-      <c r="G222" s="16"/>
-      <c r="H222" s="17"/>
-      <c r="I222" s="16"/>
-      <c r="J222" s="16"/>
-      <c r="K222" s="16"/>
-      <c r="L222" s="16"/>
-      <c r="M222" s="16"/>
-      <c r="N222" s="22"/>
-      <c r="O222" s="16"/>
-      <c r="P222" s="17"/>
-    </row>
-    <row r="223" spans="1:16" ht="15" customHeight="1">
-      <c r="A223" s="26" t="str">
-        <f t="shared" ref="A223:A239" si="17">IF(ISBLANK($B223),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B223," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
-        <v>ACTRIS_ctrl_lists:instrumentstatuscheck</v>
-      </c>
-      <c r="B223" s="27" t="s">
-        <v>233</v>
-      </c>
-      <c r="C223" s="27"/>
-      <c r="D223" s="27"/>
-      <c r="E223" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="F223" s="27" t="s">
-        <v>234</v>
-      </c>
-      <c r="G223" s="27"/>
-      <c r="H223" s="27"/>
-      <c r="I223" s="27"/>
-      <c r="J223" s="27"/>
-      <c r="K223" s="27"/>
-      <c r="L223" s="27"/>
-      <c r="M223" s="27"/>
-      <c r="N223" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="O223" s="27"/>
-      <c r="P223" s="27"/>
-    </row>
-    <row r="224" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A224" s="14" t="str">
-        <f t="shared" si="17"/>
-        <v>ACTRIS_ctrl_lists:batterylevelcheck</v>
-      </c>
-      <c r="B224" s="16" t="s">
-        <v>335</v>
-      </c>
-      <c r="C224" s="16"/>
-      <c r="D224" s="16" t="s">
-        <v>336</v>
-      </c>
-      <c r="E224" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="F224" s="16"/>
-      <c r="G224" s="16"/>
-      <c r="H224" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I224" s="16"/>
-      <c r="J224" s="16"/>
-      <c r="K224" s="16"/>
-      <c r="L224" s="16"/>
-      <c r="M224" s="16"/>
-      <c r="N224" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O224" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="P224" s="17"/>
-    </row>
-    <row r="225" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A225" s="14" t="str">
-        <f t="shared" si="17"/>
-        <v>ACTRIS_ctrl_lists:trackingsystemcheck</v>
-      </c>
-      <c r="B225" s="16" t="s">
-        <v>338</v>
-      </c>
-      <c r="C225" s="16"/>
-      <c r="D225" s="16" t="s">
-        <v>339</v>
-      </c>
-      <c r="E225" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="F225" s="16"/>
-      <c r="G225" s="16"/>
-      <c r="H225" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I225" s="16"/>
-      <c r="J225" s="16"/>
-      <c r="K225" s="16"/>
-      <c r="L225" s="16"/>
-      <c r="M225" s="16"/>
-      <c r="N225" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O225" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="P225" s="17"/>
-    </row>
-    <row r="226" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A226" s="14" t="str">
-        <f t="shared" si="17"/>
-        <v>ACTRIS_ctrl_lists:humiditysensorcheck</v>
-      </c>
-      <c r="B226" s="16" t="s">
-        <v>340</v>
-      </c>
-      <c r="C226" s="16"/>
-      <c r="D226" s="16" t="s">
-        <v>341</v>
-      </c>
-      <c r="E226" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="F226" s="16"/>
-      <c r="G226" s="16"/>
-      <c r="H226" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I226" s="16"/>
-      <c r="J226" s="16"/>
-      <c r="K226" s="16"/>
-      <c r="L226" s="16"/>
-      <c r="M226" s="16"/>
-      <c r="N226" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O226" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="P226" s="17"/>
-    </row>
-    <row r="227" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A227" s="14" t="str">
-        <f t="shared" si="17"/>
-        <v>ACTRIS_ctrl_lists:temperaturesensorcheck</v>
-      </c>
-      <c r="B227" s="16" t="s">
-        <v>342</v>
-      </c>
-      <c r="C227" s="16"/>
-      <c r="D227" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="E227" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="F227" s="16"/>
-      <c r="G227" s="16"/>
-      <c r="H227" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I227" s="16"/>
-      <c r="J227" s="16"/>
-      <c r="K227" s="16"/>
-      <c r="L227" s="16"/>
-      <c r="M227" s="16"/>
-      <c r="N227" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O227" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="P227" s="17"/>
-    </row>
-    <row r="228" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A228" s="14" t="str">
-        <f t="shared" si="17"/>
-        <v>ACTRIS_ctrl_lists:calibrationshiftcheck</v>
-      </c>
-      <c r="B228" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="C228" s="16"/>
-      <c r="D228" s="16" t="s">
-        <v>345</v>
-      </c>
-      <c r="E228" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="F228" s="16"/>
-      <c r="G228" s="16"/>
-      <c r="H228" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I228" s="16"/>
-      <c r="J228" s="16"/>
-      <c r="K228" s="16"/>
-      <c r="L228" s="16"/>
-      <c r="M228" s="16"/>
-      <c r="N228" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O228" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="P228" s="17"/>
-    </row>
-    <row r="229" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A229" s="14" t="str">
-        <f t="shared" si="17"/>
-        <v>ACTRIS_ctrl_lists:opticscheck</v>
-      </c>
-      <c r="B229" s="16" t="s">
-        <v>346</v>
-      </c>
-      <c r="C229" s="16"/>
-      <c r="D229" s="16" t="s">
-        <v>347</v>
-      </c>
-      <c r="E229" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="F229" s="16"/>
-      <c r="G229" s="16"/>
-      <c r="H229" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I229" s="16"/>
-      <c r="J229" s="16"/>
-      <c r="K229" s="16"/>
-      <c r="L229" s="16"/>
-      <c r="M229" s="16"/>
-      <c r="N229" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O229" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="P229" s="17"/>
-    </row>
-    <row r="230" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A230" s="14" t="str">
-        <f t="shared" si="17"/>
-        <v>ACTRIS_ctrl_lists:collimatorcheck</v>
-      </c>
-      <c r="B230" s="16" t="s">
-        <v>348</v>
-      </c>
-      <c r="C230" s="16"/>
-      <c r="D230" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="E230" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="F230" s="16"/>
-      <c r="G230" s="16"/>
-      <c r="H230" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I230" s="16"/>
-      <c r="J230" s="16"/>
-      <c r="K230" s="16"/>
-      <c r="L230" s="16"/>
-      <c r="M230" s="16"/>
-      <c r="N230" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O230" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="P230" s="17"/>
-    </row>
-    <row r="231" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A231" s="14" t="str">
-        <f t="shared" si="17"/>
-        <v>ACTRIS_ctrl_lists:systemcablingcheck</v>
-      </c>
-      <c r="B231" s="16" t="s">
-        <v>350</v>
-      </c>
-      <c r="C231" s="16"/>
-      <c r="D231" s="16" t="s">
-        <v>351</v>
-      </c>
-      <c r="E231" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="F231" s="16"/>
-      <c r="G231" s="16"/>
-      <c r="H231" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I231" s="16"/>
-      <c r="J231" s="16"/>
-      <c r="K231" s="16"/>
-      <c r="L231" s="16"/>
-      <c r="M231" s="16"/>
-      <c r="N231" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O231" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="P231" s="17"/>
-    </row>
-    <row r="232" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A232" s="14" t="str">
-        <f t="shared" si="17"/>
-        <v>ACTRIS_ctrl_lists:telecovertest</v>
-      </c>
-      <c r="B232" s="16" t="s">
-        <v>352</v>
-      </c>
-      <c r="C232" s="16"/>
-      <c r="D232" s="16" t="s">
-        <v>353</v>
-      </c>
-      <c r="E232" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="F232" s="16"/>
-      <c r="G232" s="16"/>
-      <c r="H232" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I232" s="16"/>
-      <c r="J232" s="16"/>
-      <c r="K232" s="16"/>
-      <c r="L232" s="16"/>
-      <c r="M232" s="16"/>
-      <c r="N232" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O232" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="P232" s="17"/>
-    </row>
-    <row r="233" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A233" s="14" t="str">
-        <f t="shared" si="17"/>
-        <v>ACTRIS_ctrl_lists:Rayleightfittest</v>
-      </c>
-      <c r="B233" s="16" t="s">
-        <v>354</v>
-      </c>
-      <c r="C233" s="16"/>
-      <c r="D233" s="16" t="s">
-        <v>355</v>
-      </c>
-      <c r="E233" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="F233" s="16"/>
-      <c r="G233" s="16"/>
-      <c r="H233" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I233" s="16"/>
-      <c r="J233" s="16"/>
-      <c r="K233" s="16"/>
-      <c r="L233" s="16"/>
-      <c r="M233" s="16"/>
-      <c r="N233" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O233" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="P233" s="17"/>
-    </row>
-    <row r="234" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A234" s="14" t="str">
-        <f t="shared" si="17"/>
-        <v>ACTRIS_ctrl_lists:fulloverlapminimumheighttest</v>
-      </c>
-      <c r="B234" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="C234" s="16"/>
-      <c r="D234" s="16" t="s">
-        <v>357</v>
-      </c>
-      <c r="E234" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="F234" s="16"/>
-      <c r="G234" s="16"/>
-      <c r="H234" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I234" s="16"/>
-      <c r="J234" s="16"/>
-      <c r="K234" s="16"/>
-      <c r="L234" s="16"/>
-      <c r="M234" s="16"/>
-      <c r="N234" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O234" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="P234" s="17"/>
-    </row>
-    <row r="235" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A235" s="14" t="str">
-        <f t="shared" si="17"/>
-        <v>ACTRIS_ctrl_lists:triggerdelaytest</v>
-      </c>
-      <c r="B235" s="16" t="s">
-        <v>358</v>
-      </c>
-      <c r="C235" s="16"/>
-      <c r="D235" s="16" t="s">
-        <v>359</v>
-      </c>
-      <c r="E235" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="F235" s="16"/>
-      <c r="G235" s="16"/>
-      <c r="H235" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I235" s="16"/>
-      <c r="J235" s="16"/>
-      <c r="K235" s="16"/>
-      <c r="L235" s="16"/>
-      <c r="M235" s="16"/>
-      <c r="N235" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O235" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="P235" s="17"/>
-    </row>
-    <row r="236" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A236" s="14" t="str">
-        <f t="shared" si="17"/>
-        <v>ACTRIS_ctrl_lists:darkcurrenttest</v>
-      </c>
-      <c r="B236" s="16" t="s">
-        <v>360</v>
-      </c>
-      <c r="C236" s="16"/>
-      <c r="D236" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="E236" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="F236" s="16"/>
-      <c r="G236" s="16"/>
-      <c r="H236" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I236" s="16"/>
-      <c r="J236" s="16"/>
-      <c r="K236" s="16"/>
-      <c r="L236" s="16"/>
-      <c r="M236" s="16"/>
-      <c r="N236" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O236" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="P236" s="17"/>
-    </row>
-    <row r="237" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A237" s="14" t="str">
-        <f t="shared" si="17"/>
-        <v>ACTRIS_ctrl_lists:offsetanglecheck</v>
-      </c>
-      <c r="B237" s="16" t="s">
-        <v>362</v>
-      </c>
-      <c r="C237" s="16"/>
-      <c r="D237" s="16" t="s">
-        <v>363</v>
-      </c>
-      <c r="E237" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="F237" s="16"/>
-      <c r="G237" s="16"/>
-      <c r="H237" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I237" s="16"/>
-      <c r="J237" s="16"/>
-      <c r="K237" s="16"/>
-      <c r="L237" s="16"/>
-      <c r="M237" s="16"/>
-      <c r="N237" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O237" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="P237" s="17"/>
-    </row>
-    <row r="238" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A238" s="14" t="str">
-        <f t="shared" si="17"/>
-        <v>ACTRIS_ctrl_lists:calibrationfactorcheck</v>
-      </c>
-      <c r="B238" s="16" t="s">
-        <v>364</v>
-      </c>
-      <c r="C238" s="16"/>
-      <c r="D238" s="16" t="s">
-        <v>365</v>
-      </c>
-      <c r="E238" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="F238" s="16"/>
-      <c r="G238" s="16"/>
-      <c r="H238" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I238" s="16"/>
-      <c r="J238" s="16"/>
-      <c r="K238" s="16"/>
-      <c r="L238" s="16"/>
-      <c r="M238" s="16"/>
-      <c r="N238" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O238" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="P238" s="17"/>
-    </row>
-    <row r="239" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A239" s="14" t="str">
-        <f t="shared" si="17"/>
-        <v>ACTRIS_ctrl_lists:GHKcoefficientscheck</v>
-      </c>
-      <c r="B239" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="C239" s="16"/>
-      <c r="D239" s="16" t="s">
-        <v>367</v>
-      </c>
-      <c r="E239" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="F239" s="16"/>
-      <c r="G239" s="16"/>
-      <c r="H239" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I239" s="16"/>
-      <c r="J239" s="16"/>
-      <c r="K239" s="16"/>
-      <c r="L239" s="16"/>
-      <c r="M239" s="16"/>
-      <c r="N239" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O239" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="P239" s="17"/>
-    </row>
-    <row r="240" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A240" s="14"/>
-      <c r="B240" s="16"/>
-      <c r="C240" s="16"/>
-      <c r="D240" s="16"/>
-      <c r="E240" s="16"/>
-      <c r="F240" s="16"/>
-      <c r="G240" s="16"/>
-      <c r="H240" s="17"/>
-      <c r="I240" s="16"/>
-      <c r="J240" s="16"/>
-      <c r="K240" s="16"/>
-      <c r="L240" s="16"/>
-      <c r="M240" s="16"/>
-      <c r="N240" s="22"/>
-      <c r="O240" s="16"/>
-      <c r="P240" s="17"/>
-    </row>
-    <row r="241" spans="1:16" ht="15" customHeight="1">
-      <c r="A241" s="26" t="str">
-        <f t="shared" ref="A241:A243" si="18">IF(ISBLANK($B241),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B241," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
-        <v>ACTRIS_ctrl_lists:stationaudit</v>
-      </c>
-      <c r="B241" s="27" t="s">
-        <v>327</v>
-      </c>
-      <c r="C241" s="27"/>
-      <c r="D241" s="27"/>
-      <c r="E241" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="F241" s="27" t="s">
-        <v>328</v>
-      </c>
-      <c r="G241" s="27"/>
-      <c r="H241" s="27"/>
-      <c r="I241" s="27"/>
-      <c r="J241" s="27"/>
-      <c r="K241" s="27"/>
-      <c r="L241" s="27"/>
-      <c r="M241" s="27"/>
-      <c r="N241" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="O241" s="27"/>
-      <c r="P241" s="27"/>
-    </row>
-    <row r="242" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A242" s="14" t="str">
-        <f t="shared" si="18"/>
-        <v>ACTRIS_ctrl_lists:checkifprocessedbyCARSapprovedlidarconfiguration</v>
-      </c>
-      <c r="B242" s="16" t="s">
-        <v>368</v>
-      </c>
-      <c r="C242" s="16"/>
-      <c r="D242" s="16" t="s">
-        <v>369</v>
-      </c>
-      <c r="E242" s="16" t="s">
-        <v>333</v>
-      </c>
-      <c r="F242" s="16"/>
-      <c r="G242" s="16"/>
-      <c r="H242" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="I242" s="16"/>
-      <c r="J242" s="16"/>
-      <c r="K242" s="16"/>
-      <c r="L242" s="16"/>
-      <c r="M242" s="16"/>
-      <c r="N242" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="O242" s="16"/>
-      <c r="P242" s="17"/>
+      <c r="F242" s="27" t="s">
+        <v>334</v>
+      </c>
+      <c r="G242" s="27"/>
+      <c r="H242" s="27"/>
+      <c r="I242" s="27"/>
+      <c r="J242" s="27"/>
+      <c r="K242" s="27"/>
+      <c r="L242" s="27"/>
+      <c r="M242" s="27"/>
+      <c r="N242" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="O242" s="27"/>
+      <c r="P242" s="27"/>
     </row>
     <row r="243" spans="1:16" ht="17.25" customHeight="1">
       <c r="A243" s="14" t="str">
+        <f t="shared" si="16"/>
+        <v>ACTRIS_ctrl_lists:Earlinetlegacydatalabeledascirruscontaminated</v>
+      </c>
+      <c r="B243" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="C243" s="16"/>
+      <c r="D243" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="E243" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="F243" s="17"/>
+      <c r="G243" s="17"/>
+      <c r="H243" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I243" s="17"/>
+      <c r="J243" s="17"/>
+      <c r="K243" s="17"/>
+      <c r="L243" s="17"/>
+      <c r="M243" s="17"/>
+      <c r="N243" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O243" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="P243" s="17"/>
+    </row>
+    <row r="244" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A244" s="14" t="str">
+        <f t="shared" si="16"/>
+        <v>ACTRIS_ctrl_lists:checkonatmosphericmolecularcalculationsource</v>
+      </c>
+      <c r="B244" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="C244" s="16"/>
+      <c r="D244" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="E244" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="F244" s="17"/>
+      <c r="G244" s="17"/>
+      <c r="H244" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I244" s="17"/>
+      <c r="J244" s="17"/>
+      <c r="K244" s="17"/>
+      <c r="L244" s="17"/>
+      <c r="M244" s="17"/>
+      <c r="N244" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O244" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="P244" s="17"/>
+    </row>
+    <row r="245" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A245" s="14" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="B245" s="16"/>
+      <c r="C245" s="17"/>
+      <c r="D245" s="16"/>
+      <c r="E245" s="17"/>
+      <c r="F245" s="17"/>
+      <c r="G245" s="17"/>
+      <c r="H245" s="17"/>
+      <c r="I245" s="17"/>
+      <c r="J245" s="17"/>
+      <c r="K245" s="17"/>
+      <c r="L245" s="17"/>
+      <c r="M245" s="17"/>
+      <c r="N245" s="22"/>
+      <c r="O245" s="22"/>
+      <c r="P245" s="17"/>
+    </row>
+    <row r="246" spans="1:16" ht="15" customHeight="1">
+      <c r="A246" s="26" t="str">
+        <f t="shared" ref="A246:A247" si="17">IF(ISBLANK($B246),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B246," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
+        <v>ACTRIS_ctrl_lists:physicaldependencecheck</v>
+      </c>
+      <c r="B246" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="C246" s="27"/>
+      <c r="D246" s="27"/>
+      <c r="E246" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="F246" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="G246" s="27"/>
+      <c r="H246" s="27"/>
+      <c r="I246" s="27"/>
+      <c r="J246" s="27"/>
+      <c r="K246" s="27"/>
+      <c r="L246" s="27"/>
+      <c r="M246" s="27"/>
+      <c r="N246" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="O246" s="27"/>
+      <c r="P246" s="27"/>
+    </row>
+    <row r="247" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A247" s="14" t="str">
+        <f t="shared" si="17"/>
+        <v>ACTRIS_ctrl_lists:consistencyofdifferentopticalproperties</v>
+      </c>
+      <c r="B247" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="C247" s="16"/>
+      <c r="D247" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="E247" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="F247" s="16"/>
+      <c r="G247" s="16"/>
+      <c r="H247" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I247" s="16"/>
+      <c r="J247" s="16"/>
+      <c r="K247" s="16"/>
+      <c r="L247" s="16"/>
+      <c r="M247" s="16"/>
+      <c r="N247" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O247" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="P247" s="17"/>
+    </row>
+    <row r="248" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A248" s="14"/>
+      <c r="B248" s="16"/>
+      <c r="C248" s="16"/>
+      <c r="D248" s="16"/>
+      <c r="E248" s="16"/>
+      <c r="F248" s="16"/>
+      <c r="G248" s="16"/>
+      <c r="H248" s="17"/>
+      <c r="I248" s="16"/>
+      <c r="J248" s="16"/>
+      <c r="K248" s="16"/>
+      <c r="L248" s="16"/>
+      <c r="M248" s="16"/>
+      <c r="N248" s="22"/>
+      <c r="O248" s="16"/>
+      <c r="P248" s="17"/>
+    </row>
+    <row r="249" spans="1:16" ht="15" customHeight="1">
+      <c r="A249" s="26" t="str">
+        <f t="shared" ref="A249:A265" si="18">IF(ISBLANK($B249),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B249," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
+        <v>ACTRIS_ctrl_lists:instrumentstatuscheck</v>
+      </c>
+      <c r="B249" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="C249" s="27"/>
+      <c r="D249" s="27"/>
+      <c r="E249" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="F249" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="G249" s="27"/>
+      <c r="H249" s="27"/>
+      <c r="I249" s="27"/>
+      <c r="J249" s="27"/>
+      <c r="K249" s="27"/>
+      <c r="L249" s="27"/>
+      <c r="M249" s="27"/>
+      <c r="N249" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="O249" s="27"/>
+      <c r="P249" s="27"/>
+    </row>
+    <row r="250" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A250" s="14" t="str">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="B243" s="16"/>
-      <c r="C243" s="16"/>
-      <c r="D243" s="16"/>
-      <c r="E243" s="16"/>
-      <c r="F243" s="16"/>
-      <c r="G243" s="16"/>
-      <c r="H243" s="17"/>
-      <c r="I243" s="16"/>
-      <c r="J243" s="16"/>
-      <c r="K243" s="16"/>
-      <c r="L243" s="16"/>
-      <c r="M243" s="16"/>
-      <c r="N243" s="22"/>
-      <c r="O243" s="16"/>
-      <c r="P243" s="17"/>
-    </row>
-    <row r="244" spans="1:16" ht="15" customHeight="1">
-      <c r="A244" s="23" t="str">
-        <f t="shared" ref="A244:A245" si="19">IF(ISBLANK($B244),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B244," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
-        <v>ACTRIS_ctrl_lists:cloudremotesensingcontrolledlists</v>
-      </c>
-      <c r="B244" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="C244" s="24"/>
-      <c r="D244" s="24"/>
-      <c r="E244" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="F244" s="24"/>
-      <c r="G244" s="24"/>
-      <c r="H244" s="24"/>
-      <c r="I244" s="24"/>
-      <c r="J244" s="24"/>
-      <c r="K244" s="24"/>
-      <c r="L244" s="24"/>
-      <c r="M244" s="24"/>
-      <c r="N244" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="O244" s="24"/>
-      <c r="P244" s="24"/>
-    </row>
-    <row r="245" spans="1:16" ht="15" customHeight="1">
-      <c r="A245" s="26" t="str">
+        <v>ACTRIS_ctrl_lists:batterylevelcheck</v>
+      </c>
+      <c r="B250" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="C250" s="16"/>
+      <c r="D250" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="E250" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F250" s="16"/>
+      <c r="G250" s="16"/>
+      <c r="H250" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I250" s="16"/>
+      <c r="J250" s="16"/>
+      <c r="K250" s="16"/>
+      <c r="L250" s="16"/>
+      <c r="M250" s="16"/>
+      <c r="N250" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O250" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="P250" s="17"/>
+    </row>
+    <row r="251" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A251" s="14" t="str">
+        <f t="shared" si="18"/>
+        <v>ACTRIS_ctrl_lists:trackingsystemcheck</v>
+      </c>
+      <c r="B251" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="C251" s="16"/>
+      <c r="D251" s="16" t="s">
+        <v>339</v>
+      </c>
+      <c r="E251" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F251" s="16"/>
+      <c r="G251" s="16"/>
+      <c r="H251" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I251" s="16"/>
+      <c r="J251" s="16"/>
+      <c r="K251" s="16"/>
+      <c r="L251" s="16"/>
+      <c r="M251" s="16"/>
+      <c r="N251" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O251" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="P251" s="17"/>
+    </row>
+    <row r="252" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A252" s="14" t="str">
+        <f t="shared" si="18"/>
+        <v>ACTRIS_ctrl_lists:humiditysensorcheck</v>
+      </c>
+      <c r="B252" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="C252" s="16"/>
+      <c r="D252" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="E252" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F252" s="16"/>
+      <c r="G252" s="16"/>
+      <c r="H252" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I252" s="16"/>
+      <c r="J252" s="16"/>
+      <c r="K252" s="16"/>
+      <c r="L252" s="16"/>
+      <c r="M252" s="16"/>
+      <c r="N252" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O252" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="P252" s="17"/>
+    </row>
+    <row r="253" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A253" s="14" t="str">
+        <f t="shared" si="18"/>
+        <v>ACTRIS_ctrl_lists:temperaturesensorcheck</v>
+      </c>
+      <c r="B253" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="C253" s="16"/>
+      <c r="D253" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="E253" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F253" s="16"/>
+      <c r="G253" s="16"/>
+      <c r="H253" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I253" s="16"/>
+      <c r="J253" s="16"/>
+      <c r="K253" s="16"/>
+      <c r="L253" s="16"/>
+      <c r="M253" s="16"/>
+      <c r="N253" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O253" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="P253" s="17"/>
+    </row>
+    <row r="254" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A254" s="14" t="str">
+        <f t="shared" si="18"/>
+        <v>ACTRIS_ctrl_lists:calibrationshiftcheck</v>
+      </c>
+      <c r="B254" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="C254" s="16"/>
+      <c r="D254" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="E254" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F254" s="16"/>
+      <c r="G254" s="16"/>
+      <c r="H254" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I254" s="16"/>
+      <c r="J254" s="16"/>
+      <c r="K254" s="16"/>
+      <c r="L254" s="16"/>
+      <c r="M254" s="16"/>
+      <c r="N254" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O254" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="P254" s="17"/>
+    </row>
+    <row r="255" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A255" s="14" t="str">
+        <f t="shared" si="18"/>
+        <v>ACTRIS_ctrl_lists:opticscheck</v>
+      </c>
+      <c r="B255" s="16" t="s">
+        <v>346</v>
+      </c>
+      <c r="C255" s="16"/>
+      <c r="D255" s="16" t="s">
+        <v>347</v>
+      </c>
+      <c r="E255" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F255" s="16"/>
+      <c r="G255" s="16"/>
+      <c r="H255" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I255" s="16"/>
+      <c r="J255" s="16"/>
+      <c r="K255" s="16"/>
+      <c r="L255" s="16"/>
+      <c r="M255" s="16"/>
+      <c r="N255" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O255" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="P255" s="17"/>
+    </row>
+    <row r="256" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A256" s="14" t="str">
+        <f t="shared" si="18"/>
+        <v>ACTRIS_ctrl_lists:collimatorcheck</v>
+      </c>
+      <c r="B256" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="C256" s="16"/>
+      <c r="D256" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="E256" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F256" s="16"/>
+      <c r="G256" s="16"/>
+      <c r="H256" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I256" s="16"/>
+      <c r="J256" s="16"/>
+      <c r="K256" s="16"/>
+      <c r="L256" s="16"/>
+      <c r="M256" s="16"/>
+      <c r="N256" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O256" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="P256" s="17"/>
+    </row>
+    <row r="257" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A257" s="14" t="str">
+        <f t="shared" si="18"/>
+        <v>ACTRIS_ctrl_lists:systemcablingcheck</v>
+      </c>
+      <c r="B257" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="C257" s="16"/>
+      <c r="D257" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="E257" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F257" s="16"/>
+      <c r="G257" s="16"/>
+      <c r="H257" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I257" s="16"/>
+      <c r="J257" s="16"/>
+      <c r="K257" s="16"/>
+      <c r="L257" s="16"/>
+      <c r="M257" s="16"/>
+      <c r="N257" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O257" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="P257" s="17"/>
+    </row>
+    <row r="258" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A258" s="14" t="str">
+        <f t="shared" si="18"/>
+        <v>ACTRIS_ctrl_lists:telecovertest</v>
+      </c>
+      <c r="B258" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="C258" s="16"/>
+      <c r="D258" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="E258" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F258" s="16"/>
+      <c r="G258" s="16"/>
+      <c r="H258" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I258" s="16"/>
+      <c r="J258" s="16"/>
+      <c r="K258" s="16"/>
+      <c r="L258" s="16"/>
+      <c r="M258" s="16"/>
+      <c r="N258" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O258" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="P258" s="17"/>
+    </row>
+    <row r="259" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A259" s="14" t="str">
+        <f t="shared" si="18"/>
+        <v>ACTRIS_ctrl_lists:Rayleightfittest</v>
+      </c>
+      <c r="B259" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="C259" s="16"/>
+      <c r="D259" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="E259" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F259" s="16"/>
+      <c r="G259" s="16"/>
+      <c r="H259" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I259" s="16"/>
+      <c r="J259" s="16"/>
+      <c r="K259" s="16"/>
+      <c r="L259" s="16"/>
+      <c r="M259" s="16"/>
+      <c r="N259" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O259" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="P259" s="17"/>
+    </row>
+    <row r="260" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A260" s="14" t="str">
+        <f t="shared" si="18"/>
+        <v>ACTRIS_ctrl_lists:fulloverlapminimumheighttest</v>
+      </c>
+      <c r="B260" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="C260" s="16"/>
+      <c r="D260" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="E260" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F260" s="16"/>
+      <c r="G260" s="16"/>
+      <c r="H260" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I260" s="16"/>
+      <c r="J260" s="16"/>
+      <c r="K260" s="16"/>
+      <c r="L260" s="16"/>
+      <c r="M260" s="16"/>
+      <c r="N260" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O260" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="P260" s="17"/>
+    </row>
+    <row r="261" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A261" s="14" t="str">
+        <f t="shared" si="18"/>
+        <v>ACTRIS_ctrl_lists:triggerdelaytest</v>
+      </c>
+      <c r="B261" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="C261" s="16"/>
+      <c r="D261" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="E261" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F261" s="16"/>
+      <c r="G261" s="16"/>
+      <c r="H261" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I261" s="16"/>
+      <c r="J261" s="16"/>
+      <c r="K261" s="16"/>
+      <c r="L261" s="16"/>
+      <c r="M261" s="16"/>
+      <c r="N261" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O261" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="P261" s="17"/>
+    </row>
+    <row r="262" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A262" s="14" t="str">
+        <f t="shared" si="18"/>
+        <v>ACTRIS_ctrl_lists:darkcurrenttest</v>
+      </c>
+      <c r="B262" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="C262" s="16"/>
+      <c r="D262" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="E262" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F262" s="16"/>
+      <c r="G262" s="16"/>
+      <c r="H262" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I262" s="16"/>
+      <c r="J262" s="16"/>
+      <c r="K262" s="16"/>
+      <c r="L262" s="16"/>
+      <c r="M262" s="16"/>
+      <c r="N262" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O262" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="P262" s="17"/>
+    </row>
+    <row r="263" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A263" s="14" t="str">
+        <f t="shared" si="18"/>
+        <v>ACTRIS_ctrl_lists:offsetanglecheck</v>
+      </c>
+      <c r="B263" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="C263" s="16"/>
+      <c r="D263" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="E263" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F263" s="16"/>
+      <c r="G263" s="16"/>
+      <c r="H263" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I263" s="16"/>
+      <c r="J263" s="16"/>
+      <c r="K263" s="16"/>
+      <c r="L263" s="16"/>
+      <c r="M263" s="16"/>
+      <c r="N263" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O263" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="P263" s="17"/>
+    </row>
+    <row r="264" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A264" s="14" t="str">
+        <f t="shared" si="18"/>
+        <v>ACTRIS_ctrl_lists:calibrationfactorcheck</v>
+      </c>
+      <c r="B264" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="C264" s="16"/>
+      <c r="D264" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="E264" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F264" s="16"/>
+      <c r="G264" s="16"/>
+      <c r="H264" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I264" s="16"/>
+      <c r="J264" s="16"/>
+      <c r="K264" s="16"/>
+      <c r="L264" s="16"/>
+      <c r="M264" s="16"/>
+      <c r="N264" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O264" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="P264" s="17"/>
+    </row>
+    <row r="265" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A265" s="14" t="str">
+        <f t="shared" si="18"/>
+        <v>ACTRIS_ctrl_lists:GHKcoefficientscheck</v>
+      </c>
+      <c r="B265" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="C265" s="16"/>
+      <c r="D265" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="E265" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="F265" s="16"/>
+      <c r="G265" s="16"/>
+      <c r="H265" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I265" s="16"/>
+      <c r="J265" s="16"/>
+      <c r="K265" s="16"/>
+      <c r="L265" s="16"/>
+      <c r="M265" s="16"/>
+      <c r="N265" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O265" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="P265" s="17"/>
+    </row>
+    <row r="266" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A266" s="14"/>
+      <c r="B266" s="16"/>
+      <c r="C266" s="16"/>
+      <c r="D266" s="16"/>
+      <c r="E266" s="16"/>
+      <c r="F266" s="16"/>
+      <c r="G266" s="16"/>
+      <c r="H266" s="17"/>
+      <c r="I266" s="16"/>
+      <c r="J266" s="16"/>
+      <c r="K266" s="16"/>
+      <c r="L266" s="16"/>
+      <c r="M266" s="16"/>
+      <c r="N266" s="22"/>
+      <c r="O266" s="16"/>
+      <c r="P266" s="17"/>
+    </row>
+    <row r="267" spans="1:16" ht="15" customHeight="1">
+      <c r="A267" s="26" t="str">
+        <f t="shared" ref="A267:A269" si="19">IF(ISBLANK($B267),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B267," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
+        <v>ACTRIS_ctrl_lists:stationaudit</v>
+      </c>
+      <c r="B267" s="27" t="s">
+        <v>327</v>
+      </c>
+      <c r="C267" s="27"/>
+      <c r="D267" s="27"/>
+      <c r="E267" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="F267" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="G267" s="27"/>
+      <c r="H267" s="27"/>
+      <c r="I267" s="27"/>
+      <c r="J267" s="27"/>
+      <c r="K267" s="27"/>
+      <c r="L267" s="27"/>
+      <c r="M267" s="27"/>
+      <c r="N267" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="O267" s="27"/>
+      <c r="P267" s="27"/>
+    </row>
+    <row r="268" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A268" s="14" t="str">
+        <f t="shared" si="19"/>
+        <v>ACTRIS_ctrl_lists:checkifprocessedbyCARSapprovedlidarconfiguration</v>
+      </c>
+      <c r="B268" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="C268" s="16"/>
+      <c r="D268" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="E268" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="F268" s="16"/>
+      <c r="G268" s="16"/>
+      <c r="H268" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="I268" s="16"/>
+      <c r="J268" s="16"/>
+      <c r="K268" s="16"/>
+      <c r="L268" s="16"/>
+      <c r="M268" s="16"/>
+      <c r="N268" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="O268" s="16"/>
+      <c r="P268" s="17"/>
+    </row>
+    <row r="269" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A269" s="14" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="B245" s="27"/>
-      <c r="C245" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="D245" s="27"/>
-      <c r="E245" s="27"/>
-      <c r="F245" s="27"/>
-      <c r="G245" s="27"/>
-      <c r="H245" s="27"/>
-      <c r="I245" s="27"/>
-      <c r="J245" s="27"/>
-      <c r="K245" s="27"/>
-      <c r="L245" s="27"/>
-      <c r="M245" s="27"/>
-      <c r="N245" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="O245" s="27"/>
-      <c r="P245" s="27"/>
-    </row>
-    <row r="246" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A246" s="14"/>
-      <c r="B246" s="16"/>
-      <c r="C246" s="17"/>
-      <c r="D246" s="16"/>
-      <c r="E246" s="17"/>
-      <c r="F246" s="17"/>
-      <c r="G246" s="17"/>
-      <c r="H246" s="17"/>
-      <c r="I246" s="17"/>
-      <c r="J246" s="17"/>
-      <c r="K246" s="17"/>
-      <c r="L246" s="17"/>
-      <c r="M246" s="17"/>
-      <c r="N246" s="22"/>
-      <c r="O246" s="22"/>
-      <c r="P246" s="17"/>
-    </row>
-    <row r="247" spans="1:16" ht="15" customHeight="1">
-      <c r="A247" s="23" t="str">
-        <f t="shared" ref="A247:A248" si="20">IF(ISBLANK($B247),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B247," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
-        <v>ACTRIS_ctrl_lists:reactivetracegasremotesensingcontrolledlists</v>
-      </c>
-      <c r="B247" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="C247" s="24"/>
-      <c r="D247" s="24"/>
-      <c r="E247" s="24" t="s">
+      <c r="B269" s="16"/>
+      <c r="C269" s="16"/>
+      <c r="D269" s="16"/>
+      <c r="E269" s="16"/>
+      <c r="F269" s="16"/>
+      <c r="G269" s="16"/>
+      <c r="H269" s="17"/>
+      <c r="I269" s="16"/>
+      <c r="J269" s="16"/>
+      <c r="K269" s="16"/>
+      <c r="L269" s="16"/>
+      <c r="M269" s="16"/>
+      <c r="N269" s="22"/>
+      <c r="O269" s="16"/>
+      <c r="P269" s="17"/>
+    </row>
+    <row r="270" spans="1:16" ht="15" customHeight="1">
+      <c r="A270" s="23" t="str">
+        <f t="shared" ref="A270:A271" si="20">IF(ISBLANK($B270),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B270," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
+        <v>ACTRIS_ctrl_lists:cloudremotesensingcontrolledlists</v>
+      </c>
+      <c r="B270" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="C270" s="24"/>
+      <c r="D270" s="24"/>
+      <c r="E270" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="F247" s="24"/>
-      <c r="G247" s="24"/>
-      <c r="H247" s="24"/>
-      <c r="I247" s="24"/>
-      <c r="J247" s="24"/>
-      <c r="K247" s="24"/>
-      <c r="L247" s="24"/>
-      <c r="M247" s="24"/>
-      <c r="N247" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="O247" s="24"/>
-      <c r="P247" s="24"/>
-    </row>
-    <row r="248" spans="1:16" ht="15" customHeight="1">
-      <c r="A248" s="26" t="str">
+      <c r="F270" s="24"/>
+      <c r="G270" s="24"/>
+      <c r="H270" s="24"/>
+      <c r="I270" s="24"/>
+      <c r="J270" s="24"/>
+      <c r="K270" s="24"/>
+      <c r="L270" s="24"/>
+      <c r="M270" s="24"/>
+      <c r="N270" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="O270" s="24"/>
+      <c r="P270" s="24"/>
+    </row>
+    <row r="271" spans="1:16" ht="15" customHeight="1">
+      <c r="A271" s="26" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="B248" s="27"/>
-      <c r="C248" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="D248" s="27"/>
-      <c r="E248" s="27"/>
-      <c r="F248" s="27"/>
-      <c r="G248" s="27"/>
-      <c r="H248" s="27"/>
-      <c r="I248" s="27"/>
-      <c r="J248" s="27"/>
-      <c r="K248" s="27"/>
-      <c r="L248" s="27"/>
-      <c r="M248" s="27"/>
-      <c r="N248" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="O248" s="27"/>
-      <c r="P248" s="27"/>
-    </row>
-    <row r="249" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A249" s="14" t="str">
-        <f t="shared" ref="A249:A255" si="21">IF(ISBLANK($B249),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B249," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
-        <v/>
-      </c>
-      <c r="B249" s="16"/>
-      <c r="C249" s="17"/>
-      <c r="D249" s="16"/>
-      <c r="E249" s="16"/>
-      <c r="F249" s="17"/>
-      <c r="G249" s="17"/>
-      <c r="H249" s="17"/>
-      <c r="I249" s="17"/>
-      <c r="J249" s="17"/>
-      <c r="K249" s="17"/>
-      <c r="L249" s="17"/>
-      <c r="M249" s="17"/>
-      <c r="N249" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="O249" s="22"/>
-      <c r="P249" s="17"/>
-    </row>
-    <row r="250" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A250" s="14" t="str">
+      <c r="B271" s="27"/>
+      <c r="C271" s="27" t="s">
+        <v>200</v>
+      </c>
+      <c r="D271" s="27"/>
+      <c r="E271" s="27"/>
+      <c r="F271" s="27"/>
+      <c r="G271" s="27"/>
+      <c r="H271" s="27"/>
+      <c r="I271" s="27"/>
+      <c r="J271" s="27"/>
+      <c r="K271" s="27"/>
+      <c r="L271" s="27"/>
+      <c r="M271" s="27"/>
+      <c r="N271" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="O271" s="27"/>
+      <c r="P271" s="27"/>
+    </row>
+    <row r="272" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A272" s="14"/>
+      <c r="B272" s="16"/>
+      <c r="C272" s="17"/>
+      <c r="D272" s="16"/>
+      <c r="E272" s="17"/>
+      <c r="F272" s="17"/>
+      <c r="G272" s="17"/>
+      <c r="H272" s="17"/>
+      <c r="I272" s="17"/>
+      <c r="J272" s="17"/>
+      <c r="K272" s="17"/>
+      <c r="L272" s="17"/>
+      <c r="M272" s="17"/>
+      <c r="N272" s="22"/>
+      <c r="O272" s="22"/>
+      <c r="P272" s="17"/>
+    </row>
+    <row r="273" spans="1:16" ht="15" customHeight="1">
+      <c r="A273" s="23" t="str">
+        <f t="shared" ref="A273:A274" si="21">IF(ISBLANK($B273),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B273," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
+        <v>ACTRIS_ctrl_lists:reactivetracegasremotesensingcontrolledlists</v>
+      </c>
+      <c r="B273" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="C273" s="24"/>
+      <c r="D273" s="24"/>
+      <c r="E273" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="F273" s="24"/>
+      <c r="G273" s="24"/>
+      <c r="H273" s="24"/>
+      <c r="I273" s="24"/>
+      <c r="J273" s="24"/>
+      <c r="K273" s="24"/>
+      <c r="L273" s="24"/>
+      <c r="M273" s="24"/>
+      <c r="N273" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="O273" s="24"/>
+      <c r="P273" s="24"/>
+    </row>
+    <row r="274" spans="1:16" ht="15" customHeight="1">
+      <c r="A274" s="26" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="B250" s="17"/>
-      <c r="C250" s="17"/>
-      <c r="D250" s="16"/>
-      <c r="E250" s="16"/>
-      <c r="F250" s="17"/>
-      <c r="G250" s="17"/>
-      <c r="H250" s="17"/>
-      <c r="I250" s="17"/>
-      <c r="J250" s="17"/>
-      <c r="K250" s="17"/>
-      <c r="L250" s="17"/>
-      <c r="M250" s="17"/>
-      <c r="N250" s="22"/>
-      <c r="O250" s="22"/>
-      <c r="P250" s="17"/>
-    </row>
-    <row r="251" spans="1:16" ht="15" customHeight="1">
-      <c r="A251" s="11" t="str">
-        <f t="shared" si="21"/>
+      <c r="B274" s="27"/>
+      <c r="C274" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="D274" s="27"/>
+      <c r="E274" s="27"/>
+      <c r="F274" s="27"/>
+      <c r="G274" s="27"/>
+      <c r="H274" s="27"/>
+      <c r="I274" s="27"/>
+      <c r="J274" s="27"/>
+      <c r="K274" s="27"/>
+      <c r="L274" s="27"/>
+      <c r="M274" s="27"/>
+      <c r="N274" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="O274" s="27"/>
+      <c r="P274" s="27"/>
+    </row>
+    <row r="275" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A275" s="14" t="str">
+        <f t="shared" ref="A275:A281" si="22">IF(ISBLANK($B275),"",$B$2 &amp; ":" &amp; (SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B275," ",""),"/","Div"),",","-"),"(","-"),")",""),"+","plus"),"--","-")," ",""),"&amp;","-")))</f>
         <v/>
       </c>
-      <c r="B251" s="12"/>
-      <c r="C251" s="12"/>
-      <c r="D251" s="12"/>
-      <c r="E251" s="12"/>
-      <c r="F251" s="12"/>
-      <c r="G251" s="12"/>
-      <c r="H251" s="12"/>
-      <c r="I251" s="12"/>
-      <c r="J251" s="12"/>
-      <c r="K251" s="12"/>
-      <c r="L251" s="12"/>
-      <c r="M251" s="12"/>
-      <c r="N251" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="O251" s="12"/>
-      <c r="P251" s="12"/>
-    </row>
-    <row r="252" spans="1:16" ht="15" customHeight="1">
-      <c r="A252" s="23" t="str">
-        <f t="shared" si="21"/>
+      <c r="B275" s="16"/>
+      <c r="C275" s="17"/>
+      <c r="D275" s="16"/>
+      <c r="E275" s="16"/>
+      <c r="F275" s="17"/>
+      <c r="G275" s="17"/>
+      <c r="H275" s="17"/>
+      <c r="I275" s="17"/>
+      <c r="J275" s="17"/>
+      <c r="K275" s="17"/>
+      <c r="L275" s="17"/>
+      <c r="M275" s="17"/>
+      <c r="N275" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="O275" s="22"/>
+      <c r="P275" s="17"/>
+    </row>
+    <row r="276" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A276" s="14" t="str">
+        <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="B252" s="24"/>
-      <c r="C252" s="24"/>
-      <c r="D252" s="24"/>
-      <c r="E252" s="24"/>
-      <c r="F252" s="24"/>
-      <c r="G252" s="24"/>
-      <c r="H252" s="24"/>
-      <c r="I252" s="24"/>
-      <c r="J252" s="24"/>
-      <c r="K252" s="24"/>
-      <c r="L252" s="24"/>
-      <c r="M252" s="24"/>
-      <c r="N252" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="O252" s="24"/>
-      <c r="P252" s="24"/>
-    </row>
-    <row r="253" spans="1:16" ht="15" customHeight="1">
-      <c r="A253" s="26" t="str">
-        <f t="shared" si="21"/>
+      <c r="B276" s="17"/>
+      <c r="C276" s="17"/>
+      <c r="D276" s="16"/>
+      <c r="E276" s="16"/>
+      <c r="F276" s="17"/>
+      <c r="G276" s="17"/>
+      <c r="H276" s="17"/>
+      <c r="I276" s="17"/>
+      <c r="J276" s="17"/>
+      <c r="K276" s="17"/>
+      <c r="L276" s="17"/>
+      <c r="M276" s="17"/>
+      <c r="N276" s="22"/>
+      <c r="O276" s="22"/>
+      <c r="P276" s="17"/>
+    </row>
+    <row r="277" spans="1:16" ht="15" customHeight="1">
+      <c r="A277" s="11" t="str">
+        <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="B253" s="27"/>
-      <c r="C253" s="27"/>
-      <c r="D253" s="27"/>
-      <c r="E253" s="27"/>
-      <c r="F253" s="27"/>
-      <c r="G253" s="27"/>
-      <c r="H253" s="27"/>
-      <c r="I253" s="27"/>
-      <c r="J253" s="27"/>
-      <c r="K253" s="27"/>
-      <c r="L253" s="27"/>
-      <c r="M253" s="27"/>
-      <c r="N253" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="O253" s="27"/>
-      <c r="P253" s="27"/>
-    </row>
-    <row r="254" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A254" s="14" t="str">
-        <f t="shared" si="21"/>
+      <c r="B277" s="12"/>
+      <c r="C277" s="12"/>
+      <c r="D277" s="12"/>
+      <c r="E277" s="12"/>
+      <c r="F277" s="12"/>
+      <c r="G277" s="12"/>
+      <c r="H277" s="12"/>
+      <c r="I277" s="12"/>
+      <c r="J277" s="12"/>
+      <c r="K277" s="12"/>
+      <c r="L277" s="12"/>
+      <c r="M277" s="12"/>
+      <c r="N277" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="O277" s="12"/>
+      <c r="P277" s="12"/>
+    </row>
+    <row r="278" spans="1:16" ht="15" customHeight="1">
+      <c r="A278" s="23" t="str">
+        <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="B254" s="16"/>
-      <c r="C254" s="17"/>
-      <c r="D254" s="16"/>
-      <c r="E254" s="16"/>
-      <c r="F254" s="17"/>
-      <c r="G254" s="17"/>
-      <c r="H254" s="17"/>
-      <c r="I254" s="17"/>
-      <c r="J254" s="17"/>
-      <c r="K254" s="17"/>
-      <c r="L254" s="17"/>
-      <c r="M254" s="17"/>
-      <c r="N254" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="O254" s="22"/>
-      <c r="P254" s="17"/>
-    </row>
-    <row r="255" spans="1:16" ht="17.25" customHeight="1">
-      <c r="A255" s="14" t="str">
-        <f t="shared" si="21"/>
+      <c r="B278" s="24"/>
+      <c r="C278" s="24"/>
+      <c r="D278" s="24"/>
+      <c r="E278" s="24"/>
+      <c r="F278" s="24"/>
+      <c r="G278" s="24"/>
+      <c r="H278" s="24"/>
+      <c r="I278" s="24"/>
+      <c r="J278" s="24"/>
+      <c r="K278" s="24"/>
+      <c r="L278" s="24"/>
+      <c r="M278" s="24"/>
+      <c r="N278" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="O278" s="24"/>
+      <c r="P278" s="24"/>
+    </row>
+    <row r="279" spans="1:16" ht="15" customHeight="1">
+      <c r="A279" s="26" t="str">
+        <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="B255" s="17"/>
-      <c r="C255" s="17"/>
-      <c r="D255" s="16"/>
-      <c r="E255" s="16"/>
-      <c r="F255" s="17"/>
-      <c r="G255" s="17"/>
-      <c r="H255" s="17"/>
-      <c r="I255" s="17"/>
-      <c r="J255" s="17"/>
-      <c r="K255" s="17"/>
-      <c r="L255" s="17"/>
-      <c r="M255" s="17"/>
-      <c r="N255" s="22"/>
-      <c r="O255" s="22"/>
-      <c r="P255" s="17"/>
+      <c r="B279" s="27"/>
+      <c r="C279" s="27"/>
+      <c r="D279" s="27"/>
+      <c r="E279" s="27"/>
+      <c r="F279" s="27"/>
+      <c r="G279" s="27"/>
+      <c r="H279" s="27"/>
+      <c r="I279" s="27"/>
+      <c r="J279" s="27"/>
+      <c r="K279" s="27"/>
+      <c r="L279" s="27"/>
+      <c r="M279" s="27"/>
+      <c r="N279" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="O279" s="27"/>
+      <c r="P279" s="27"/>
+    </row>
+    <row r="280" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A280" s="14" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="B280" s="16"/>
+      <c r="C280" s="17"/>
+      <c r="D280" s="16"/>
+      <c r="E280" s="16"/>
+      <c r="F280" s="17"/>
+      <c r="G280" s="17"/>
+      <c r="H280" s="17"/>
+      <c r="I280" s="17"/>
+      <c r="J280" s="17"/>
+      <c r="K280" s="17"/>
+      <c r="L280" s="17"/>
+      <c r="M280" s="17"/>
+      <c r="N280" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="O280" s="22"/>
+      <c r="P280" s="17"/>
+    </row>
+    <row r="281" spans="1:16" ht="17.25" customHeight="1">
+      <c r="A281" s="14" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="B281" s="17"/>
+      <c r="C281" s="17"/>
+      <c r="D281" s="16"/>
+      <c r="E281" s="16"/>
+      <c r="F281" s="17"/>
+      <c r="G281" s="17"/>
+      <c r="H281" s="17"/>
+      <c r="I281" s="17"/>
+      <c r="J281" s="17"/>
+      <c r="K281" s="17"/>
+      <c r="L281" s="17"/>
+      <c r="M281" s="17"/>
+      <c r="N281" s="22"/>
+      <c r="O281" s="22"/>
+      <c r="P281" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
@@ -8776,124 +9704,105 @@
     <hyperlink ref="F72" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
     <hyperlink ref="N72" r:id="rId85" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
     <hyperlink ref="O72" r:id="rId86" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="O85" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="N86" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="O86" r:id="rId89" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="N87" r:id="rId90" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="O87" r:id="rId91" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="N88" r:id="rId92" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="O88" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="N90" r:id="rId94" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
-    <hyperlink ref="O90" r:id="rId95" xr:uid="{00000000-0004-0000-0000-000064000000}"/>
-    <hyperlink ref="N91" r:id="rId96" xr:uid="{00000000-0004-0000-0000-000065000000}"/>
-    <hyperlink ref="O91" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000066000000}"/>
-    <hyperlink ref="N92" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000067000000}"/>
-    <hyperlink ref="O92" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000068000000}"/>
-    <hyperlink ref="N93" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000069000000}"/>
-    <hyperlink ref="O93" r:id="rId101" xr:uid="{00000000-0004-0000-0000-00006A000000}"/>
-    <hyperlink ref="N94" r:id="rId102" xr:uid="{00000000-0004-0000-0000-00006B000000}"/>
-    <hyperlink ref="O94" r:id="rId103" xr:uid="{00000000-0004-0000-0000-00006C000000}"/>
-    <hyperlink ref="N95" r:id="rId104" xr:uid="{00000000-0004-0000-0000-00006D000000}"/>
-    <hyperlink ref="O95" r:id="rId105" xr:uid="{00000000-0004-0000-0000-00006E000000}"/>
-    <hyperlink ref="N96" r:id="rId106" xr:uid="{00000000-0004-0000-0000-00006F000000}"/>
-    <hyperlink ref="O96" r:id="rId107" xr:uid="{00000000-0004-0000-0000-000070000000}"/>
-    <hyperlink ref="N97" r:id="rId108" xr:uid="{00000000-0004-0000-0000-000071000000}"/>
-    <hyperlink ref="O97" r:id="rId109" xr:uid="{00000000-0004-0000-0000-000072000000}"/>
-    <hyperlink ref="N98" r:id="rId110" xr:uid="{00000000-0004-0000-0000-000073000000}"/>
-    <hyperlink ref="O98" r:id="rId111" xr:uid="{00000000-0004-0000-0000-000074000000}"/>
-    <hyperlink ref="N99" r:id="rId112" xr:uid="{00000000-0004-0000-0000-000075000000}"/>
-    <hyperlink ref="O99" r:id="rId113" xr:uid="{00000000-0004-0000-0000-000076000000}"/>
-    <hyperlink ref="N100" r:id="rId114" xr:uid="{00000000-0004-0000-0000-000077000000}"/>
-    <hyperlink ref="O100" r:id="rId115" xr:uid="{00000000-0004-0000-0000-000078000000}"/>
-    <hyperlink ref="N101" r:id="rId116" xr:uid="{00000000-0004-0000-0000-000079000000}"/>
-    <hyperlink ref="O101" r:id="rId117" xr:uid="{00000000-0004-0000-0000-00007A000000}"/>
-    <hyperlink ref="N102" r:id="rId118" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
-    <hyperlink ref="O102" r:id="rId119" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
-    <hyperlink ref="N103" r:id="rId120" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
-    <hyperlink ref="O103" r:id="rId121" xr:uid="{00000000-0004-0000-0000-00007E000000}"/>
-    <hyperlink ref="N140" r:id="rId122" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
-    <hyperlink ref="N141" r:id="rId123" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
-    <hyperlink ref="N142" r:id="rId124" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
-    <hyperlink ref="N73" r:id="rId125" xr:uid="{9AF6E984-1653-430E-A3FB-A3D26D9878D9}"/>
-    <hyperlink ref="N104:N106" r:id="rId126" display="https://orcid.org/0000-0002-3380-3470" xr:uid="{C0237BC4-BA79-4297-A3EA-35626BCC8ACE}"/>
-    <hyperlink ref="N66:N69" r:id="rId127" display="https://orcid.org/0000-0002-3380-3470" xr:uid="{705A572F-F571-4480-A1DC-8DBA00CA101F}"/>
-    <hyperlink ref="N64" r:id="rId128" xr:uid="{1B7D45FB-4ED7-4ED1-BBC7-821751CC3EB3}"/>
-    <hyperlink ref="N65" r:id="rId129" xr:uid="{226E8F98-6EA9-42BC-9935-B19751C3752C}"/>
-    <hyperlink ref="N78" r:id="rId130" xr:uid="{265B2C5B-2BD4-4B09-BF2D-1D182ADD6769}"/>
-    <hyperlink ref="N249" r:id="rId131" xr:uid="{BFA3A315-68ED-41AC-A422-E5B270BCAA65}"/>
-    <hyperlink ref="N252" r:id="rId132" xr:uid="{EF50E818-5C00-457D-A67A-B09335A7D545}"/>
-    <hyperlink ref="N253" r:id="rId133" xr:uid="{7271C232-2EEF-47E3-BD2F-E8FCA1B9195C}"/>
-    <hyperlink ref="N254" r:id="rId134" xr:uid="{9B567F81-6F3A-4D2A-B380-E99564D4295D}"/>
-    <hyperlink ref="N156" r:id="rId135" xr:uid="{BEAB9E3F-2C94-4909-9BE6-8DF462A2C30F}"/>
-    <hyperlink ref="N157" r:id="rId136" xr:uid="{111B9A1B-3F82-4F34-9566-46C7A83C04DB}"/>
-    <hyperlink ref="N188" r:id="rId137" xr:uid="{612D57F9-55A6-4BFA-B2C5-222EFEB10181}"/>
-    <hyperlink ref="N189" r:id="rId138" xr:uid="{2354DB23-F51A-45D0-8DC0-494B9A9E76F1}"/>
-    <hyperlink ref="N192" r:id="rId139" xr:uid="{864B7DC4-2B18-48D9-A771-D5C980DC5D0F}"/>
-    <hyperlink ref="N193" r:id="rId140" xr:uid="{76D79C66-0314-4400-BA60-9A4924CE1344}"/>
-    <hyperlink ref="N205" r:id="rId141" xr:uid="{CBDAF360-DD30-4FFE-9873-8D715A36F95E}"/>
-    <hyperlink ref="N206" r:id="rId142" xr:uid="{78708F00-E983-42F1-AD4A-F42143EE0641}"/>
-    <hyperlink ref="N244" r:id="rId143" xr:uid="{0C8BD3CC-3F65-4CDB-9F7F-68AE696A848E}"/>
-    <hyperlink ref="N245" r:id="rId144" xr:uid="{718F6210-5612-476D-BD89-516382F3AC7B}"/>
-    <hyperlink ref="N247" r:id="rId145" xr:uid="{D72136AE-8722-4F19-B815-D2BC69B3790F}"/>
-    <hyperlink ref="N248" r:id="rId146" xr:uid="{63035A47-7690-4D5B-83D1-48366F2115A7}"/>
-    <hyperlink ref="N148" r:id="rId147" xr:uid="{DB3FA559-07DB-4E3F-8F33-03E67AA6594B}"/>
-    <hyperlink ref="N143:N146" r:id="rId148" display="https://orcid.org/0000-0002-3380-3470" xr:uid="{3B067DB1-3926-4DF6-B802-C6C41B490EE4}"/>
-    <hyperlink ref="N149:N153" r:id="rId149" display="https://orcid.org/0000-0002-3380-3470" xr:uid="{72F1B155-0CBB-46FF-8205-A0C52E9A070F}"/>
-    <hyperlink ref="N158:N160" r:id="rId150" display="https://orcid.org/0000-0002-3380-3470" xr:uid="{8B4DB69A-EF9C-4ADB-9268-6813A7479022}"/>
-    <hyperlink ref="N113:N137" r:id="rId151" display="https://orcid.org/0000-0002-3380-3470" xr:uid="{D910B8A1-D308-48B2-83CB-146A9C4481A6}"/>
-    <hyperlink ref="N162" r:id="rId152" xr:uid="{58016CD7-EF7A-440B-8AAD-A1FDB81B8F3D}"/>
-    <hyperlink ref="N173" r:id="rId153" xr:uid="{FDA9C017-8A74-46A8-AA92-4E0F1122BC95}"/>
-    <hyperlink ref="N183" r:id="rId154" xr:uid="{48B4D16D-FB2A-47C8-8020-17F55612FB2A}"/>
-    <hyperlink ref="N163:N171" r:id="rId155" display="https://orcid.org/0000-0002-3380-3470" xr:uid="{A01CF1B5-EF07-41C1-A386-A166C31EBC99}"/>
-    <hyperlink ref="N174:N181" r:id="rId156" display="https://orcid.org/0000-0002-3380-3470" xr:uid="{0B09D58F-EB80-4AE4-BCBF-D63750491C1B}"/>
-    <hyperlink ref="N184:N186" r:id="rId157" display="https://orcid.org/0000-0002-3380-3470" xr:uid="{08882DA6-3D74-4D77-AFAD-80368B236024}"/>
-    <hyperlink ref="N216" r:id="rId158" xr:uid="{5B70B258-A97D-4B44-BF1D-FFF168385287}"/>
-    <hyperlink ref="N220" r:id="rId159" xr:uid="{45D5197C-EA26-4E70-AC31-4F14BB0B807F}"/>
-    <hyperlink ref="O207" r:id="rId160" xr:uid="{1EBB631F-875B-4BF1-82A4-4EE3B6BF14DD}"/>
-    <hyperlink ref="O208" r:id="rId161" xr:uid="{F47C77B2-2114-4C29-8BA1-CA87306CE765}"/>
-    <hyperlink ref="O209" r:id="rId162" xr:uid="{631C74BD-8E3F-4F79-A7DA-0F00D5F75BD7}"/>
-    <hyperlink ref="O210" r:id="rId163" xr:uid="{7B48D6CF-DA5B-413A-8658-A46C468AFD73}"/>
-    <hyperlink ref="O211" r:id="rId164" xr:uid="{90A33C07-7970-43BB-B688-43123EA96ABC}"/>
-    <hyperlink ref="O212" r:id="rId165" xr:uid="{E924623B-DD36-4203-AC65-6AA262ED72AF}"/>
-    <hyperlink ref="O213" r:id="rId166" xr:uid="{333CFBA5-197B-4AE0-8098-B936D7AED0E4}"/>
-    <hyperlink ref="O214" r:id="rId167" xr:uid="{AE3C9486-26CD-4FE1-B731-E1088260BFDD}"/>
-    <hyperlink ref="O217" r:id="rId168" xr:uid="{065E090B-26B6-4790-A342-3B8AB0D890E3}"/>
-    <hyperlink ref="O218" r:id="rId169" xr:uid="{DC972FEE-AB02-4592-BBAE-46E972C5A15E}"/>
-    <hyperlink ref="O221" r:id="rId170" xr:uid="{A5ADFAF1-1FCF-431A-90F5-B3EF956CEAF5}"/>
-    <hyperlink ref="N194" r:id="rId171" xr:uid="{9B663FD4-16F8-42D9-9C80-6F4E2EC4BCD9}"/>
-    <hyperlink ref="N195:N197" r:id="rId172" display="https://orcid.org/0000-0003-0648-6622" xr:uid="{E82137E4-C00F-4A77-AA69-C2CEE9E69A3A}"/>
-    <hyperlink ref="N199" r:id="rId173" xr:uid="{20B711D6-836B-4415-8D55-E8D98729A8EB}"/>
-    <hyperlink ref="N200:N203" r:id="rId174" display="https://orcid.org/0000-0003-0648-6622" xr:uid="{7FFCDCFE-A881-4C0D-8EA8-F5508101BB4C}"/>
-    <hyperlink ref="N223" r:id="rId175" xr:uid="{470FEC31-B0F7-4340-A9D7-6F8436D59027}"/>
-    <hyperlink ref="O224" r:id="rId176" xr:uid="{C14C8BA3-B370-4D24-92A2-EAEF3178542D}"/>
-    <hyperlink ref="O225" r:id="rId177" xr:uid="{7606C661-1B21-43AA-93BD-E87FD900068D}"/>
-    <hyperlink ref="O226" r:id="rId178" xr:uid="{8E39C1EE-7AEE-4F84-9342-E7AC1AFF9599}"/>
-    <hyperlink ref="O227" r:id="rId179" xr:uid="{331573AE-C7EC-460C-9030-5B21AA95DFDF}"/>
-    <hyperlink ref="O228" r:id="rId180" xr:uid="{0A775B8B-BFD5-4254-BB4C-1CA4211AD056}"/>
-    <hyperlink ref="O229" r:id="rId181" xr:uid="{005825C9-6102-4B28-9148-24D9D3C1B4B7}"/>
-    <hyperlink ref="O230" r:id="rId182" xr:uid="{14E29CE9-4BA3-4FCE-BC22-0ED5350CCB03}"/>
-    <hyperlink ref="O231" r:id="rId183" xr:uid="{EB52FA76-8701-4484-9280-6E536C765C64}"/>
-    <hyperlink ref="O232" r:id="rId184" xr:uid="{A80B1F14-419B-41AE-BE92-D0F4EC16BF3D}"/>
-    <hyperlink ref="O233" r:id="rId185" xr:uid="{D5261389-817C-4743-BE43-B2CF88894BC5}"/>
-    <hyperlink ref="O234" r:id="rId186" xr:uid="{55931C1C-D86A-4D54-A70B-46004EAE9041}"/>
-    <hyperlink ref="O235" r:id="rId187" xr:uid="{790A2585-4116-4253-B043-5DDA3345B718}"/>
-    <hyperlink ref="O236" r:id="rId188" xr:uid="{9F7A0555-F908-43E0-9E00-FCB40D75B08F}"/>
-    <hyperlink ref="O237" r:id="rId189" xr:uid="{7AFC96CA-C659-4BFE-9E8C-A5115A9C40F1}"/>
-    <hyperlink ref="O238" r:id="rId190" xr:uid="{C0D68BD3-8356-4705-BFCC-AE58BEB688BC}"/>
-    <hyperlink ref="O239" r:id="rId191" xr:uid="{BFFA46D2-EC1A-45A6-BD66-98F92969FD8A}"/>
-    <hyperlink ref="N241" r:id="rId192" xr:uid="{42E6E708-2690-451E-871F-23B1CB3F06BA}"/>
-    <hyperlink ref="N74" r:id="rId193" xr:uid="{D30F63DA-5786-45D2-A437-17CC24A8E2AE}"/>
-    <hyperlink ref="N75" r:id="rId194" xr:uid="{2AE77B84-F9CF-4A82-B64B-6C0607CC2D5A}"/>
-    <hyperlink ref="B1" r:id="rId195" display="https://vocabulary" xr:uid="{F588C3C7-D754-4249-8CD6-F241F484B7A5}"/>
-    <hyperlink ref="C2" r:id="rId196" display="https://vocabulary" xr:uid="{6D0987C6-CE28-4ED1-B035-2D3E7D0F6D8C}"/>
-    <hyperlink ref="C3" r:id="rId197" xr:uid="{59DA185D-8E47-4646-A4DF-34AFC1FAE925}"/>
+    <hyperlink ref="N86" r:id="rId87" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="N88" r:id="rId88" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="N89" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="N92" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="N166" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00007F000000}"/>
+    <hyperlink ref="N167" r:id="rId92" xr:uid="{00000000-0004-0000-0000-000080000000}"/>
+    <hyperlink ref="N168" r:id="rId93" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
+    <hyperlink ref="N73" r:id="rId94" xr:uid="{9AF6E984-1653-430E-A3FB-A3D26D9878D9}"/>
+    <hyperlink ref="N66:N69" r:id="rId95" display="https://orcid.org/0000-0002-3380-3470" xr:uid="{705A572F-F571-4480-A1DC-8DBA00CA101F}"/>
+    <hyperlink ref="N64" r:id="rId96" xr:uid="{1B7D45FB-4ED7-4ED1-BBC7-821751CC3EB3}"/>
+    <hyperlink ref="N65" r:id="rId97" xr:uid="{226E8F98-6EA9-42BC-9935-B19751C3752C}"/>
+    <hyperlink ref="N78" r:id="rId98" xr:uid="{265B2C5B-2BD4-4B09-BF2D-1D182ADD6769}"/>
+    <hyperlink ref="N275" r:id="rId99" xr:uid="{BFA3A315-68ED-41AC-A422-E5B270BCAA65}"/>
+    <hyperlink ref="N278" r:id="rId100" xr:uid="{EF50E818-5C00-457D-A67A-B09335A7D545}"/>
+    <hyperlink ref="N279" r:id="rId101" xr:uid="{7271C232-2EEF-47E3-BD2F-E8FCA1B9195C}"/>
+    <hyperlink ref="N280" r:id="rId102" xr:uid="{9B567F81-6F3A-4D2A-B380-E99564D4295D}"/>
+    <hyperlink ref="N182" r:id="rId103" xr:uid="{BEAB9E3F-2C94-4909-9BE6-8DF462A2C30F}"/>
+    <hyperlink ref="N183" r:id="rId104" xr:uid="{111B9A1B-3F82-4F34-9566-46C7A83C04DB}"/>
+    <hyperlink ref="N214" r:id="rId105" xr:uid="{612D57F9-55A6-4BFA-B2C5-222EFEB10181}"/>
+    <hyperlink ref="N215" r:id="rId106" xr:uid="{2354DB23-F51A-45D0-8DC0-494B9A9E76F1}"/>
+    <hyperlink ref="N218" r:id="rId107" xr:uid="{864B7DC4-2B18-48D9-A771-D5C980DC5D0F}"/>
+    <hyperlink ref="N219" r:id="rId108" xr:uid="{76D79C66-0314-4400-BA60-9A4924CE1344}"/>
+    <hyperlink ref="N231" r:id="rId109" xr:uid="{CBDAF360-DD30-4FFE-9873-8D715A36F95E}"/>
+    <hyperlink ref="N232" r:id="rId110" xr:uid="{78708F00-E983-42F1-AD4A-F42143EE0641}"/>
+    <hyperlink ref="N270" r:id="rId111" xr:uid="{0C8BD3CC-3F65-4CDB-9F7F-68AE696A848E}"/>
+    <hyperlink ref="N271" r:id="rId112" xr:uid="{718F6210-5612-476D-BD89-516382F3AC7B}"/>
+    <hyperlink ref="N273" r:id="rId113" xr:uid="{D72136AE-8722-4F19-B815-D2BC69B3790F}"/>
+    <hyperlink ref="N274" r:id="rId114" xr:uid="{63035A47-7690-4D5B-83D1-48366F2115A7}"/>
+    <hyperlink ref="N174" r:id="rId115" xr:uid="{DB3FA559-07DB-4E3F-8F33-03E67AA6594B}"/>
+    <hyperlink ref="N169:N172" r:id="rId116" display="https://orcid.org/0000-0002-3380-3470" xr:uid="{3B067DB1-3926-4DF6-B802-C6C41B490EE4}"/>
+    <hyperlink ref="N175:N179" r:id="rId117" display="https://orcid.org/0000-0002-3380-3470" xr:uid="{72F1B155-0CBB-46FF-8205-A0C52E9A070F}"/>
+    <hyperlink ref="N184:N186" r:id="rId118" display="https://orcid.org/0000-0002-3380-3470" xr:uid="{8B4DB69A-EF9C-4ADB-9268-6813A7479022}"/>
+    <hyperlink ref="N139:N163" r:id="rId119" display="https://orcid.org/0000-0002-3380-3470" xr:uid="{D910B8A1-D308-48B2-83CB-146A9C4481A6}"/>
+    <hyperlink ref="N188" r:id="rId120" xr:uid="{58016CD7-EF7A-440B-8AAD-A1FDB81B8F3D}"/>
+    <hyperlink ref="N199" r:id="rId121" xr:uid="{FDA9C017-8A74-46A8-AA92-4E0F1122BC95}"/>
+    <hyperlink ref="N209" r:id="rId122" xr:uid="{48B4D16D-FB2A-47C8-8020-17F55612FB2A}"/>
+    <hyperlink ref="N189:N197" r:id="rId123" display="https://orcid.org/0000-0002-3380-3470" xr:uid="{A01CF1B5-EF07-41C1-A386-A166C31EBC99}"/>
+    <hyperlink ref="N200:N207" r:id="rId124" display="https://orcid.org/0000-0002-3380-3470" xr:uid="{0B09D58F-EB80-4AE4-BCBF-D63750491C1B}"/>
+    <hyperlink ref="N210:N212" r:id="rId125" display="https://orcid.org/0000-0002-3380-3470" xr:uid="{08882DA6-3D74-4D77-AFAD-80368B236024}"/>
+    <hyperlink ref="N242" r:id="rId126" xr:uid="{5B70B258-A97D-4B44-BF1D-FFF168385287}"/>
+    <hyperlink ref="N246" r:id="rId127" xr:uid="{45D5197C-EA26-4E70-AC31-4F14BB0B807F}"/>
+    <hyperlink ref="O233" r:id="rId128" xr:uid="{1EBB631F-875B-4BF1-82A4-4EE3B6BF14DD}"/>
+    <hyperlink ref="O234" r:id="rId129" xr:uid="{F47C77B2-2114-4C29-8BA1-CA87306CE765}"/>
+    <hyperlink ref="O235" r:id="rId130" xr:uid="{631C74BD-8E3F-4F79-A7DA-0F00D5F75BD7}"/>
+    <hyperlink ref="O236" r:id="rId131" xr:uid="{7B48D6CF-DA5B-413A-8658-A46C468AFD73}"/>
+    <hyperlink ref="O237" r:id="rId132" xr:uid="{90A33C07-7970-43BB-B688-43123EA96ABC}"/>
+    <hyperlink ref="O238" r:id="rId133" xr:uid="{E924623B-DD36-4203-AC65-6AA262ED72AF}"/>
+    <hyperlink ref="O239" r:id="rId134" xr:uid="{333CFBA5-197B-4AE0-8098-B936D7AED0E4}"/>
+    <hyperlink ref="O240" r:id="rId135" xr:uid="{AE3C9486-26CD-4FE1-B731-E1088260BFDD}"/>
+    <hyperlink ref="O243" r:id="rId136" xr:uid="{065E090B-26B6-4790-A342-3B8AB0D890E3}"/>
+    <hyperlink ref="O244" r:id="rId137" xr:uid="{DC972FEE-AB02-4592-BBAE-46E972C5A15E}"/>
+    <hyperlink ref="O247" r:id="rId138" xr:uid="{A5ADFAF1-1FCF-431A-90F5-B3EF956CEAF5}"/>
+    <hyperlink ref="N220" r:id="rId139" xr:uid="{9B663FD4-16F8-42D9-9C80-6F4E2EC4BCD9}"/>
+    <hyperlink ref="N221:N223" r:id="rId140" display="https://orcid.org/0000-0003-0648-6622" xr:uid="{E82137E4-C00F-4A77-AA69-C2CEE9E69A3A}"/>
+    <hyperlink ref="N225" r:id="rId141" xr:uid="{20B711D6-836B-4415-8D55-E8D98729A8EB}"/>
+    <hyperlink ref="N226:N229" r:id="rId142" display="https://orcid.org/0000-0003-0648-6622" xr:uid="{7FFCDCFE-A881-4C0D-8EA8-F5508101BB4C}"/>
+    <hyperlink ref="N249" r:id="rId143" xr:uid="{470FEC31-B0F7-4340-A9D7-6F8436D59027}"/>
+    <hyperlink ref="O250" r:id="rId144" xr:uid="{C14C8BA3-B370-4D24-92A2-EAEF3178542D}"/>
+    <hyperlink ref="O251" r:id="rId145" xr:uid="{7606C661-1B21-43AA-93BD-E87FD900068D}"/>
+    <hyperlink ref="O252" r:id="rId146" xr:uid="{8E39C1EE-7AEE-4F84-9342-E7AC1AFF9599}"/>
+    <hyperlink ref="O253" r:id="rId147" xr:uid="{331573AE-C7EC-460C-9030-5B21AA95DFDF}"/>
+    <hyperlink ref="O254" r:id="rId148" xr:uid="{0A775B8B-BFD5-4254-BB4C-1CA4211AD056}"/>
+    <hyperlink ref="O255" r:id="rId149" xr:uid="{005825C9-6102-4B28-9148-24D9D3C1B4B7}"/>
+    <hyperlink ref="O256" r:id="rId150" xr:uid="{14E29CE9-4BA3-4FCE-BC22-0ED5350CCB03}"/>
+    <hyperlink ref="O257" r:id="rId151" xr:uid="{EB52FA76-8701-4484-9280-6E536C765C64}"/>
+    <hyperlink ref="O258" r:id="rId152" xr:uid="{A80B1F14-419B-41AE-BE92-D0F4EC16BF3D}"/>
+    <hyperlink ref="O259" r:id="rId153" xr:uid="{D5261389-817C-4743-BE43-B2CF88894BC5}"/>
+    <hyperlink ref="O260" r:id="rId154" xr:uid="{55931C1C-D86A-4D54-A70B-46004EAE9041}"/>
+    <hyperlink ref="O261" r:id="rId155" xr:uid="{790A2585-4116-4253-B043-5DDA3345B718}"/>
+    <hyperlink ref="O262" r:id="rId156" xr:uid="{9F7A0555-F908-43E0-9E00-FCB40D75B08F}"/>
+    <hyperlink ref="O263" r:id="rId157" xr:uid="{7AFC96CA-C659-4BFE-9E8C-A5115A9C40F1}"/>
+    <hyperlink ref="O264" r:id="rId158" xr:uid="{C0D68BD3-8356-4705-BFCC-AE58BEB688BC}"/>
+    <hyperlink ref="O265" r:id="rId159" xr:uid="{BFFA46D2-EC1A-45A6-BD66-98F92969FD8A}"/>
+    <hyperlink ref="N267" r:id="rId160" xr:uid="{42E6E708-2690-451E-871F-23B1CB3F06BA}"/>
+    <hyperlink ref="N74" r:id="rId161" xr:uid="{D30F63DA-5786-45D2-A437-17CC24A8E2AE}"/>
+    <hyperlink ref="N75" r:id="rId162" xr:uid="{2AE77B84-F9CF-4A82-B64B-6C0607CC2D5A}"/>
+    <hyperlink ref="N90" r:id="rId163" xr:uid="{05F5707B-5CE9-49AC-8381-467DC9D2924C}"/>
+    <hyperlink ref="N91" r:id="rId164" xr:uid="{250CD542-154A-46D8-A2F3-BBB82FCCE88D}"/>
+    <hyperlink ref="N87" r:id="rId165" xr:uid="{41D4693D-E29E-4009-8678-49C50762787E}"/>
+    <hyperlink ref="N93:N132" r:id="rId166" display="https://orcid.org/0000-0002-3380-3470" xr:uid="{7881D7FB-26E1-4464-99D4-141178409ADC}"/>
+    <hyperlink ref="B1" r:id="rId167" display="https://vocabulary" xr:uid="{70A275BE-2965-4418-92CB-935F7A57A4D1}"/>
+    <hyperlink ref="C2" r:id="rId168" display="https://vocabulary" xr:uid="{87234C9B-98F0-4BCC-8344-67DFBE3396FF}"/>
+    <hyperlink ref="C3" r:id="rId169" xr:uid="{D71F6E5D-A839-49CD-943E-877EAADC70BB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId198"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId170"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="48a2b2ea-4ae5-49be-a8c4-5009d504025a">
@@ -8904,7 +9813,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006481788B230DB442BDFB5C65881F7436" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f8fef1c2717e652c18441c3de6c23c6c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="48a2b2ea-4ae5-49be-a8c4-5009d504025a" xmlns:ns3="7fcf429e-959f-41cd-b9fc-3fe372134937" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cf2dbfef60470889a3a6d83395b17bd3" ns2:_="" ns3:_="">
     <xsd:import namespace="48a2b2ea-4ae5-49be-a8c4-5009d504025a"/>
@@ -9165,16 +10074,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BC35E7A-1AF8-4A96-AC97-C8D582699722}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC81F36B-8C49-4A34-8033-560B108372C9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -9185,7 +10093,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{667681BC-BE13-4E21-8924-3641F34D5C45}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9202,12 +10110,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BC35E7A-1AF8-4A96-AC97-C8D582699722}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>